--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -520,31 +520,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.015000000000001</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>8.086</v>
+        <v>8.061</v>
       </c>
       <c r="G2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.023</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.121</v>
+        <v>-0.112</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7151</v>
+        <v>7152</v>
       </c>
       <c r="M2" t="n">
         <v>0.726</v>
@@ -583,31 +583,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="F3" t="n">
-        <v>6.184</v>
+        <v>6.191</v>
       </c>
       <c r="G3" t="n">
         <v>6.22</v>
       </c>
       <c r="H3" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="I3" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08</v>
+        <v>0.064</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14187</v>
+        <v>14188</v>
       </c>
       <c r="M3" t="n">
         <v>0.509</v>
@@ -646,31 +646,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.622</v>
+        <v>4.56</v>
       </c>
       <c r="F4" t="n">
-        <v>4.976</v>
+        <v>4.844</v>
       </c>
       <c r="G4" t="n">
-        <v>5.41</v>
+        <v>5.148</v>
       </c>
       <c r="H4" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="I4" t="n">
-        <v>4.723</v>
+        <v>4.641</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.506</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13791</v>
+        <v>13792</v>
       </c>
       <c r="M4" t="n">
         <v>0.429</v>
@@ -709,31 +709,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11.911</v>
+        <v>11.828</v>
       </c>
       <c r="F5" t="n">
-        <v>12.179</v>
+        <v>12.1</v>
       </c>
       <c r="G5" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="H5" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="I5" t="n">
-        <v>11.989</v>
+        <v>11.83</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.315</v>
+        <v>-0.453</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9794</v>
+        <v>9795</v>
       </c>
       <c r="M5" t="n">
         <v>0.05</v>
@@ -772,31 +772,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>110.56</v>
+        <v>110.021</v>
       </c>
       <c r="F6" t="n">
-        <v>111.725</v>
+        <v>111.384</v>
       </c>
       <c r="G6" t="n">
-        <v>112.174</v>
+        <v>112.08</v>
       </c>
       <c r="H6" t="n">
-        <v>112.161</v>
+        <v>112.06</v>
       </c>
       <c r="I6" t="n">
-        <v>111.15</v>
+        <v>110.579</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.011</v>
+        <v>-1.481</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9954</v>
+        <v>9955</v>
       </c>
       <c r="M6" t="n">
         <v>0.129</v>
@@ -816,7 +816,7 @@
         <v>0.129</v>
       </c>
       <c r="P6" t="n">
-        <v>36.031</v>
+        <v>36.054</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -835,31 +835,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="F7" t="n">
-        <v>9.657999999999999</v>
+        <v>9.145</v>
       </c>
       <c r="G7" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="H7" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="I7" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.413</v>
+        <v>-3.255</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="F8" t="n">
-        <v>8.753</v>
+        <v>8.612</v>
       </c>
       <c r="G8" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.554</v>
+        <v>-0.893</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6444</v>
+        <v>6445</v>
       </c>
       <c r="M8" t="n">
         <v>0.823</v>
@@ -961,31 +961,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.281</v>
+        <v>5.28</v>
       </c>
       <c r="F9" t="n">
-        <v>5.548</v>
+        <v>5.47</v>
       </c>
       <c r="G9" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.283</v>
+        <v>5.302</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.521</v>
+        <v>-0.498</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="M9" t="n">
         <v>0.829</v>
@@ -1024,31 +1024,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="F10" t="n">
-        <v>6.206</v>
+        <v>6.247</v>
       </c>
       <c r="G10" t="n">
-        <v>6.353</v>
+        <v>6.362</v>
       </c>
       <c r="H10" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="I10" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
       <c r="J10" t="n">
-        <v>0.329</v>
+        <v>0.155</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8985</v>
+        <v>8986</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>0.63</v>
@@ -1087,31 +1087,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.952</v>
+        <v>3.846</v>
       </c>
       <c r="F11" t="n">
-        <v>4.89</v>
+        <v>4.707</v>
       </c>
       <c r="G11" t="n">
-        <v>5.452</v>
+        <v>4.969</v>
       </c>
       <c r="H11" t="n">
-        <v>4.756</v>
+        <v>4.668</v>
       </c>
       <c r="I11" t="n">
-        <v>4.649</v>
+        <v>4.313</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.107</v>
+        <v>-0.355</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.547</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6.675</v>
+        <v>6.638</v>
       </c>
       <c r="G12" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="H12" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="I12" t="n">
-        <v>6.548</v>
+        <v>6.509</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.229</v>
+        <v>-0.241</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>14031</v>
+        <v>14032</v>
       </c>
       <c r="M12" t="n">
         <v>0.781</v>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.448</v>
+        <v>10.271</v>
       </c>
       <c r="F13" t="n">
-        <v>10.947</v>
+        <v>10.77</v>
       </c>
       <c r="G13" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="H13" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="I13" t="n">
-        <v>10.462</v>
+        <v>10.348</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.042</v>
+        <v>-1.021</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>0.335</v>
       </c>
       <c r="P13" t="n">
-        <v>2.698</v>
+        <v>2.697</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.693</v>
+        <v>6.85</v>
       </c>
       <c r="F14" t="n">
-        <v>7.03</v>
+        <v>7.052</v>
       </c>
       <c r="G14" t="n">
         <v>7.205</v>
       </c>
       <c r="H14" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="I14" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="J14" t="n">
-        <v>0.364</v>
+        <v>-0.026</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13850</v>
+        <v>13851</v>
       </c>
       <c r="M14" t="n">
         <v>0.762</v>
@@ -1339,39 +1339,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.968</v>
+        <v>6.898</v>
       </c>
       <c r="F15" t="n">
-        <v>7.075</v>
+        <v>7.058</v>
       </c>
       <c r="G15" t="n">
-        <v>7.17</v>
+        <v>7.157</v>
       </c>
       <c r="H15" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="I15" t="n">
-        <v>6.969</v>
+        <v>6.899</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.051</v>
+        <v>-0.191</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8825</v>
+        <v>8826</v>
       </c>
       <c r="M15" t="n">
         <v>0.305</v>
@@ -1402,39 +1402,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.866</v>
+        <v>4.642</v>
       </c>
       <c r="F16" t="n">
-        <v>5.807</v>
+        <v>5.654</v>
       </c>
       <c r="G16" t="n">
-        <v>6.254</v>
+        <v>6.037</v>
       </c>
       <c r="H16" t="n">
-        <v>5.591</v>
+        <v>5.717</v>
       </c>
       <c r="I16" t="n">
-        <v>5.526</v>
+        <v>5.218</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.065</v>
+        <v>-0.499</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="M16" t="n">
         <v>0.6</v>
@@ -1446,7 +1446,7 @@
         <v>0.597</v>
       </c>
       <c r="P16" t="n">
-        <v>1.489</v>
+        <v>1.488</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1465,31 +1465,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.78</v>
+        <v>4.622</v>
       </c>
       <c r="F17" t="n">
-        <v>5.18</v>
+        <v>5.058</v>
       </c>
       <c r="G17" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="H17" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="I17" t="n">
-        <v>4.78</v>
+        <v>4.629</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.703</v>
+        <v>-0.823</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10214</v>
+        <v>10215</v>
       </c>
       <c r="M17" t="n">
         <v>0.867</v>
@@ -1528,31 +1528,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.295</v>
+        <v>3.317</v>
       </c>
       <c r="F18" t="n">
-        <v>3.565</v>
+        <v>3.636</v>
       </c>
       <c r="G18" t="n">
-        <v>3.761</v>
+        <v>3.764</v>
       </c>
       <c r="H18" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="I18" t="n">
-        <v>3.761</v>
+        <v>3.742</v>
       </c>
       <c r="J18" t="n">
-        <v>0.466</v>
+        <v>0.424</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>14532</v>
+        <v>14533</v>
       </c>
       <c r="M18" t="n">
         <v>0.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>0.778</v>
@@ -1671,39 +1671,39 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1716,39 +1716,39 @@
         <v>9043370</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.128</v>
+        <v>8.112</v>
       </c>
       <c r="F3" t="n">
-        <v>8.128</v>
+        <v>8.112</v>
       </c>
       <c r="G3" t="n">
-        <v>8.127000000000001</v>
+        <v>8.113</v>
       </c>
       <c r="H3" t="n">
-        <v>8.127000000000001</v>
+        <v>8.112</v>
       </c>
       <c r="I3" t="n">
-        <v>8.127000000000001</v>
+        <v>8.112</v>
       </c>
       <c r="J3" t="n">
-        <v>8.127000000000001</v>
+        <v>8.112</v>
       </c>
       <c r="K3" t="n">
-        <v>8.127000000000001</v>
+        <v>8.112</v>
       </c>
       <c r="L3" t="n">
-        <v>8.128</v>
+        <v>8.112</v>
       </c>
       <c r="M3" t="n">
-        <v>8.128</v>
+        <v>8.113</v>
       </c>
     </row>
     <row r="4">
@@ -1761,39 +1761,39 @@
         <v>9043370</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.086</v>
       </c>
       <c r="F4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.086</v>
       </c>
       <c r="G4" t="n">
-        <v>8.117000000000001</v>
+        <v>8.087</v>
       </c>
       <c r="H4" t="n">
-        <v>8.116</v>
+        <v>8.083</v>
       </c>
       <c r="I4" t="n">
-        <v>8.116</v>
+        <v>8.083</v>
       </c>
       <c r="J4" t="n">
-        <v>8.117000000000001</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>8.118</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.086</v>
       </c>
       <c r="M4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.087</v>
       </c>
     </row>
     <row r="5">
@@ -1806,39 +1806,39 @@
         <v>9043370</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.095000000000001</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>8.105</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.090999999999999</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>8.081</v>
+        <v>8.045999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>8.081</v>
+        <v>8.045999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>8.087999999999999</v>
+        <v>8.048</v>
       </c>
       <c r="K5" t="n">
-        <v>8.093</v>
+        <v>8.048</v>
       </c>
       <c r="L5" t="n">
-        <v>8.098000000000001</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>8.105</v>
+        <v>8.048999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1851,39 +1851,39 @@
         <v>9043370</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8.071</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>8.08</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>8.042999999999999</v>
+        <v>8.028</v>
       </c>
       <c r="I6" t="n">
-        <v>8.042999999999999</v>
+        <v>8.028</v>
       </c>
       <c r="J6" t="n">
-        <v>8.048</v>
+        <v>8.029</v>
       </c>
       <c r="K6" t="n">
-        <v>8.061</v>
+        <v>8.029</v>
       </c>
       <c r="L6" t="n">
-        <v>8.073</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>8.08</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1896,39 +1896,39 @@
         <v>9043370</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.037000000000001</v>
+        <v>8.018000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>8.050000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="G7" t="n">
-        <v>8.029999999999999</v>
+        <v>8.016999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>8.029999999999999</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.029999999999999</v>
+        <v>8.016</v>
       </c>
       <c r="K7" t="n">
-        <v>8.037000000000001</v>
+        <v>8.016999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.039999999999999</v>
+        <v>8.019</v>
       </c>
       <c r="M7" t="n">
-        <v>8.050000000000001</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="8">
@@ -1941,39 +1941,39 @@
         <v>9043370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.029999999999999</v>
+        <v>8.012</v>
       </c>
       <c r="F8" t="n">
-        <v>8.029999999999999</v>
+        <v>8.012</v>
       </c>
       <c r="G8" t="n">
-        <v>8.018000000000001</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>8.015000000000001</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8.015000000000001</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>8.016999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="K8" t="n">
-        <v>8.023</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>8.029999999999999</v>
+        <v>8.012</v>
       </c>
       <c r="M8" t="n">
-        <v>8.029999999999999</v>
+        <v>8.012</v>
       </c>
     </row>
     <row r="9">
@@ -1986,39 +1986,39 @@
         <v>9036028</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="F9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="G9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="H9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="I9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="J9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="K9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="L9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="M9" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
     </row>
     <row r="10">
@@ -2031,39 +2031,39 @@
         <v>9036028</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="F10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="G10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="H10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="I10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="J10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="K10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="L10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="M10" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="11">
@@ -2076,39 +2076,39 @@
         <v>9036028</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
       <c r="F11" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
       <c r="G11" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="H11" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="I11" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="J11" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="K11" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
       <c r="L11" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
       <c r="M11" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
     </row>
     <row r="12">
@@ -2121,39 +2121,39 @@
         <v>9036028</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.183</v>
+        <v>6.22</v>
       </c>
       <c r="F12" t="n">
-        <v>6.186</v>
+        <v>6.22</v>
       </c>
       <c r="G12" t="n">
-        <v>6.188</v>
+        <v>6.217</v>
       </c>
       <c r="H12" t="n">
-        <v>6.185</v>
+        <v>6.217</v>
       </c>
       <c r="I12" t="n">
-        <v>6.183</v>
+        <v>6.217</v>
       </c>
       <c r="J12" t="n">
-        <v>6.184</v>
+        <v>6.217</v>
       </c>
       <c r="K12" t="n">
-        <v>6.186</v>
+        <v>6.218</v>
       </c>
       <c r="L12" t="n">
-        <v>6.187</v>
+        <v>6.22</v>
       </c>
       <c r="M12" t="n">
-        <v>6.188</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="13">
@@ -2166,11 +2166,11 @@
         <v>9036028</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2211,11 +2211,11 @@
         <v>9036028</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2256,39 +2256,39 @@
         <v>9036028</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="F15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="K15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="M15" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16">
@@ -2301,39 +2301,39 @@
         <v>9040208</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="F16" t="n">
-        <v>5.41</v>
+        <v>5.148</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="H16" t="n">
-        <v>5.41</v>
+        <v>5.146</v>
       </c>
       <c r="I16" t="n">
-        <v>5.41</v>
+        <v>5.146</v>
       </c>
       <c r="J16" t="n">
-        <v>5.41</v>
+        <v>5.146</v>
       </c>
       <c r="K16" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="L16" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="M16" t="n">
-        <v>5.41</v>
+        <v>5.148</v>
       </c>
     </row>
     <row r="17">
@@ -2346,39 +2346,39 @@
         <v>9040208</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.156</v>
+        <v>4.981</v>
       </c>
       <c r="F17" t="n">
-        <v>5.16</v>
+        <v>4.985</v>
       </c>
       <c r="G17" t="n">
-        <v>5.159</v>
+        <v>4.982</v>
       </c>
       <c r="H17" t="n">
-        <v>5.16</v>
+        <v>4.98</v>
       </c>
       <c r="I17" t="n">
-        <v>5.156</v>
+        <v>4.98</v>
       </c>
       <c r="J17" t="n">
-        <v>5.158</v>
+        <v>4.981</v>
       </c>
       <c r="K17" t="n">
-        <v>5.159</v>
+        <v>4.982</v>
       </c>
       <c r="L17" t="n">
-        <v>5.16</v>
+        <v>4.983</v>
       </c>
       <c r="M17" t="n">
-        <v>5.16</v>
+        <v>4.985</v>
       </c>
     </row>
     <row r="18">
@@ -2391,39 +2391,39 @@
         <v>9040208</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.996</v>
+        <v>4.878</v>
       </c>
       <c r="F18" t="n">
-        <v>5.012</v>
+        <v>4.887</v>
       </c>
       <c r="G18" t="n">
-        <v>5.015</v>
+        <v>4.887</v>
       </c>
       <c r="H18" t="n">
-        <v>5.012</v>
+        <v>4.87</v>
       </c>
       <c r="I18" t="n">
-        <v>4.996</v>
+        <v>4.87</v>
       </c>
       <c r="J18" t="n">
-        <v>5.008</v>
+        <v>4.876</v>
       </c>
       <c r="K18" t="n">
-        <v>5.009</v>
+        <v>4.881</v>
       </c>
       <c r="L18" t="n">
-        <v>5.013</v>
+        <v>4.887</v>
       </c>
       <c r="M18" t="n">
-        <v>5.015</v>
+        <v>4.887</v>
       </c>
     </row>
     <row r="19">
@@ -2436,39 +2436,39 @@
         <v>9040208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.89</v>
+        <v>4.802</v>
       </c>
       <c r="F19" t="n">
-        <v>4.9</v>
+        <v>4.832</v>
       </c>
       <c r="G19" t="n">
-        <v>4.939</v>
+        <v>4.835</v>
       </c>
       <c r="H19" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="I19" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="J19" t="n">
-        <v>4.89</v>
+        <v>4.799</v>
       </c>
       <c r="K19" t="n">
-        <v>4.905</v>
+        <v>4.815</v>
       </c>
       <c r="L19" t="n">
-        <v>4.91</v>
+        <v>4.833</v>
       </c>
       <c r="M19" t="n">
-        <v>4.939</v>
+        <v>4.835</v>
       </c>
     </row>
     <row r="20">
@@ -2481,39 +2481,39 @@
         <v>9040208</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.801</v>
+        <v>4.75</v>
       </c>
       <c r="F20" t="n">
-        <v>4.84</v>
+        <v>4.788</v>
       </c>
       <c r="G20" t="n">
-        <v>4.88</v>
+        <v>4.79</v>
       </c>
       <c r="H20" t="n">
-        <v>4.833</v>
+        <v>4.705</v>
       </c>
       <c r="I20" t="n">
-        <v>4.801</v>
+        <v>4.705</v>
       </c>
       <c r="J20" t="n">
-        <v>4.825</v>
+        <v>4.739</v>
       </c>
       <c r="K20" t="n">
-        <v>4.838</v>
+        <v>4.758</v>
       </c>
       <c r="L20" t="n">
-        <v>4.85</v>
+        <v>4.788</v>
       </c>
       <c r="M20" t="n">
-        <v>4.88</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
@@ -2526,39 +2526,39 @@
         <v>9040208</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.725</v>
+        <v>4.676</v>
       </c>
       <c r="F21" t="n">
-        <v>4.785</v>
+        <v>4.72</v>
       </c>
       <c r="G21" t="n">
-        <v>4.868</v>
+        <v>4.77</v>
       </c>
       <c r="H21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.684</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4.732</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.77</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.725</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.759</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.787</v>
-      </c>
-      <c r="L21" t="n">
-        <v>4.806</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.868</v>
       </c>
     </row>
     <row r="22">
@@ -2571,39 +2571,39 @@
         <v>9040208</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.622</v>
+        <v>4.565</v>
       </c>
       <c r="F22" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="G22" t="n">
-        <v>4.87</v>
+        <v>4.77</v>
       </c>
       <c r="H22" t="n">
-        <v>4.69</v>
+        <v>4.56</v>
       </c>
       <c r="I22" t="n">
-        <v>4.622</v>
+        <v>4.56</v>
       </c>
       <c r="J22" t="n">
-        <v>4.673</v>
+        <v>4.564</v>
       </c>
       <c r="K22" t="n">
-        <v>4.723</v>
+        <v>4.641</v>
       </c>
       <c r="L22" t="n">
-        <v>4.75</v>
+        <v>4.695</v>
       </c>
       <c r="M22" t="n">
-        <v>4.87</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="23">
@@ -2616,39 +2616,39 @@
         <v>9053555</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="F23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="G23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="H23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="I23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="J23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="K23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="L23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="M23" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
     </row>
     <row r="24">
@@ -2661,39 +2661,39 @@
         <v>9053555</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="F24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="G24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="H24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="I24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="J24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="K24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="L24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="M24" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="25">
@@ -2706,39 +2706,39 @@
         <v>9053555</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="F25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="G25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="H25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="I25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="J25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="K25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="L25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="M25" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
     </row>
     <row r="26">
@@ -2751,39 +2751,39 @@
         <v>9053555</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
       <c r="F26" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
       <c r="G26" t="n">
-        <v>12.198</v>
+        <v>12.137</v>
       </c>
       <c r="H26" t="n">
-        <v>12.198</v>
+        <v>12.137</v>
       </c>
       <c r="I26" t="n">
-        <v>12.198</v>
+        <v>12.137</v>
       </c>
       <c r="J26" t="n">
-        <v>12.198</v>
+        <v>12.137</v>
       </c>
       <c r="K26" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
       <c r="L26" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
       <c r="M26" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
     </row>
     <row r="27">
@@ -2796,39 +2796,39 @@
         <v>9053555</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12.148</v>
+        <v>12.09</v>
       </c>
       <c r="F27" t="n">
-        <v>12.148</v>
+        <v>12.089</v>
       </c>
       <c r="G27" t="n">
-        <v>12.145</v>
+        <v>12.09</v>
       </c>
       <c r="H27" t="n">
-        <v>12.144</v>
+        <v>12.089</v>
       </c>
       <c r="I27" t="n">
-        <v>12.144</v>
+        <v>12.089</v>
       </c>
       <c r="J27" t="n">
-        <v>12.145</v>
+        <v>12.089</v>
       </c>
       <c r="K27" t="n">
-        <v>12.146</v>
+        <v>12.089</v>
       </c>
       <c r="L27" t="n">
-        <v>12.148</v>
+        <v>12.09</v>
       </c>
       <c r="M27" t="n">
-        <v>12.148</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="28">
@@ -2841,39 +2841,39 @@
         <v>9053555</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12.104</v>
+        <v>11.949</v>
       </c>
       <c r="F28" t="n">
-        <v>12.106</v>
+        <v>11.951</v>
       </c>
       <c r="G28" t="n">
-        <v>12.092</v>
+        <v>11.954</v>
       </c>
       <c r="H28" t="n">
-        <v>12.091</v>
+        <v>11.904</v>
       </c>
       <c r="I28" t="n">
-        <v>12.091</v>
+        <v>11.904</v>
       </c>
       <c r="J28" t="n">
-        <v>12.092</v>
+        <v>11.938</v>
       </c>
       <c r="K28" t="n">
-        <v>12.098</v>
+        <v>11.939</v>
       </c>
       <c r="L28" t="n">
-        <v>12.105</v>
+        <v>11.951</v>
       </c>
       <c r="M28" t="n">
-        <v>12.106</v>
+        <v>11.954</v>
       </c>
     </row>
     <row r="29">
@@ -2886,39 +2886,39 @@
         <v>9053555</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12.024</v>
+        <v>11.83</v>
       </c>
       <c r="F29" t="n">
-        <v>12.027</v>
+        <v>11.83</v>
       </c>
       <c r="G29" t="n">
-        <v>11.992</v>
+        <v>11.83</v>
       </c>
       <c r="H29" t="n">
-        <v>11.911</v>
+        <v>11.828</v>
       </c>
       <c r="I29" t="n">
-        <v>11.911</v>
+        <v>11.828</v>
       </c>
       <c r="J29" t="n">
-        <v>11.972</v>
+        <v>11.829</v>
       </c>
       <c r="K29" t="n">
-        <v>11.989</v>
+        <v>11.83</v>
       </c>
       <c r="L29" t="n">
-        <v>12.025</v>
+        <v>11.83</v>
       </c>
       <c r="M29" t="n">
-        <v>12.027</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="30">
@@ -2931,39 +2931,39 @@
         <v>9038134</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112.152</v>
+        <v>112.08</v>
       </c>
       <c r="F30" t="n">
-        <v>112.167</v>
+        <v>112.08</v>
       </c>
       <c r="G30" t="n">
-        <v>112.174</v>
+        <v>112.08</v>
       </c>
       <c r="H30" t="n">
-        <v>112.152</v>
+        <v>112</v>
       </c>
       <c r="I30" t="n">
-        <v>112.152</v>
+        <v>112</v>
       </c>
       <c r="J30" t="n">
-        <v>112.152</v>
+        <v>112.06</v>
       </c>
       <c r="K30" t="n">
-        <v>112.161</v>
+        <v>112.06</v>
       </c>
       <c r="L30" t="n">
-        <v>112.168</v>
+        <v>112.08</v>
       </c>
       <c r="M30" t="n">
-        <v>112.174</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="31">
@@ -2976,39 +2976,39 @@
         <v>9038134</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112.08</v>
+        <v>111.9</v>
       </c>
       <c r="F31" t="n">
-        <v>112.121</v>
+        <v>111.9</v>
       </c>
       <c r="G31" t="n">
-        <v>112.132</v>
+        <v>111.93</v>
       </c>
       <c r="H31" t="n">
-        <v>112.08</v>
+        <v>111.69</v>
       </c>
       <c r="I31" t="n">
-        <v>112.08</v>
+        <v>111.69</v>
       </c>
       <c r="J31" t="n">
-        <v>112.08</v>
+        <v>111.848</v>
       </c>
       <c r="K31" t="n">
-        <v>112.103</v>
+        <v>111.855</v>
       </c>
       <c r="L31" t="n">
-        <v>112.124</v>
+        <v>111.908</v>
       </c>
       <c r="M31" t="n">
-        <v>112.132</v>
+        <v>111.93</v>
       </c>
     </row>
     <row r="32">
@@ -3021,39 +3021,39 @@
         <v>9038134</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>111.868</v>
+        <v>111.659</v>
       </c>
       <c r="F32" t="n">
-        <v>112.009</v>
+        <v>111.73</v>
       </c>
       <c r="G32" t="n">
-        <v>112.08</v>
+        <v>111.75</v>
       </c>
       <c r="H32" t="n">
-        <v>111.838</v>
+        <v>111.44</v>
       </c>
       <c r="I32" t="n">
-        <v>111.838</v>
+        <v>111.44</v>
       </c>
       <c r="J32" t="n">
-        <v>111.861</v>
+        <v>111.604</v>
       </c>
       <c r="K32" t="n">
-        <v>111.949</v>
+        <v>111.645</v>
       </c>
       <c r="L32" t="n">
-        <v>112.026</v>
+        <v>111.735</v>
       </c>
       <c r="M32" t="n">
-        <v>112.08</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="33">
@@ -3066,39 +3066,39 @@
         <v>9038134</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>111.66</v>
+        <v>111.44</v>
       </c>
       <c r="F33" t="n">
-        <v>111.906</v>
+        <v>111.59</v>
       </c>
       <c r="G33" t="n">
-        <v>111.796</v>
+        <v>111.56</v>
       </c>
       <c r="H33" t="n">
-        <v>111.56</v>
+        <v>111.192</v>
       </c>
       <c r="I33" t="n">
-        <v>111.56</v>
+        <v>111.192</v>
       </c>
       <c r="J33" t="n">
-        <v>111.635</v>
+        <v>111.378</v>
       </c>
       <c r="K33" t="n">
-        <v>111.731</v>
+        <v>111.446</v>
       </c>
       <c r="L33" t="n">
-        <v>111.824</v>
+        <v>111.568</v>
       </c>
       <c r="M33" t="n">
-        <v>111.906</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="34">
@@ -3111,39 +3111,39 @@
         <v>9038134</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>111.66</v>
+        <v>111.2</v>
       </c>
       <c r="F34" t="n">
-        <v>111.87</v>
+        <v>111.44</v>
       </c>
       <c r="G34" t="n">
-        <v>111.56</v>
+        <v>111.324</v>
       </c>
       <c r="H34" t="n">
-        <v>111.27</v>
+        <v>110.81</v>
       </c>
       <c r="I34" t="n">
-        <v>111.27</v>
+        <v>110.81</v>
       </c>
       <c r="J34" t="n">
-        <v>111.488</v>
+        <v>111.102</v>
       </c>
       <c r="K34" t="n">
-        <v>111.59</v>
+        <v>111.193</v>
       </c>
       <c r="L34" t="n">
-        <v>111.712</v>
+        <v>111.353</v>
       </c>
       <c r="M34" t="n">
-        <v>111.87</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="35">
@@ -3156,39 +3156,39 @@
         <v>9038134</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>111.647</v>
+        <v>110.8</v>
       </c>
       <c r="F35" t="n">
-        <v>111.76</v>
+        <v>111.266</v>
       </c>
       <c r="G35" t="n">
-        <v>111.28</v>
+        <v>111.18</v>
       </c>
       <c r="H35" t="n">
-        <v>110.89</v>
+        <v>110.4</v>
       </c>
       <c r="I35" t="n">
-        <v>110.89</v>
+        <v>110.4</v>
       </c>
       <c r="J35" t="n">
-        <v>111.182</v>
+        <v>110.7</v>
       </c>
       <c r="K35" t="n">
-        <v>111.394</v>
+        <v>110.911</v>
       </c>
       <c r="L35" t="n">
-        <v>111.675</v>
+        <v>111.201</v>
       </c>
       <c r="M35" t="n">
-        <v>111.76</v>
+        <v>111.266</v>
       </c>
     </row>
     <row r="36">
@@ -3201,39 +3201,39 @@
         <v>9038134</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>111.499</v>
+        <v>110.35</v>
       </c>
       <c r="F36" t="n">
-        <v>111.591</v>
+        <v>111</v>
       </c>
       <c r="G36" t="n">
-        <v>110.95</v>
+        <v>110.947</v>
       </c>
       <c r="H36" t="n">
-        <v>110.56</v>
+        <v>110.021</v>
       </c>
       <c r="I36" t="n">
-        <v>110.56</v>
+        <v>110.021</v>
       </c>
       <c r="J36" t="n">
-        <v>110.852</v>
+        <v>110.268</v>
       </c>
       <c r="K36" t="n">
-        <v>111.15</v>
+        <v>110.579</v>
       </c>
       <c r="L36" t="n">
-        <v>111.522</v>
+        <v>110.96</v>
       </c>
       <c r="M36" t="n">
-        <v>111.591</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
@@ -3246,39 +3246,39 @@
         <v>9044756</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="F37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="G37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="H37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="I37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="J37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="K37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="L37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="M37" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
     </row>
     <row r="38">
@@ -3291,39 +3291,39 @@
         <v>9044756</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3336,39 +3336,39 @@
         <v>9044756</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="G39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="H39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.987</v>
       </c>
       <c r="I39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.987</v>
       </c>
       <c r="J39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="M39" t="n">
-        <v>9.348000000000001</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="40">
@@ -3381,39 +3381,39 @@
         <v>9044756</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>9.042999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>9.044</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>9.045</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>9.042</v>
+        <v>8.699</v>
       </c>
       <c r="I40" t="n">
-        <v>9.042</v>
+        <v>8.699</v>
       </c>
       <c r="J40" t="n">
-        <v>9.042999999999999</v>
+        <v>8.699</v>
       </c>
       <c r="K40" t="n">
-        <v>9.042999999999999</v>
+        <v>8.699</v>
       </c>
       <c r="L40" t="n">
-        <v>9.044</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>9.045</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3426,39 +3426,39 @@
         <v>9044756</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="F41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="G41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="H41" t="n">
-        <v>8.724</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>8.724</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>8.724</v>
+        <v>8.477</v>
       </c>
       <c r="K41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="L41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="M41" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
     </row>
     <row r="42">
@@ -3471,39 +3471,39 @@
         <v>9044756</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3516,39 +3516,39 @@
         <v>9044756</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="F43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="G43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="H43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="I43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="J43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="K43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="L43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
       <c r="M43" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
     </row>
     <row r="44">
@@ -3561,39 +3561,39 @@
         <v>9042214</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3606,39 +3606,39 @@
         <v>9042214</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3651,39 +3651,39 @@
         <v>9042214</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="F46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="G46" t="n">
-        <v>8.862</v>
+        <v>8.827999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="I46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="J46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="K46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="L46" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="M46" t="n">
-        <v>8.862</v>
+        <v>8.827999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3696,39 +3696,39 @@
         <v>9042214</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3741,39 +3741,39 @@
         <v>9042214</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.759</v>
+        <v>8.49</v>
       </c>
       <c r="F48" t="n">
-        <v>8.759</v>
+        <v>8.496</v>
       </c>
       <c r="G48" t="n">
-        <v>8.759</v>
+        <v>8.493</v>
       </c>
       <c r="H48" t="n">
-        <v>8.757999999999999</v>
+        <v>8.487</v>
       </c>
       <c r="I48" t="n">
-        <v>8.757999999999999</v>
+        <v>8.487</v>
       </c>
       <c r="J48" t="n">
-        <v>8.759</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>8.759</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>8.759</v>
+        <v>8.494</v>
       </c>
       <c r="M48" t="n">
-        <v>8.759</v>
+        <v>8.496</v>
       </c>
     </row>
     <row r="49">
@@ -3786,39 +3786,39 @@
         <v>9042214</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8.510999999999999</v>
+        <v>8.395</v>
       </c>
       <c r="F49" t="n">
-        <v>8.515000000000001</v>
+        <v>8.396000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>8.512</v>
+        <v>8.395</v>
       </c>
       <c r="H49" t="n">
-        <v>8.510999999999999</v>
+        <v>8.395</v>
       </c>
       <c r="I49" t="n">
-        <v>8.510999999999999</v>
+        <v>8.395</v>
       </c>
       <c r="J49" t="n">
-        <v>8.510999999999999</v>
+        <v>8.395</v>
       </c>
       <c r="K49" t="n">
-        <v>8.512</v>
+        <v>8.395</v>
       </c>
       <c r="L49" t="n">
-        <v>8.513</v>
+        <v>8.395</v>
       </c>
       <c r="M49" t="n">
-        <v>8.515000000000001</v>
+        <v>8.396000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3831,39 +3831,39 @@
         <v>9042214</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="F50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.036</v>
       </c>
       <c r="G50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="H50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="I50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="J50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="K50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="L50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
       <c r="M50" t="n">
-        <v>8.414999999999999</v>
+        <v>8.036</v>
       </c>
     </row>
     <row r="51">
@@ -3876,39 +3876,39 @@
         <v>9043597</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="F51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="G51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="H51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="I51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="K51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="L51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="M51" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="52">
@@ -3921,39 +3921,39 @@
         <v>9043597</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="F52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="G52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="H52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="I52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="J52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="K52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="L52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="M52" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
     </row>
     <row r="53">
@@ -3966,39 +3966,39 @@
         <v>9043597</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="F53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="G53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="H53" t="n">
-        <v>5.709</v>
+        <v>5.543</v>
       </c>
       <c r="I53" t="n">
-        <v>5.709</v>
+        <v>5.543</v>
       </c>
       <c r="J53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="K53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="L53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="M53" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
     </row>
     <row r="54">
@@ -4011,39 +4011,39 @@
         <v>9043597</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="F54" t="n">
-        <v>5.552</v>
+        <v>5.379</v>
       </c>
       <c r="G54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="H54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="I54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="J54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="K54" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="L54" t="n">
-        <v>5.552</v>
+        <v>5.379</v>
       </c>
       <c r="M54" t="n">
-        <v>5.552</v>
+        <v>5.379</v>
       </c>
     </row>
     <row r="55">
@@ -4056,39 +4056,39 @@
         <v>9043597</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.391</v>
+        <v>5.286</v>
       </c>
       <c r="F55" t="n">
-        <v>5.391</v>
+        <v>5.287</v>
       </c>
       <c r="G55" t="n">
-        <v>5.39</v>
+        <v>5.286</v>
       </c>
       <c r="H55" t="n">
-        <v>5.389</v>
+        <v>5.285</v>
       </c>
       <c r="I55" t="n">
-        <v>5.389</v>
+        <v>5.285</v>
       </c>
       <c r="J55" t="n">
-        <v>5.39</v>
+        <v>5.286</v>
       </c>
       <c r="K55" t="n">
-        <v>5.39</v>
+        <v>5.286</v>
       </c>
       <c r="L55" t="n">
-        <v>5.391</v>
+        <v>5.286</v>
       </c>
       <c r="M55" t="n">
-        <v>5.391</v>
+        <v>5.287</v>
       </c>
     </row>
     <row r="56">
@@ -4101,39 +4101,39 @@
         <v>9043597</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.294</v>
+        <v>5.28</v>
       </c>
       <c r="F56" t="n">
-        <v>5.296</v>
+        <v>5.281</v>
       </c>
       <c r="G56" t="n">
-        <v>5.294</v>
+        <v>5.28</v>
       </c>
       <c r="H56" t="n">
-        <v>5.292</v>
+        <v>5.28</v>
       </c>
       <c r="I56" t="n">
-        <v>5.292</v>
+        <v>5.28</v>
       </c>
       <c r="J56" t="n">
-        <v>5.294</v>
+        <v>5.28</v>
       </c>
       <c r="K56" t="n">
-        <v>5.294</v>
+        <v>5.28</v>
       </c>
       <c r="L56" t="n">
-        <v>5.295</v>
+        <v>5.28</v>
       </c>
       <c r="M56" t="n">
-        <v>5.296</v>
+        <v>5.281</v>
       </c>
     </row>
     <row r="57">
@@ -4146,39 +4146,39 @@
         <v>9043597</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.282</v>
+        <v>5.298</v>
       </c>
       <c r="F57" t="n">
-        <v>5.282</v>
+        <v>5.313</v>
       </c>
       <c r="G57" t="n">
-        <v>5.285</v>
+        <v>5.299</v>
       </c>
       <c r="H57" t="n">
-        <v>5.281</v>
+        <v>5.296</v>
       </c>
       <c r="I57" t="n">
-        <v>5.281</v>
+        <v>5.296</v>
       </c>
       <c r="J57" t="n">
-        <v>5.282</v>
+        <v>5.298</v>
       </c>
       <c r="K57" t="n">
-        <v>5.283</v>
+        <v>5.302</v>
       </c>
       <c r="L57" t="n">
-        <v>5.283</v>
+        <v>5.302</v>
       </c>
       <c r="M57" t="n">
-        <v>5.285</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="58">
@@ -4191,39 +4191,39 @@
         <v>9040454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="F58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="G58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="H58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="I58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="J58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="K58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="L58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="M58" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
     </row>
     <row r="59">
@@ -4236,39 +4236,39 @@
         <v>9040454</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="F59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="G59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="H59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="I59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="J59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="K59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="L59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="M59" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
     </row>
     <row r="60">
@@ -4281,39 +4281,39 @@
         <v>9040454</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="F60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="G60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="H60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="I60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="J60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="K60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="L60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="M60" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="61">
@@ -4326,39 +4326,39 @@
         <v>9040454</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="F61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="G61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="H61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="I61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="J61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="K61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="L61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="M61" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="62">
@@ -4371,39 +4371,39 @@
         <v>9040454</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="F62" t="n">
-        <v>6.322</v>
+        <v>6.362</v>
       </c>
       <c r="G62" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="H62" t="n">
-        <v>6.321</v>
+        <v>6.361</v>
       </c>
       <c r="I62" t="n">
-        <v>6.321</v>
+        <v>6.361</v>
       </c>
       <c r="J62" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="K62" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="L62" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="M62" t="n">
-        <v>6.322</v>
+        <v>6.362</v>
       </c>
     </row>
     <row r="63">
@@ -4416,39 +4416,39 @@
         <v>9040454</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="F63" t="n">
-        <v>6.353</v>
+        <v>6.321</v>
       </c>
       <c r="G63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="H63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="I63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="J63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="K63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="L63" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="M63" t="n">
-        <v>6.353</v>
+        <v>6.321</v>
       </c>
     </row>
     <row r="64">
@@ -4461,39 +4461,39 @@
         <v>9040454</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.311</v>
+        <v>6.232</v>
       </c>
       <c r="F64" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
       <c r="G64" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
       <c r="H64" t="n">
-        <v>6.311</v>
+        <v>6.232</v>
       </c>
       <c r="I64" t="n">
-        <v>6.311</v>
+        <v>6.232</v>
       </c>
       <c r="J64" t="n">
-        <v>6.311</v>
+        <v>6.232</v>
       </c>
       <c r="K64" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
       <c r="L64" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
       <c r="M64" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
     </row>
     <row r="65">
@@ -4506,39 +4506,39 @@
         <v>9037610</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.756</v>
+        <v>4.672</v>
       </c>
       <c r="F65" t="n">
-        <v>4.756</v>
+        <v>4.672</v>
       </c>
       <c r="G65" t="n">
-        <v>4.756</v>
+        <v>4.67</v>
       </c>
       <c r="H65" t="n">
-        <v>4.756</v>
+        <v>4.66</v>
       </c>
       <c r="I65" t="n">
-        <v>4.756</v>
+        <v>4.66</v>
       </c>
       <c r="J65" t="n">
-        <v>4.756</v>
+        <v>4.667</v>
       </c>
       <c r="K65" t="n">
-        <v>4.756</v>
+        <v>4.668</v>
       </c>
       <c r="L65" t="n">
-        <v>4.756</v>
+        <v>4.672</v>
       </c>
       <c r="M65" t="n">
-        <v>4.756</v>
+        <v>4.672</v>
       </c>
     </row>
     <row r="66">
@@ -4551,39 +4551,39 @@
         <v>9037610</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.731</v>
+        <v>4.818</v>
       </c>
       <c r="F66" t="n">
-        <v>4.74</v>
+        <v>4.823</v>
       </c>
       <c r="G66" t="n">
-        <v>4.757</v>
+        <v>4.816</v>
       </c>
       <c r="H66" t="n">
-        <v>4.712</v>
+        <v>4.802</v>
       </c>
       <c r="I66" t="n">
-        <v>4.712</v>
+        <v>4.802</v>
       </c>
       <c r="J66" t="n">
-        <v>4.726</v>
+        <v>4.812</v>
       </c>
       <c r="K66" t="n">
-        <v>4.735</v>
+        <v>4.815</v>
       </c>
       <c r="L66" t="n">
-        <v>4.744</v>
+        <v>4.819</v>
       </c>
       <c r="M66" t="n">
-        <v>4.757</v>
+        <v>4.823</v>
       </c>
     </row>
     <row r="67">
@@ -4596,39 +4596,39 @@
         <v>9037610</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.907</v>
+        <v>4.93</v>
       </c>
       <c r="F67" t="n">
-        <v>4.938</v>
+        <v>4.943</v>
       </c>
       <c r="G67" t="n">
-        <v>4.978</v>
+        <v>4.939</v>
       </c>
       <c r="H67" t="n">
-        <v>4.853</v>
+        <v>4.857</v>
       </c>
       <c r="I67" t="n">
-        <v>4.853</v>
+        <v>4.857</v>
       </c>
       <c r="J67" t="n">
-        <v>4.893</v>
+        <v>4.912</v>
       </c>
       <c r="K67" t="n">
-        <v>4.919</v>
+        <v>4.917</v>
       </c>
       <c r="L67" t="n">
-        <v>4.948</v>
+        <v>4.94</v>
       </c>
       <c r="M67" t="n">
-        <v>4.978</v>
+        <v>4.943</v>
       </c>
     </row>
     <row r="68">
@@ -4641,39 +4641,39 @@
         <v>9037610</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.028</v>
+        <v>4.907</v>
       </c>
       <c r="F68" t="n">
-        <v>5.121</v>
+        <v>4.969</v>
       </c>
       <c r="G68" t="n">
-        <v>5.329</v>
+        <v>4.955</v>
       </c>
       <c r="H68" t="n">
-        <v>4.934</v>
+        <v>4.761</v>
       </c>
       <c r="I68" t="n">
-        <v>4.934</v>
+        <v>4.761</v>
       </c>
       <c r="J68" t="n">
-        <v>5.005</v>
+        <v>4.871</v>
       </c>
       <c r="K68" t="n">
-        <v>5.103</v>
+        <v>4.898</v>
       </c>
       <c r="L68" t="n">
-        <v>5.173</v>
+        <v>4.959</v>
       </c>
       <c r="M68" t="n">
-        <v>5.329</v>
+        <v>4.969</v>
       </c>
     </row>
     <row r="69">
@@ -4686,39 +4686,39 @@
         <v>9037610</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.032</v>
+        <v>4.757</v>
       </c>
       <c r="F69" t="n">
-        <v>5.348</v>
+        <v>4.943</v>
       </c>
       <c r="G69" t="n">
-        <v>5.452</v>
+        <v>4.882</v>
       </c>
       <c r="H69" t="n">
-        <v>4.813</v>
+        <v>4.535</v>
       </c>
       <c r="I69" t="n">
-        <v>4.813</v>
+        <v>4.535</v>
       </c>
       <c r="J69" t="n">
-        <v>4.978</v>
+        <v>4.702</v>
       </c>
       <c r="K69" t="n">
-        <v>5.162</v>
+        <v>4.779</v>
       </c>
       <c r="L69" t="n">
-        <v>5.374</v>
+        <v>4.897</v>
       </c>
       <c r="M69" t="n">
-        <v>5.452</v>
+        <v>4.943</v>
       </c>
     </row>
     <row r="70">
@@ -4731,39 +4731,39 @@
         <v>9037610</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.945</v>
+        <v>4.475</v>
       </c>
       <c r="F70" t="n">
-        <v>5.187</v>
+        <v>4.861</v>
       </c>
       <c r="G70" t="n">
-        <v>5.127</v>
+        <v>4.629</v>
       </c>
       <c r="H70" t="n">
-        <v>4.37</v>
+        <v>4.258</v>
       </c>
       <c r="I70" t="n">
-        <v>4.37</v>
+        <v>4.258</v>
       </c>
       <c r="J70" t="n">
-        <v>4.801</v>
+        <v>4.421</v>
       </c>
       <c r="K70" t="n">
-        <v>4.907</v>
+        <v>4.556</v>
       </c>
       <c r="L70" t="n">
-        <v>5.142</v>
+        <v>4.687</v>
       </c>
       <c r="M70" t="n">
-        <v>5.187</v>
+        <v>4.861</v>
       </c>
     </row>
     <row r="71">
@@ -4776,39 +4776,39 @@
         <v>9037610</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.73</v>
+        <v>4.243</v>
       </c>
       <c r="F71" t="n">
-        <v>5.012</v>
+        <v>4.785</v>
       </c>
       <c r="G71" t="n">
-        <v>4.902</v>
+        <v>4.378</v>
       </c>
       <c r="H71" t="n">
-        <v>3.952</v>
+        <v>3.846</v>
       </c>
       <c r="I71" t="n">
-        <v>3.952</v>
+        <v>3.846</v>
       </c>
       <c r="J71" t="n">
-        <v>4.536</v>
+        <v>4.144</v>
       </c>
       <c r="K71" t="n">
-        <v>4.649</v>
+        <v>4.313</v>
       </c>
       <c r="L71" t="n">
-        <v>4.93</v>
+        <v>4.48</v>
       </c>
       <c r="M71" t="n">
-        <v>5.012</v>
+        <v>4.785</v>
       </c>
     </row>
     <row r="72">
@@ -4821,39 +4821,39 @@
         <v>9043425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="F72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="G72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="H72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="I72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="J72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="K72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="L72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="M72" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="73">
@@ -4866,39 +4866,39 @@
         <v>9043425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="F73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="G73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="H73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="I73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="J73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="K73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="L73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="M73" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="74">
@@ -4911,39 +4911,39 @@
         <v>9043425</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="F74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="G74" t="n">
-        <v>6.72</v>
+        <v>6.691</v>
       </c>
       <c r="H74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="I74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="J74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="K74" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="L74" t="n">
-        <v>6.72</v>
+        <v>6.691</v>
       </c>
       <c r="M74" t="n">
-        <v>6.72</v>
+        <v>6.691</v>
       </c>
     </row>
     <row r="75">
@@ -4956,39 +4956,39 @@
         <v>9043425</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="F75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="G75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="H75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="I75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="J75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="K75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="L75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="M75" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="76">
@@ -5001,39 +5001,39 @@
         <v>9043425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.638</v>
+        <v>6.61</v>
       </c>
       <c r="F76" t="n">
-        <v>6.638</v>
+        <v>6.61</v>
       </c>
       <c r="G76" t="n">
-        <v>6.637</v>
+        <v>6.609</v>
       </c>
       <c r="H76" t="n">
-        <v>6.637</v>
+        <v>6.609</v>
       </c>
       <c r="I76" t="n">
-        <v>6.637</v>
+        <v>6.609</v>
       </c>
       <c r="J76" t="n">
-        <v>6.637</v>
+        <v>6.609</v>
       </c>
       <c r="K76" t="n">
-        <v>6.637</v>
+        <v>6.61</v>
       </c>
       <c r="L76" t="n">
-        <v>6.638</v>
+        <v>6.61</v>
       </c>
       <c r="M76" t="n">
-        <v>6.638</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="77">
@@ -5046,39 +5046,39 @@
         <v>9043425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.603</v>
+        <v>6.55</v>
       </c>
       <c r="F77" t="n">
-        <v>6.604</v>
+        <v>6.55</v>
       </c>
       <c r="G77" t="n">
-        <v>6.602</v>
+        <v>6.549</v>
       </c>
       <c r="H77" t="n">
-        <v>6.601</v>
+        <v>6.55</v>
       </c>
       <c r="I77" t="n">
-        <v>6.601</v>
+        <v>6.549</v>
       </c>
       <c r="J77" t="n">
-        <v>6.602</v>
+        <v>6.55</v>
       </c>
       <c r="K77" t="n">
-        <v>6.603</v>
+        <v>6.55</v>
       </c>
       <c r="L77" t="n">
-        <v>6.603</v>
+        <v>6.55</v>
       </c>
       <c r="M77" t="n">
-        <v>6.604</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="78">
@@ -5091,39 +5091,39 @@
         <v>9043425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6.548</v>
+        <v>6.51</v>
       </c>
       <c r="F78" t="n">
-        <v>6.55</v>
+        <v>6.514</v>
       </c>
       <c r="G78" t="n">
-        <v>6.547</v>
+        <v>6.5</v>
       </c>
       <c r="H78" t="n">
-        <v>6.547</v>
+        <v>6.513</v>
       </c>
       <c r="I78" t="n">
-        <v>6.547</v>
+        <v>6.5</v>
       </c>
       <c r="J78" t="n">
-        <v>6.547</v>
+        <v>6.508</v>
       </c>
       <c r="K78" t="n">
-        <v>6.548</v>
+        <v>6.509</v>
       </c>
       <c r="L78" t="n">
-        <v>6.548</v>
+        <v>6.513</v>
       </c>
       <c r="M78" t="n">
-        <v>6.55</v>
+        <v>6.514</v>
       </c>
     </row>
     <row r="79">
@@ -5136,39 +5136,39 @@
         <v>9042153</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="F79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="G79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="H79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="I79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="J79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="K79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="L79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="M79" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
     </row>
     <row r="80">
@@ -5181,39 +5181,39 @@
         <v>9042153</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="F80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="G80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="H80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="I80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="J80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="K80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="L80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="M80" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
     </row>
     <row r="81">
@@ -5226,39 +5226,39 @@
         <v>9042153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="F81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="G81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="H81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="I81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="J81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="K81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="L81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="M81" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
     </row>
     <row r="82">
@@ -5271,39 +5271,39 @@
         <v>9042153</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10.869</v>
+        <v>10.715</v>
       </c>
       <c r="F82" t="n">
-        <v>10.869</v>
+        <v>10.716</v>
       </c>
       <c r="G82" t="n">
-        <v>10.869</v>
+        <v>10.716</v>
       </c>
       <c r="H82" t="n">
-        <v>10.869</v>
+        <v>10.703</v>
       </c>
       <c r="I82" t="n">
-        <v>10.869</v>
+        <v>10.703</v>
       </c>
       <c r="J82" t="n">
-        <v>10.869</v>
+        <v>10.712</v>
       </c>
       <c r="K82" t="n">
-        <v>10.869</v>
+        <v>10.712</v>
       </c>
       <c r="L82" t="n">
-        <v>10.869</v>
+        <v>10.716</v>
       </c>
       <c r="M82" t="n">
-        <v>10.869</v>
+        <v>10.716</v>
       </c>
     </row>
     <row r="83">
@@ -5316,39 +5316,39 @@
         <v>9042153</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10.725</v>
+        <v>10.546</v>
       </c>
       <c r="F83" t="n">
-        <v>10.734</v>
+        <v>10.58</v>
       </c>
       <c r="G83" t="n">
-        <v>10.735</v>
+        <v>10.576</v>
       </c>
       <c r="H83" t="n">
-        <v>10.73</v>
+        <v>10.525</v>
       </c>
       <c r="I83" t="n">
-        <v>10.725</v>
+        <v>10.525</v>
       </c>
       <c r="J83" t="n">
-        <v>10.729</v>
+        <v>10.541</v>
       </c>
       <c r="K83" t="n">
-        <v>10.731</v>
+        <v>10.557</v>
       </c>
       <c r="L83" t="n">
-        <v>10.734</v>
+        <v>10.577</v>
       </c>
       <c r="M83" t="n">
-        <v>10.735</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="84">
@@ -5361,39 +5361,39 @@
         <v>9042153</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>10.583</v>
+        <v>10.445</v>
       </c>
       <c r="F84" t="n">
-        <v>10.589</v>
+        <v>10.453</v>
       </c>
       <c r="G84" t="n">
-        <v>10.6</v>
+        <v>10.453</v>
       </c>
       <c r="H84" t="n">
-        <v>10.588</v>
+        <v>10.4</v>
       </c>
       <c r="I84" t="n">
-        <v>10.583</v>
+        <v>10.4</v>
       </c>
       <c r="J84" t="n">
-        <v>10.586</v>
+        <v>10.433</v>
       </c>
       <c r="K84" t="n">
-        <v>10.59</v>
+        <v>10.438</v>
       </c>
       <c r="L84" t="n">
-        <v>10.592</v>
+        <v>10.453</v>
       </c>
       <c r="M84" t="n">
-        <v>10.6</v>
+        <v>10.453</v>
       </c>
     </row>
     <row r="85">
@@ -5406,39 +5406,39 @@
         <v>9042153</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10.448</v>
+        <v>10.353</v>
       </c>
       <c r="F85" t="n">
-        <v>10.457</v>
+        <v>10.383</v>
       </c>
       <c r="G85" t="n">
-        <v>10.487</v>
+        <v>10.383</v>
       </c>
       <c r="H85" t="n">
-        <v>10.456</v>
+        <v>10.271</v>
       </c>
       <c r="I85" t="n">
-        <v>10.448</v>
+        <v>10.271</v>
       </c>
       <c r="J85" t="n">
-        <v>10.454</v>
+        <v>10.333</v>
       </c>
       <c r="K85" t="n">
-        <v>10.462</v>
+        <v>10.348</v>
       </c>
       <c r="L85" t="n">
-        <v>10.464</v>
+        <v>10.383</v>
       </c>
       <c r="M85" t="n">
-        <v>10.487</v>
+        <v>10.383</v>
       </c>
     </row>
     <row r="86">
@@ -5451,39 +5451,39 @@
         <v>9040439</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="F86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="G86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="H86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="I86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="J86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="K86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="L86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="M86" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
     </row>
     <row r="87">
@@ -5496,39 +5496,39 @@
         <v>9040439</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="F87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="G87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="H87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="I87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="J87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="K87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="L87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="M87" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
     </row>
     <row r="88">
@@ -5541,39 +5541,39 @@
         <v>9040439</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="F88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="G88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="H88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="I88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="J88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="K88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="L88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="M88" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="89">
@@ -5586,39 +5586,39 @@
         <v>9040439</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="F89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="G89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="H89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="I89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="J89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="K89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="L89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
       <c r="M89" t="n">
-        <v>7.15</v>
+        <v>7.205</v>
       </c>
     </row>
     <row r="90">
@@ -5631,39 +5631,39 @@
         <v>9040439</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="F90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="G90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="H90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="I90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="J90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="K90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="L90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
       <c r="M90" t="n">
-        <v>7.205</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="91">
@@ -5676,39 +5676,39 @@
         <v>9040439</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="F91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="G91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="H91" t="n">
-        <v>7.15</v>
+        <v>7.056</v>
       </c>
       <c r="I91" t="n">
-        <v>7.15</v>
+        <v>7.056</v>
       </c>
       <c r="J91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="K91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="L91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="M91" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
     </row>
     <row r="92">
@@ -5721,39 +5721,39 @@
         <v>9040439</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="F92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="G92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="H92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="I92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="J92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="K92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="L92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
       <c r="M92" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="93">
@@ -5766,39 +5766,39 @@
         <v>9032282</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="F93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="G93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="H93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="I93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="J93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="K93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="L93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="M93" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="94">
@@ -5811,39 +5811,39 @@
         <v>9032282</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7.087</v>
+        <v>7.138</v>
       </c>
       <c r="F94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="G94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="H94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="I94" t="n">
-        <v>7.087</v>
+        <v>7.138</v>
       </c>
       <c r="J94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="K94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="L94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="M94" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
     </row>
     <row r="95">
@@ -5856,39 +5856,39 @@
         <v>9032282</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.136</v>
+        <v>7.156</v>
       </c>
       <c r="F95" t="n">
-        <v>7.136</v>
+        <v>7.157</v>
       </c>
       <c r="G95" t="n">
-        <v>7.137</v>
+        <v>7.155</v>
       </c>
       <c r="H95" t="n">
-        <v>7.136</v>
+        <v>7.155</v>
       </c>
       <c r="I95" t="n">
-        <v>7.136</v>
+        <v>7.155</v>
       </c>
       <c r="J95" t="n">
-        <v>7.136</v>
+        <v>7.155</v>
       </c>
       <c r="K95" t="n">
-        <v>7.136</v>
+        <v>7.156</v>
       </c>
       <c r="L95" t="n">
-        <v>7.136</v>
+        <v>7.156</v>
       </c>
       <c r="M95" t="n">
-        <v>7.137</v>
+        <v>7.157</v>
       </c>
     </row>
     <row r="96">
@@ -5901,39 +5901,39 @@
         <v>9032282</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7.156</v>
+        <v>7.113</v>
       </c>
       <c r="F96" t="n">
-        <v>7.161</v>
+        <v>7.114</v>
       </c>
       <c r="G96" t="n">
-        <v>7.17</v>
+        <v>7.113</v>
       </c>
       <c r="H96" t="n">
-        <v>7.16</v>
+        <v>7.112</v>
       </c>
       <c r="I96" t="n">
-        <v>7.156</v>
+        <v>7.112</v>
       </c>
       <c r="J96" t="n">
-        <v>7.159</v>
+        <v>7.112</v>
       </c>
       <c r="K96" t="n">
-        <v>7.162</v>
+        <v>7.113</v>
       </c>
       <c r="L96" t="n">
-        <v>7.163</v>
+        <v>7.113</v>
       </c>
       <c r="M96" t="n">
-        <v>7.17</v>
+        <v>7.114</v>
       </c>
     </row>
     <row r="97">
@@ -5946,39 +5946,39 @@
         <v>9032282</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>7.11</v>
+        <v>7.04</v>
       </c>
       <c r="F97" t="n">
-        <v>7.111</v>
+        <v>7.04</v>
       </c>
       <c r="G97" t="n">
-        <v>7.113</v>
+        <v>7.04</v>
       </c>
       <c r="H97" t="n">
-        <v>7.11</v>
+        <v>7.04</v>
       </c>
       <c r="I97" t="n">
-        <v>7.11</v>
+        <v>7.04</v>
       </c>
       <c r="J97" t="n">
-        <v>7.11</v>
+        <v>7.04</v>
       </c>
       <c r="K97" t="n">
-        <v>7.111</v>
+        <v>7.04</v>
       </c>
       <c r="L97" t="n">
-        <v>7.112</v>
+        <v>7.04</v>
       </c>
       <c r="M97" t="n">
-        <v>7.113</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="98">
@@ -5991,39 +5991,39 @@
         <v>9032282</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="F98" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="G98" t="n">
-        <v>7.041</v>
+        <v>6.968</v>
       </c>
       <c r="H98" t="n">
-        <v>7.04</v>
+        <v>6.967</v>
       </c>
       <c r="I98" t="n">
-        <v>7.04</v>
+        <v>6.967</v>
       </c>
       <c r="J98" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="K98" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="L98" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="M98" t="n">
-        <v>7.041</v>
+        <v>6.968</v>
       </c>
     </row>
     <row r="99">
@@ -6036,39 +6036,39 @@
         <v>9032282</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6.969</v>
+        <v>6.899</v>
       </c>
       <c r="F99" t="n">
-        <v>6.969</v>
+        <v>6.9</v>
       </c>
       <c r="G99" t="n">
-        <v>6.969</v>
+        <v>6.898</v>
       </c>
       <c r="H99" t="n">
-        <v>6.968</v>
+        <v>6.898</v>
       </c>
       <c r="I99" t="n">
-        <v>6.968</v>
+        <v>6.898</v>
       </c>
       <c r="J99" t="n">
-        <v>6.969</v>
+        <v>6.898</v>
       </c>
       <c r="K99" t="n">
-        <v>6.969</v>
+        <v>6.899</v>
       </c>
       <c r="L99" t="n">
-        <v>6.969</v>
+        <v>6.899</v>
       </c>
       <c r="M99" t="n">
-        <v>6.969</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="100">
@@ -6081,39 +6081,39 @@
         <v>9037738</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5.585</v>
+        <v>5.726</v>
       </c>
       <c r="F100" t="n">
-        <v>5.599</v>
+        <v>5.728</v>
       </c>
       <c r="G100" t="n">
-        <v>5.637</v>
+        <v>5.726</v>
       </c>
       <c r="H100" t="n">
-        <v>5.542</v>
+        <v>5.687</v>
       </c>
       <c r="I100" t="n">
-        <v>5.542</v>
+        <v>5.687</v>
       </c>
       <c r="J100" t="n">
-        <v>5.574</v>
+        <v>5.716</v>
       </c>
       <c r="K100" t="n">
-        <v>5.591</v>
+        <v>5.717</v>
       </c>
       <c r="L100" t="n">
-        <v>5.609</v>
+        <v>5.726</v>
       </c>
       <c r="M100" t="n">
-        <v>5.637</v>
+        <v>5.728</v>
       </c>
     </row>
     <row r="101">
@@ -6126,39 +6126,39 @@
         <v>9037738</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5.877</v>
+        <v>5.935</v>
       </c>
       <c r="F101" t="n">
-        <v>5.92</v>
+        <v>5.973</v>
       </c>
       <c r="G101" t="n">
-        <v>5.99</v>
+        <v>5.974</v>
       </c>
       <c r="H101" t="n">
-        <v>5.736</v>
+        <v>5.803</v>
       </c>
       <c r="I101" t="n">
-        <v>5.736</v>
+        <v>5.803</v>
       </c>
       <c r="J101" t="n">
-        <v>5.841</v>
+        <v>5.902</v>
       </c>
       <c r="K101" t="n">
-        <v>5.881</v>
+        <v>5.921</v>
       </c>
       <c r="L101" t="n">
-        <v>5.938</v>
+        <v>5.974</v>
       </c>
       <c r="M101" t="n">
-        <v>5.99</v>
+        <v>5.974</v>
       </c>
     </row>
     <row r="102">
@@ -6171,39 +6171,39 @@
         <v>9037738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6.049</v>
+        <v>5.962</v>
       </c>
       <c r="F102" t="n">
-        <v>6.189</v>
+        <v>6.037</v>
       </c>
       <c r="G102" t="n">
-        <v>6.222</v>
+        <v>6.036</v>
       </c>
       <c r="H102" t="n">
-        <v>5.886</v>
+        <v>5.776</v>
       </c>
       <c r="I102" t="n">
-        <v>5.886</v>
+        <v>5.776</v>
       </c>
       <c r="J102" t="n">
-        <v>6.008</v>
+        <v>5.915</v>
       </c>
       <c r="K102" t="n">
-        <v>6.086</v>
+        <v>5.953</v>
       </c>
       <c r="L102" t="n">
-        <v>6.197</v>
+        <v>6.036</v>
       </c>
       <c r="M102" t="n">
-        <v>6.222</v>
+        <v>6.037</v>
       </c>
     </row>
     <row r="103">
@@ -6216,39 +6216,39 @@
         <v>9037738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6.098</v>
+        <v>5.788</v>
       </c>
       <c r="F103" t="n">
-        <v>6.254</v>
+        <v>6.026</v>
       </c>
       <c r="G103" t="n">
-        <v>6.248</v>
+        <v>5.946</v>
       </c>
       <c r="H103" t="n">
-        <v>5.683</v>
+        <v>5.519</v>
       </c>
       <c r="I103" t="n">
-        <v>5.683</v>
+        <v>5.519</v>
       </c>
       <c r="J103" t="n">
-        <v>5.994</v>
+        <v>5.721</v>
       </c>
       <c r="K103" t="n">
-        <v>6.071</v>
+        <v>5.82</v>
       </c>
       <c r="L103" t="n">
-        <v>6.25</v>
+        <v>5.966</v>
       </c>
       <c r="M103" t="n">
-        <v>6.254</v>
+        <v>6.026</v>
       </c>
     </row>
     <row r="104">
@@ -6261,39 +6261,39 @@
         <v>9037738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6.01</v>
+        <v>5.555</v>
       </c>
       <c r="F104" t="n">
-        <v>6.23</v>
+        <v>5.936</v>
       </c>
       <c r="G104" t="n">
-        <v>6.118</v>
+        <v>5.728</v>
       </c>
       <c r="H104" t="n">
-        <v>5.153</v>
+        <v>5.113</v>
       </c>
       <c r="I104" t="n">
-        <v>5.153</v>
+        <v>5.113</v>
       </c>
       <c r="J104" t="n">
-        <v>5.795</v>
+        <v>5.444</v>
       </c>
       <c r="K104" t="n">
-        <v>5.877</v>
+        <v>5.583</v>
       </c>
       <c r="L104" t="n">
-        <v>6.146</v>
+        <v>5.78</v>
       </c>
       <c r="M104" t="n">
-        <v>6.23</v>
+        <v>5.936</v>
       </c>
     </row>
     <row r="105">
@@ -6306,39 +6306,39 @@
         <v>9037738</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5.722</v>
+        <v>5.357</v>
       </c>
       <c r="F105" t="n">
-        <v>6.069</v>
+        <v>5.859</v>
       </c>
       <c r="G105" t="n">
-        <v>5.811</v>
+        <v>5.454</v>
       </c>
       <c r="H105" t="n">
-        <v>4.866</v>
+        <v>4.807</v>
       </c>
       <c r="I105" t="n">
-        <v>4.866</v>
+        <v>4.807</v>
       </c>
       <c r="J105" t="n">
-        <v>5.508</v>
+        <v>5.22</v>
       </c>
       <c r="K105" t="n">
-        <v>5.617</v>
+        <v>5.369</v>
       </c>
       <c r="L105" t="n">
-        <v>5.875</v>
+        <v>5.556</v>
       </c>
       <c r="M105" t="n">
-        <v>6.069</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="106">
@@ -6351,39 +6351,39 @@
         <v>9037738</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.32</v>
+        <v>5.171</v>
       </c>
       <c r="F106" t="n">
-        <v>5.87</v>
+        <v>5.795</v>
       </c>
       <c r="G106" t="n">
-        <v>5.458</v>
+        <v>5.265</v>
       </c>
       <c r="H106" t="n">
-        <v>5.458</v>
+        <v>4.642</v>
       </c>
       <c r="I106" t="n">
-        <v>5.32</v>
+        <v>4.642</v>
       </c>
       <c r="J106" t="n">
-        <v>5.423</v>
+        <v>5.039</v>
       </c>
       <c r="K106" t="n">
-        <v>5.526</v>
+        <v>5.218</v>
       </c>
       <c r="L106" t="n">
-        <v>5.561</v>
+        <v>5.397</v>
       </c>
       <c r="M106" t="n">
-        <v>5.87</v>
+        <v>5.795</v>
       </c>
     </row>
     <row r="107">
@@ -6396,39 +6396,39 @@
         <v>9039635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="F107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="G107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="H107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="I107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="J107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="K107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="L107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="M107" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
     </row>
     <row r="108">
@@ -6441,39 +6441,39 @@
         <v>9039635</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5.441</v>
+        <v>5.355</v>
       </c>
       <c r="F108" t="n">
-        <v>5.441</v>
+        <v>5.355</v>
       </c>
       <c r="G108" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="H108" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="I108" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="J108" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="K108" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="L108" t="n">
-        <v>5.441</v>
+        <v>5.355</v>
       </c>
       <c r="M108" t="n">
-        <v>5.441</v>
+        <v>5.355</v>
       </c>
     </row>
     <row r="109">
@@ -6486,39 +6486,39 @@
         <v>9039635</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5.349</v>
+        <v>5.196</v>
       </c>
       <c r="F109" t="n">
-        <v>5.352</v>
+        <v>5.197</v>
       </c>
       <c r="G109" t="n">
-        <v>5.349</v>
+        <v>5.194</v>
       </c>
       <c r="H109" t="n">
-        <v>5.349</v>
+        <v>5.193</v>
       </c>
       <c r="I109" t="n">
-        <v>5.349</v>
+        <v>5.193</v>
       </c>
       <c r="J109" t="n">
-        <v>5.349</v>
+        <v>5.194</v>
       </c>
       <c r="K109" t="n">
-        <v>5.35</v>
+        <v>5.195</v>
       </c>
       <c r="L109" t="n">
-        <v>5.35</v>
+        <v>5.196</v>
       </c>
       <c r="M109" t="n">
-        <v>5.352</v>
+        <v>5.197</v>
       </c>
     </row>
     <row r="110">
@@ -6531,39 +6531,39 @@
         <v>9039635</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5.19</v>
+        <v>5.081</v>
       </c>
       <c r="F110" t="n">
-        <v>5.217</v>
+        <v>5.081</v>
       </c>
       <c r="G110" t="n">
-        <v>5.188</v>
+        <v>5.073</v>
       </c>
       <c r="H110" t="n">
-        <v>5.191</v>
+        <v>5.072</v>
       </c>
       <c r="I110" t="n">
-        <v>5.188</v>
+        <v>5.072</v>
       </c>
       <c r="J110" t="n">
-        <v>5.19</v>
+        <v>5.073</v>
       </c>
       <c r="K110" t="n">
-        <v>5.197</v>
+        <v>5.077</v>
       </c>
       <c r="L110" t="n">
-        <v>5.198</v>
+        <v>5.081</v>
       </c>
       <c r="M110" t="n">
-        <v>5.217</v>
+        <v>5.081</v>
       </c>
     </row>
     <row r="111">
@@ -6576,39 +6576,39 @@
         <v>9039635</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="F111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="G111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="H111" t="n">
-        <v>5.079</v>
+        <v>4.929</v>
       </c>
       <c r="I111" t="n">
-        <v>5.079</v>
+        <v>4.929</v>
       </c>
       <c r="J111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="K111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="L111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="M111" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="112">
@@ -6621,39 +6621,39 @@
         <v>9039635</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4.93</v>
+        <v>4.78</v>
       </c>
       <c r="F112" t="n">
-        <v>4.932</v>
+        <v>4.78</v>
       </c>
       <c r="G112" t="n">
-        <v>4.93</v>
+        <v>4.761</v>
       </c>
       <c r="H112" t="n">
-        <v>4.93</v>
+        <v>4.761</v>
       </c>
       <c r="I112" t="n">
-        <v>4.93</v>
+        <v>4.761</v>
       </c>
       <c r="J112" t="n">
-        <v>4.93</v>
+        <v>4.761</v>
       </c>
       <c r="K112" t="n">
-        <v>4.93</v>
+        <v>4.77</v>
       </c>
       <c r="L112" t="n">
-        <v>4.93</v>
+        <v>4.78</v>
       </c>
       <c r="M112" t="n">
-        <v>4.932</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="113">
@@ -6666,39 +6666,39 @@
         <v>9039635</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4.78</v>
+        <v>4.633</v>
       </c>
       <c r="F113" t="n">
-        <v>4.78</v>
+        <v>4.64</v>
       </c>
       <c r="G113" t="n">
-        <v>4.78</v>
+        <v>4.622</v>
       </c>
       <c r="H113" t="n">
-        <v>4.78</v>
+        <v>4.622</v>
       </c>
       <c r="I113" t="n">
-        <v>4.78</v>
+        <v>4.622</v>
       </c>
       <c r="J113" t="n">
-        <v>4.78</v>
+        <v>4.622</v>
       </c>
       <c r="K113" t="n">
-        <v>4.78</v>
+        <v>4.629</v>
       </c>
       <c r="L113" t="n">
-        <v>4.78</v>
+        <v>4.634</v>
       </c>
       <c r="M113" t="n">
-        <v>4.78</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="114">
@@ -6711,39 +6711,39 @@
         <v>9038269</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="F114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="G114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="H114" t="n">
-        <v>3.295</v>
+        <v>3.317</v>
       </c>
       <c r="I114" t="n">
-        <v>3.295</v>
+        <v>3.317</v>
       </c>
       <c r="J114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="K114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="L114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="M114" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
     </row>
     <row r="115">
@@ -6756,39 +6756,39 @@
         <v>9038269</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="F115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="G115" t="n">
-        <v>3.31</v>
+        <v>3.462</v>
       </c>
       <c r="H115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="I115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="J115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="K115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="L115" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="M115" t="n">
-        <v>3.31</v>
+        <v>3.462</v>
       </c>
     </row>
     <row r="116">
@@ -6801,39 +6801,39 @@
         <v>9038269</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="F116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="G116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="H116" t="n">
-        <v>3.46</v>
+        <v>3.674</v>
       </c>
       <c r="I116" t="n">
-        <v>3.46</v>
+        <v>3.674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.46</v>
+        <v>3.675</v>
       </c>
       <c r="K116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="L116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="M116" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
     </row>
     <row r="117">
@@ -6846,39 +6846,39 @@
         <v>9038269</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="F117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="G117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="H117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="I117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="J117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="K117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="L117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="M117" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="118">
@@ -6891,39 +6891,39 @@
         <v>9038269</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="F118" t="n">
-        <v>3.723</v>
+        <v>3.76</v>
       </c>
       <c r="G118" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="H118" t="n">
-        <v>3.723</v>
+        <v>3.758</v>
       </c>
       <c r="I118" t="n">
-        <v>3.723</v>
+        <v>3.758</v>
       </c>
       <c r="J118" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="K118" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="L118" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="M118" t="n">
-        <v>3.723</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="119">
@@ -6936,39 +6936,39 @@
         <v>9038269</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="F119" t="n">
-        <v>3.751</v>
+        <v>3.764</v>
       </c>
       <c r="G119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="H119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="I119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="J119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="K119" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="L119" t="n">
-        <v>3.751</v>
+        <v>3.763</v>
       </c>
       <c r="M119" t="n">
-        <v>3.751</v>
+        <v>3.764</v>
       </c>
     </row>
     <row r="120">
@@ -6981,39 +6981,39 @@
         <v>9038269</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3.761</v>
+        <v>3.742</v>
       </c>
       <c r="F120" t="n">
-        <v>3.761</v>
+        <v>3.743</v>
       </c>
       <c r="G120" t="n">
-        <v>3.76</v>
+        <v>3.742</v>
       </c>
       <c r="H120" t="n">
-        <v>3.76</v>
+        <v>3.741</v>
       </c>
       <c r="I120" t="n">
-        <v>3.76</v>
+        <v>3.741</v>
       </c>
       <c r="J120" t="n">
-        <v>3.76</v>
+        <v>3.742</v>
       </c>
       <c r="K120" t="n">
-        <v>3.761</v>
+        <v>3.742</v>
       </c>
       <c r="L120" t="n">
-        <v>3.761</v>
+        <v>3.742</v>
       </c>
       <c r="M120" t="n">
-        <v>3.761</v>
+        <v>3.743</v>
       </c>
     </row>
   </sheetData>
@@ -7043,37 +7043,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -7087,25 +7087,25 @@
         <v>9043370</v>
       </c>
       <c r="C2" t="n">
-        <v>8.144</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>8.127000000000001</v>
+        <v>8.112</v>
       </c>
       <c r="E2" t="n">
-        <v>8.118</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>8.093</v>
+        <v>8.048</v>
       </c>
       <c r="G2" t="n">
-        <v>8.061</v>
+        <v>8.029</v>
       </c>
       <c r="H2" t="n">
-        <v>8.037000000000001</v>
+        <v>8.016999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.023</v>
+        <v>8.010999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -7118,16 +7118,16 @@
         <v>9036028</v>
       </c>
       <c r="C3" t="n">
-        <v>6.14</v>
+        <v>6.136</v>
       </c>
       <c r="D3" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="E3" t="n">
-        <v>6.16</v>
+        <v>6.183</v>
       </c>
       <c r="F3" t="n">
-        <v>6.186</v>
+        <v>6.218</v>
       </c>
       <c r="G3" t="n">
         <v>6.22</v>
@@ -7136,7 +7136,7 @@
         <v>6.22</v>
       </c>
       <c r="I3" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4">
@@ -7149,25 +7149,25 @@
         <v>9040208</v>
       </c>
       <c r="C4" t="n">
-        <v>5.41</v>
+        <v>5.147</v>
       </c>
       <c r="D4" t="n">
-        <v>5.159</v>
+        <v>4.982</v>
       </c>
       <c r="E4" t="n">
-        <v>5.009</v>
+        <v>4.881</v>
       </c>
       <c r="F4" t="n">
-        <v>4.905</v>
+        <v>4.815</v>
       </c>
       <c r="G4" t="n">
-        <v>4.838</v>
+        <v>4.758</v>
       </c>
       <c r="H4" t="n">
-        <v>4.787</v>
+        <v>4.684</v>
       </c>
       <c r="I4" t="n">
-        <v>4.723</v>
+        <v>4.641</v>
       </c>
     </row>
     <row r="5">
@@ -7180,25 +7180,25 @@
         <v>9053555</v>
       </c>
       <c r="C5" t="n">
-        <v>12.304</v>
+        <v>12.283</v>
       </c>
       <c r="D5" t="n">
-        <v>12.288</v>
+        <v>12.23</v>
       </c>
       <c r="E5" t="n">
-        <v>12.232</v>
+        <v>12.195</v>
       </c>
       <c r="F5" t="n">
-        <v>12.199</v>
+        <v>12.137</v>
       </c>
       <c r="G5" t="n">
-        <v>12.146</v>
+        <v>12.089</v>
       </c>
       <c r="H5" t="n">
-        <v>12.098</v>
+        <v>11.939</v>
       </c>
       <c r="I5" t="n">
-        <v>11.989</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="6">
@@ -7211,25 +7211,25 @@
         <v>9038134</v>
       </c>
       <c r="C6" t="n">
-        <v>112.161</v>
+        <v>112.06</v>
       </c>
       <c r="D6" t="n">
-        <v>112.103</v>
+        <v>111.855</v>
       </c>
       <c r="E6" t="n">
-        <v>111.949</v>
+        <v>111.645</v>
       </c>
       <c r="F6" t="n">
-        <v>111.731</v>
+        <v>111.446</v>
       </c>
       <c r="G6" t="n">
-        <v>111.59</v>
+        <v>111.193</v>
       </c>
       <c r="H6" t="n">
-        <v>111.394</v>
+        <v>110.911</v>
       </c>
       <c r="I6" t="n">
-        <v>111.15</v>
+        <v>110.579</v>
       </c>
     </row>
     <row r="7">
@@ -7242,25 +7242,25 @@
         <v>9044756</v>
       </c>
       <c r="C7" t="n">
-        <v>11.878</v>
+        <v>11.652</v>
       </c>
       <c r="D7" t="n">
-        <v>11.67</v>
+        <v>9.335000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>9.348000000000001</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>9.042999999999999</v>
+        <v>8.699</v>
       </c>
       <c r="G7" t="n">
-        <v>8.725</v>
+        <v>8.477</v>
       </c>
       <c r="H7" t="n">
-        <v>8.478</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>8.465</v>
+        <v>8.397</v>
       </c>
     </row>
     <row r="8">
@@ -7273,25 +7273,25 @@
         <v>9042214</v>
       </c>
       <c r="C8" t="n">
-        <v>8.968999999999999</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>8.928000000000001</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>8.862</v>
+        <v>8.827</v>
       </c>
       <c r="F8" t="n">
-        <v>8.827999999999999</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>8.759</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>8.512</v>
+        <v>8.395</v>
       </c>
       <c r="I8" t="n">
-        <v>8.414999999999999</v>
+        <v>8.035</v>
       </c>
     </row>
     <row r="9">
@@ -7304,25 +7304,25 @@
         <v>9043597</v>
       </c>
       <c r="C9" t="n">
-        <v>5.804</v>
+        <v>5.8</v>
       </c>
       <c r="D9" t="n">
-        <v>5.801</v>
+        <v>5.701</v>
       </c>
       <c r="E9" t="n">
-        <v>5.709</v>
+        <v>5.544</v>
       </c>
       <c r="F9" t="n">
-        <v>5.552</v>
+        <v>5.378</v>
       </c>
       <c r="G9" t="n">
-        <v>5.39</v>
+        <v>5.286</v>
       </c>
       <c r="H9" t="n">
-        <v>5.294</v>
+        <v>5.28</v>
       </c>
       <c r="I9" t="n">
-        <v>5.283</v>
+        <v>5.302</v>
       </c>
     </row>
     <row r="10">
@@ -7335,25 +7335,25 @@
         <v>9040454</v>
       </c>
       <c r="C10" t="n">
-        <v>5.982</v>
+        <v>6.078</v>
       </c>
       <c r="D10" t="n">
-        <v>6.074</v>
+        <v>6.165</v>
       </c>
       <c r="E10" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="F10" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="G10" t="n">
-        <v>6.322</v>
+        <v>6.361</v>
       </c>
       <c r="H10" t="n">
-        <v>6.352</v>
+        <v>6.32</v>
       </c>
       <c r="I10" t="n">
-        <v>6.311</v>
+        <v>6.233</v>
       </c>
     </row>
     <row r="11">
@@ -7366,25 +7366,25 @@
         <v>9037610</v>
       </c>
       <c r="C11" t="n">
-        <v>4.756</v>
+        <v>4.668</v>
       </c>
       <c r="D11" t="n">
-        <v>4.735</v>
+        <v>4.815</v>
       </c>
       <c r="E11" t="n">
-        <v>4.919</v>
+        <v>4.917</v>
       </c>
       <c r="F11" t="n">
-        <v>5.103</v>
+        <v>4.898</v>
       </c>
       <c r="G11" t="n">
-        <v>5.162</v>
+        <v>4.779</v>
       </c>
       <c r="H11" t="n">
-        <v>4.907</v>
+        <v>4.556</v>
       </c>
       <c r="I11" t="n">
-        <v>4.649</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="12">
@@ -7397,25 +7397,25 @@
         <v>9043425</v>
       </c>
       <c r="C12" t="n">
-        <v>6.777</v>
+        <v>6.75</v>
       </c>
       <c r="D12" t="n">
-        <v>6.748</v>
+        <v>6.72</v>
       </c>
       <c r="E12" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="F12" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="G12" t="n">
-        <v>6.637</v>
+        <v>6.61</v>
       </c>
       <c r="H12" t="n">
-        <v>6.603</v>
+        <v>6.55</v>
       </c>
       <c r="I12" t="n">
-        <v>6.548</v>
+        <v>6.509</v>
       </c>
     </row>
     <row r="13">
@@ -7428,25 +7428,25 @@
         <v>9042153</v>
       </c>
       <c r="C13" t="n">
-        <v>11.504</v>
+        <v>11.369</v>
       </c>
       <c r="D13" t="n">
-        <v>11.372</v>
+        <v>11.098</v>
       </c>
       <c r="E13" t="n">
-        <v>11.099</v>
+        <v>10.868</v>
       </c>
       <c r="F13" t="n">
-        <v>10.869</v>
+        <v>10.712</v>
       </c>
       <c r="G13" t="n">
-        <v>10.731</v>
+        <v>10.557</v>
       </c>
       <c r="H13" t="n">
-        <v>10.59</v>
+        <v>10.438</v>
       </c>
       <c r="I13" t="n">
-        <v>10.462</v>
+        <v>10.348</v>
       </c>
     </row>
     <row r="14">
@@ -7459,25 +7459,25 @@
         <v>9040439</v>
       </c>
       <c r="C14" t="n">
-        <v>6.693</v>
+        <v>6.876</v>
       </c>
       <c r="D14" t="n">
-        <v>6.876</v>
+        <v>7.079</v>
       </c>
       <c r="E14" t="n">
-        <v>7.079</v>
+        <v>7.15</v>
       </c>
       <c r="F14" t="n">
+        <v>7.205</v>
+      </c>
+      <c r="G14" t="n">
         <v>7.15</v>
       </c>
-      <c r="G14" t="n">
-        <v>7.205</v>
-      </c>
       <c r="H14" t="n">
-        <v>7.15</v>
+        <v>7.057</v>
       </c>
       <c r="I14" t="n">
-        <v>7.057</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="15">
@@ -7490,25 +7490,25 @@
         <v>9032282</v>
       </c>
       <c r="C15" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="D15" t="n">
-        <v>7.088</v>
+        <v>7.138</v>
       </c>
       <c r="E15" t="n">
-        <v>7.136</v>
+        <v>7.156</v>
       </c>
       <c r="F15" t="n">
-        <v>7.162</v>
+        <v>7.113</v>
       </c>
       <c r="G15" t="n">
-        <v>7.111</v>
+        <v>7.04</v>
       </c>
       <c r="H15" t="n">
-        <v>7.04</v>
+        <v>6.968</v>
       </c>
       <c r="I15" t="n">
-        <v>6.969</v>
+        <v>6.899</v>
       </c>
     </row>
     <row r="16">
@@ -7521,25 +7521,25 @@
         <v>9037738</v>
       </c>
       <c r="C16" t="n">
-        <v>5.591</v>
+        <v>5.717</v>
       </c>
       <c r="D16" t="n">
-        <v>5.881</v>
+        <v>5.921</v>
       </c>
       <c r="E16" t="n">
-        <v>6.086</v>
+        <v>5.953</v>
       </c>
       <c r="F16" t="n">
-        <v>6.071</v>
+        <v>5.82</v>
       </c>
       <c r="G16" t="n">
-        <v>5.877</v>
+        <v>5.583</v>
       </c>
       <c r="H16" t="n">
-        <v>5.617</v>
+        <v>5.369</v>
       </c>
       <c r="I16" t="n">
-        <v>5.526</v>
+        <v>5.218</v>
       </c>
     </row>
     <row r="17">
@@ -7552,25 +7552,25 @@
         <v>9039635</v>
       </c>
       <c r="C17" t="n">
-        <v>5.483</v>
+        <v>5.452</v>
       </c>
       <c r="D17" t="n">
-        <v>5.44</v>
+        <v>5.355</v>
       </c>
       <c r="E17" t="n">
-        <v>5.35</v>
+        <v>5.195</v>
       </c>
       <c r="F17" t="n">
-        <v>5.197</v>
+        <v>5.077</v>
       </c>
       <c r="G17" t="n">
-        <v>5.079</v>
+        <v>4.93</v>
       </c>
       <c r="H17" t="n">
-        <v>4.93</v>
+        <v>4.77</v>
       </c>
       <c r="I17" t="n">
-        <v>4.78</v>
+        <v>4.629</v>
       </c>
     </row>
     <row r="18">
@@ -7583,25 +7583,25 @@
         <v>9038269</v>
       </c>
       <c r="C18" t="n">
-        <v>3.295</v>
+        <v>3.318</v>
       </c>
       <c r="D18" t="n">
-        <v>3.309</v>
+        <v>3.462</v>
       </c>
       <c r="E18" t="n">
-        <v>3.46</v>
+        <v>3.676</v>
       </c>
       <c r="F18" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="G18" t="n">
-        <v>3.723</v>
+        <v>3.759</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>3.763</v>
       </c>
       <c r="I18" t="n">
-        <v>3.761</v>
+        <v>3.742</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -520,31 +520,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.007999999999999</v>
+        <v>8.103</v>
       </c>
       <c r="F2" t="n">
-        <v>8.061</v>
+        <v>8.169</v>
       </c>
       <c r="G2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="H2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="I2" t="n">
-        <v>8.010999999999999</v>
+        <v>8.113</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.112</v>
+        <v>-0.121</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7152</v>
+        <v>7153</v>
       </c>
       <c r="M2" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="N2" t="n">
-        <v>0.469</v>
+        <v>0.467</v>
       </c>
       <c r="O2" t="n">
-        <v>0.679</v>
+        <v>0.676</v>
       </c>
       <c r="P2" t="n">
-        <v>2.751</v>
+        <v>2.756</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -583,31 +583,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.136</v>
+        <v>6.121</v>
       </c>
       <c r="F3" t="n">
-        <v>6.191</v>
+        <v>6.19</v>
       </c>
       <c r="G3" t="n">
-        <v>6.22</v>
+        <v>6.239</v>
       </c>
       <c r="H3" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2</v>
+        <v>6.128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.064</v>
+        <v>-0.016</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14188</v>
+        <v>14189</v>
       </c>
       <c r="M3" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="N3" t="n">
-        <v>0.075</v>
+        <v>0.067</v>
       </c>
       <c r="O3" t="n">
         <v>0.505</v>
       </c>
       <c r="P3" t="n">
-        <v>1.495</v>
+        <v>1.501</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -646,31 +646,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="F4" t="n">
-        <v>4.844</v>
+        <v>4.715</v>
       </c>
       <c r="G4" t="n">
-        <v>5.148</v>
+        <v>4.978</v>
       </c>
       <c r="H4" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="I4" t="n">
-        <v>4.641</v>
+        <v>4.63</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.506</v>
+        <v>-0.348</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13792</v>
+        <v>13793</v>
       </c>
       <c r="M4" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.082</v>
+        <v>-0.089</v>
       </c>
       <c r="O4" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="P4" t="n">
-        <v>1.477</v>
+        <v>1.482</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -709,31 +709,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11.828</v>
+        <v>11.773</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1</v>
+        <v>12.037</v>
       </c>
       <c r="G5" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="H5" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="I5" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.453</v>
+        <v>-0.468</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9795</v>
+        <v>9796</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05</v>
+        <v>0.034</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.597</v>
+        <v>-0.761</v>
       </c>
       <c r="O5" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="P5" t="n">
-        <v>11.068</v>
+        <v>11.623</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -772,31 +772,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>110.021</v>
+        <v>95.876</v>
       </c>
       <c r="F6" t="n">
-        <v>111.384</v>
+        <v>105.301</v>
       </c>
       <c r="G6" t="n">
-        <v>112.08</v>
+        <v>109.3</v>
       </c>
       <c r="H6" t="n">
-        <v>112.06</v>
+        <v>109.237</v>
       </c>
       <c r="I6" t="n">
-        <v>110.579</v>
+        <v>103.54</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.481</v>
+        <v>-5.697</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9955</v>
+        <v>9956</v>
       </c>
       <c r="M6" t="n">
-        <v>0.129</v>
+        <v>0.136</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.738</v>
+        <v>-0.325</v>
       </c>
       <c r="O6" t="n">
-        <v>0.129</v>
+        <v>0.066</v>
       </c>
       <c r="P6" t="n">
-        <v>36.054</v>
+        <v>31.506</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -835,31 +835,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="F7" t="n">
-        <v>9.145</v>
+        <v>9.068</v>
       </c>
       <c r="G7" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="H7" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="I7" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.255</v>
+        <v>-1.08</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>3099</v>
       </c>
       <c r="M7" t="n">
-        <v>0.794</v>
+        <v>0.801</v>
       </c>
       <c r="N7" t="n">
-        <v>0.609</v>
+        <v>0.621</v>
       </c>
       <c r="O7" t="n">
-        <v>0.786</v>
+        <v>0.792</v>
       </c>
       <c r="P7" t="n">
-        <v>2.701</v>
+        <v>2.659</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.035</v>
+        <v>7.99</v>
       </c>
       <c r="F8" t="n">
-        <v>8.612</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.893</v>
+        <v>-0.853</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -930,19 +930,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="M8" t="n">
-        <v>0.823</v>
+        <v>0.825</v>
       </c>
       <c r="N8" t="n">
-        <v>0.648</v>
+        <v>0.654</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>2.155</v>
+        <v>2.139</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -961,31 +961,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.28</v>
+        <v>5.289</v>
       </c>
       <c r="F9" t="n">
-        <v>5.47</v>
+        <v>5.413</v>
       </c>
       <c r="G9" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="I9" t="n">
-        <v>5.302</v>
+        <v>5.339</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.498</v>
+        <v>-0.378</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4110</v>
+        <v>4111</v>
       </c>
       <c r="M9" t="n">
-        <v>0.829</v>
+        <v>0.791</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.827</v>
+        <v>0.788</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2</v>
+        <v>1.343</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1024,51 +1024,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.078</v>
+        <v>6.142</v>
       </c>
       <c r="F10" t="n">
-        <v>6.247</v>
+        <v>6.267</v>
       </c>
       <c r="G10" t="n">
-        <v>6.362</v>
+        <v>6.36</v>
       </c>
       <c r="H10" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="I10" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
       <c r="J10" t="n">
-        <v>0.155</v>
+        <v>-0.028</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8986</v>
+        <v>8987</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.63</v>
+        <v>0.642</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="P10" t="n">
-        <v>1.823</v>
+        <v>1.793</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1087,31 +1087,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.846</v>
+        <v>3.462</v>
       </c>
       <c r="F11" t="n">
-        <v>4.707</v>
+        <v>4.433</v>
       </c>
       <c r="G11" t="n">
-        <v>4.969</v>
+        <v>4.906</v>
       </c>
       <c r="H11" t="n">
-        <v>4.668</v>
+        <v>4.685</v>
       </c>
       <c r="I11" t="n">
-        <v>4.313</v>
+        <v>4.386</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.355</v>
+        <v>-0.299</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1122,16 +1122,16 @@
         <v>2305</v>
       </c>
       <c r="M11" t="n">
-        <v>0.518</v>
+        <v>0.534</v>
       </c>
       <c r="N11" t="n">
-        <v>0.015</v>
+        <v>0.09</v>
       </c>
       <c r="O11" t="n">
-        <v>0.515</v>
+        <v>0.528</v>
       </c>
       <c r="P11" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>6.559</v>
       </c>
       <c r="F12" t="n">
-        <v>6.638</v>
+        <v>6.669</v>
       </c>
       <c r="G12" t="n">
-        <v>6.75</v>
+        <v>6.774</v>
       </c>
       <c r="H12" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="I12" t="n">
-        <v>6.509</v>
+        <v>6.561</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.241</v>
+        <v>-0.212</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1182,19 +1182,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>14032</v>
+        <v>14033</v>
       </c>
       <c r="M12" t="n">
-        <v>0.781</v>
+        <v>0.776</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="O12" t="n">
-        <v>0.78</v>
+        <v>0.776</v>
       </c>
       <c r="P12" t="n">
-        <v>2.286</v>
+        <v>2.322</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.271</v>
+        <v>10.185</v>
       </c>
       <c r="F13" t="n">
-        <v>10.77</v>
+        <v>10.577</v>
       </c>
       <c r="G13" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="H13" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="I13" t="n">
-        <v>10.348</v>
+        <v>10.22</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.021</v>
+        <v>-0.872</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>3737</v>
       </c>
       <c r="M13" t="n">
-        <v>0.356</v>
+        <v>0.331</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.12</v>
+        <v>-0.272</v>
       </c>
       <c r="O13" t="n">
-        <v>0.335</v>
+        <v>0.325</v>
       </c>
       <c r="P13" t="n">
-        <v>2.697</v>
+        <v>2.874</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1276,51 +1276,51 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="F14" t="n">
-        <v>7.052</v>
+        <v>6.973</v>
       </c>
       <c r="G14" t="n">
-        <v>7.205</v>
+        <v>7.132</v>
       </c>
       <c r="H14" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="I14" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.026</v>
+        <v>-0.327</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13851</v>
+        <v>13852</v>
       </c>
       <c r="M14" t="n">
-        <v>0.762</v>
+        <v>0.753</v>
       </c>
       <c r="N14" t="n">
-        <v>0.536</v>
+        <v>0.516</v>
       </c>
       <c r="O14" t="n">
-        <v>0.76</v>
+        <v>0.752</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.962</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1339,31 +1339,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.898</v>
+        <v>6.946</v>
       </c>
       <c r="F15" t="n">
-        <v>7.058</v>
+        <v>7.11</v>
       </c>
       <c r="G15" t="n">
-        <v>7.157</v>
+        <v>7.223</v>
       </c>
       <c r="H15" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="I15" t="n">
-        <v>6.899</v>
+        <v>6.949</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.191</v>
+        <v>-0.267</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1371,19 +1371,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8826</v>
+        <v>8827</v>
       </c>
       <c r="M15" t="n">
-        <v>0.305</v>
+        <v>0.296</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.198</v>
+        <v>-0.116</v>
       </c>
       <c r="O15" t="n">
-        <v>0.28</v>
+        <v>0.247</v>
       </c>
       <c r="P15" t="n">
-        <v>1.911</v>
+        <v>1.845</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1402,51 +1402,51 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.642</v>
+        <v>4.554</v>
       </c>
       <c r="F16" t="n">
-        <v>5.654</v>
+        <v>5.525</v>
       </c>
       <c r="G16" t="n">
-        <v>6.037</v>
+        <v>6.248</v>
       </c>
       <c r="H16" t="n">
-        <v>5.717</v>
+        <v>5.725</v>
       </c>
       <c r="I16" t="n">
-        <v>5.218</v>
+        <v>5.956</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.499</v>
+        <v>0.231</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6</v>
+        <v>0.607</v>
       </c>
       <c r="N16" t="n">
-        <v>0.215</v>
+        <v>0.226</v>
       </c>
       <c r="O16" t="n">
-        <v>0.597</v>
+        <v>0.604</v>
       </c>
       <c r="P16" t="n">
-        <v>1.488</v>
+        <v>1.479</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1465,31 +1465,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.622</v>
+        <v>4.672</v>
       </c>
       <c r="F17" t="n">
-        <v>5.058</v>
+        <v>4.998</v>
       </c>
       <c r="G17" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="H17" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="I17" t="n">
-        <v>4.629</v>
+        <v>4.686</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.823</v>
+        <v>-0.723</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1497,19 +1497,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10215</v>
+        <v>10216</v>
       </c>
       <c r="M17" t="n">
-        <v>0.867</v>
+        <v>0.868</v>
       </c>
       <c r="N17" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="O17" t="n">
         <v>0.847</v>
       </c>
       <c r="P17" t="n">
-        <v>1.685</v>
+        <v>1.678</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1528,31 +1528,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.317</v>
+        <v>3.431</v>
       </c>
       <c r="F18" t="n">
-        <v>3.636</v>
+        <v>3.628</v>
       </c>
       <c r="G18" t="n">
-        <v>3.764</v>
+        <v>3.721</v>
       </c>
       <c r="H18" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="I18" t="n">
-        <v>3.742</v>
+        <v>3.617</v>
       </c>
       <c r="J18" t="n">
-        <v>0.424</v>
+        <v>0.185</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>14533</v>
+        <v>14534</v>
       </c>
       <c r="M18" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="P18" t="n">
-        <v>1.726</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1671,39 +1671,39 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="F2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="G2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="H2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="I2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="J2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="K2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="L2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="M2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
     </row>
     <row r="3">
@@ -1716,39 +1716,39 @@
         <v>9043370</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.112</v>
+        <v>8.211</v>
       </c>
       <c r="F3" t="n">
-        <v>8.112</v>
+        <v>8.212</v>
       </c>
       <c r="G3" t="n">
-        <v>8.113</v>
+        <v>8.212</v>
       </c>
       <c r="H3" t="n">
-        <v>8.112</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>8.112</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>8.112</v>
+        <v>8.211</v>
       </c>
       <c r="K3" t="n">
-        <v>8.112</v>
+        <v>8.211</v>
       </c>
       <c r="L3" t="n">
-        <v>8.112</v>
+        <v>8.212</v>
       </c>
       <c r="M3" t="n">
-        <v>8.113</v>
+        <v>8.212</v>
       </c>
     </row>
     <row r="4">
@@ -1761,39 +1761,39 @@
         <v>9043370</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.086</v>
+        <v>8.186</v>
       </c>
       <c r="F4" t="n">
-        <v>8.086</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>8.087</v>
+        <v>8.191000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.083</v>
+        <v>8.182</v>
       </c>
       <c r="I4" t="n">
-        <v>8.083</v>
+        <v>8.182</v>
       </c>
       <c r="J4" t="n">
-        <v>8.085000000000001</v>
+        <v>8.185</v>
       </c>
       <c r="K4" t="n">
-        <v>8.085000000000001</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>8.086</v>
+        <v>8.189</v>
       </c>
       <c r="M4" t="n">
-        <v>8.087</v>
+        <v>8.191000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1806,39 +1806,39 @@
         <v>9043370</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.048999999999999</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>8.048999999999999</v>
+        <v>8.169</v>
       </c>
       <c r="G5" t="n">
-        <v>8.048999999999999</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>8.045999999999999</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>8.045999999999999</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>8.048</v>
+        <v>8.163</v>
       </c>
       <c r="K5" t="n">
-        <v>8.048</v>
+        <v>8.166</v>
       </c>
       <c r="L5" t="n">
-        <v>8.048999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="M5" t="n">
-        <v>8.048999999999999</v>
+        <v>8.175000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1851,39 +1851,39 @@
         <v>9043370</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8.029999999999999</v>
+        <v>8.148</v>
       </c>
       <c r="F6" t="n">
-        <v>8.029999999999999</v>
+        <v>8.153</v>
       </c>
       <c r="G6" t="n">
-        <v>8.029999999999999</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>8.028</v>
+        <v>8.129</v>
       </c>
       <c r="I6" t="n">
-        <v>8.028</v>
+        <v>8.129</v>
       </c>
       <c r="J6" t="n">
-        <v>8.029</v>
+        <v>8.143000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>8.029</v>
+        <v>8.147</v>
       </c>
       <c r="L6" t="n">
-        <v>8.029999999999999</v>
+        <v>8.154</v>
       </c>
       <c r="M6" t="n">
-        <v>8.029999999999999</v>
+        <v>8.157999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1896,39 +1896,39 @@
         <v>9043370</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.018000000000001</v>
+        <v>8.129</v>
       </c>
       <c r="F7" t="n">
-        <v>8.02</v>
+        <v>8.135</v>
       </c>
       <c r="G7" t="n">
-        <v>8.016999999999999</v>
+        <v>8.138</v>
       </c>
       <c r="H7" t="n">
-        <v>8.013999999999999</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.013999999999999</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>8.016</v>
+        <v>8.125</v>
       </c>
       <c r="K7" t="n">
-        <v>8.016999999999999</v>
+        <v>8.128</v>
       </c>
       <c r="L7" t="n">
-        <v>8.019</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>8.02</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="8">
@@ -1941,39 +1941,39 @@
         <v>9043370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.012</v>
+        <v>8.109</v>
       </c>
       <c r="F8" t="n">
-        <v>8.012</v>
+        <v>8.116</v>
       </c>
       <c r="G8" t="n">
-        <v>8.007999999999999</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>8.010999999999999</v>
+        <v>8.103</v>
       </c>
       <c r="I8" t="n">
-        <v>8.007999999999999</v>
+        <v>8.103</v>
       </c>
       <c r="J8" t="n">
-        <v>8.01</v>
+        <v>8.106999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>8.010999999999999</v>
+        <v>8.113</v>
       </c>
       <c r="L8" t="n">
-        <v>8.012</v>
+        <v>8.118</v>
       </c>
       <c r="M8" t="n">
-        <v>8.012</v>
+        <v>8.122999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1986,39 +1986,39 @@
         <v>9036028</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="F9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="G9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="H9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="I9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="J9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="K9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="L9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="M9" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
     </row>
     <row r="10">
@@ -2031,39 +2031,39 @@
         <v>9036028</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="F10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="G10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="H10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="I10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="J10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="K10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="L10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="M10" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
     </row>
     <row r="11">
@@ -2076,39 +2076,39 @@
         <v>9036028</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
       <c r="F11" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
       <c r="G11" t="n">
-        <v>6.182</v>
+        <v>6.222</v>
       </c>
       <c r="H11" t="n">
-        <v>6.182</v>
+        <v>6.222</v>
       </c>
       <c r="I11" t="n">
-        <v>6.182</v>
+        <v>6.222</v>
       </c>
       <c r="J11" t="n">
-        <v>6.182</v>
+        <v>6.222</v>
       </c>
       <c r="K11" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
       <c r="L11" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
       <c r="M11" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
     </row>
     <row r="12">
@@ -2121,39 +2121,39 @@
         <v>9036028</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.22</v>
+        <v>6.239</v>
       </c>
       <c r="F12" t="n">
-        <v>6.22</v>
+        <v>6.239</v>
       </c>
       <c r="G12" t="n">
-        <v>6.217</v>
+        <v>6.238</v>
       </c>
       <c r="H12" t="n">
-        <v>6.217</v>
+        <v>6.238</v>
       </c>
       <c r="I12" t="n">
-        <v>6.217</v>
+        <v>6.238</v>
       </c>
       <c r="J12" t="n">
-        <v>6.217</v>
+        <v>6.238</v>
       </c>
       <c r="K12" t="n">
-        <v>6.218</v>
+        <v>6.238</v>
       </c>
       <c r="L12" t="n">
-        <v>6.22</v>
+        <v>6.239</v>
       </c>
       <c r="M12" t="n">
-        <v>6.22</v>
+        <v>6.239</v>
       </c>
     </row>
     <row r="13">
@@ -2166,39 +2166,39 @@
         <v>9036028</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="F13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="G13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="H13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="I13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="J13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="K13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="L13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="M13" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
     </row>
     <row r="14">
@@ -2211,39 +2211,39 @@
         <v>9036028</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.22</v>
+        <v>6.196</v>
       </c>
       <c r="F14" t="n">
-        <v>6.22</v>
+        <v>6.197</v>
       </c>
       <c r="G14" t="n">
-        <v>6.22</v>
+        <v>6.193</v>
       </c>
       <c r="H14" t="n">
-        <v>6.22</v>
+        <v>6.187</v>
       </c>
       <c r="I14" t="n">
-        <v>6.22</v>
+        <v>6.187</v>
       </c>
       <c r="J14" t="n">
-        <v>6.22</v>
+        <v>6.191</v>
       </c>
       <c r="K14" t="n">
-        <v>6.22</v>
+        <v>6.193</v>
       </c>
       <c r="L14" t="n">
-        <v>6.22</v>
+        <v>6.197</v>
       </c>
       <c r="M14" t="n">
-        <v>6.22</v>
+        <v>6.197</v>
       </c>
     </row>
     <row r="15">
@@ -2256,39 +2256,39 @@
         <v>9036028</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.2</v>
+        <v>6.129</v>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>6.132</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.129</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6.121</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6.121</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>6.127</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>6.128</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="M15" t="n">
-        <v>6.2</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="16">
@@ -2301,39 +2301,39 @@
         <v>9040208</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="F16" t="n">
-        <v>5.148</v>
+        <v>4.978</v>
       </c>
       <c r="G16" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="H16" t="n">
-        <v>5.146</v>
+        <v>4.977</v>
       </c>
       <c r="I16" t="n">
-        <v>5.146</v>
+        <v>4.977</v>
       </c>
       <c r="J16" t="n">
-        <v>5.146</v>
+        <v>4.978</v>
       </c>
       <c r="K16" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="L16" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="M16" t="n">
-        <v>5.148</v>
+        <v>4.978</v>
       </c>
     </row>
     <row r="17">
@@ -2346,39 +2346,39 @@
         <v>9040208</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.981</v>
+        <v>4.837</v>
       </c>
       <c r="F17" t="n">
-        <v>4.985</v>
+        <v>4.839</v>
       </c>
       <c r="G17" t="n">
-        <v>4.982</v>
+        <v>4.837</v>
       </c>
       <c r="H17" t="n">
-        <v>4.98</v>
+        <v>4.831</v>
       </c>
       <c r="I17" t="n">
-        <v>4.98</v>
+        <v>4.831</v>
       </c>
       <c r="J17" t="n">
-        <v>4.981</v>
+        <v>4.835</v>
       </c>
       <c r="K17" t="n">
-        <v>4.982</v>
+        <v>4.836</v>
       </c>
       <c r="L17" t="n">
-        <v>4.983</v>
+        <v>4.837</v>
       </c>
       <c r="M17" t="n">
-        <v>4.985</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="18">
@@ -2391,39 +2391,39 @@
         <v>9040208</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.878</v>
+        <v>4.74</v>
       </c>
       <c r="F18" t="n">
-        <v>4.887</v>
+        <v>4.745</v>
       </c>
       <c r="G18" t="n">
-        <v>4.887</v>
+        <v>4.745</v>
       </c>
       <c r="H18" t="n">
-        <v>4.87</v>
+        <v>4.716</v>
       </c>
       <c r="I18" t="n">
-        <v>4.87</v>
+        <v>4.716</v>
       </c>
       <c r="J18" t="n">
-        <v>4.876</v>
+        <v>4.734</v>
       </c>
       <c r="K18" t="n">
-        <v>4.881</v>
+        <v>4.736</v>
       </c>
       <c r="L18" t="n">
-        <v>4.887</v>
+        <v>4.745</v>
       </c>
       <c r="M18" t="n">
-        <v>4.887</v>
+        <v>4.745</v>
       </c>
     </row>
     <row r="19">
@@ -2436,39 +2436,39 @@
         <v>9040208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.802</v>
+        <v>4.644</v>
       </c>
       <c r="F19" t="n">
-        <v>4.832</v>
+        <v>4.66</v>
       </c>
       <c r="G19" t="n">
-        <v>4.835</v>
+        <v>4.689</v>
       </c>
       <c r="H19" t="n">
-        <v>4.79</v>
+        <v>4.618</v>
       </c>
       <c r="I19" t="n">
-        <v>4.79</v>
+        <v>4.618</v>
       </c>
       <c r="J19" t="n">
-        <v>4.799</v>
+        <v>4.637</v>
       </c>
       <c r="K19" t="n">
-        <v>4.815</v>
+        <v>4.653</v>
       </c>
       <c r="L19" t="n">
-        <v>4.833</v>
+        <v>4.667</v>
       </c>
       <c r="M19" t="n">
-        <v>4.835</v>
+        <v>4.689</v>
       </c>
     </row>
     <row r="20">
@@ -2481,39 +2481,39 @@
         <v>9040208</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.75</v>
+        <v>4.556</v>
       </c>
       <c r="F20" t="n">
-        <v>4.788</v>
+        <v>4.579</v>
       </c>
       <c r="G20" t="n">
-        <v>4.79</v>
+        <v>4.675</v>
       </c>
       <c r="H20" t="n">
-        <v>4.705</v>
+        <v>4.544</v>
       </c>
       <c r="I20" t="n">
-        <v>4.705</v>
+        <v>4.544</v>
       </c>
       <c r="J20" t="n">
-        <v>4.739</v>
+        <v>4.553</v>
       </c>
       <c r="K20" t="n">
-        <v>4.758</v>
+        <v>4.588</v>
       </c>
       <c r="L20" t="n">
-        <v>4.788</v>
+        <v>4.603</v>
       </c>
       <c r="M20" t="n">
-        <v>4.79</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="21">
@@ -2526,39 +2526,39 @@
         <v>9040208</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.676</v>
+        <v>4.508</v>
       </c>
       <c r="F21" t="n">
-        <v>4.72</v>
+        <v>4.541</v>
       </c>
       <c r="G21" t="n">
-        <v>4.77</v>
+        <v>4.704</v>
       </c>
       <c r="H21" t="n">
-        <v>4.57</v>
+        <v>4.585</v>
       </c>
       <c r="I21" t="n">
-        <v>4.57</v>
+        <v>4.508</v>
       </c>
       <c r="J21" t="n">
-        <v>4.65</v>
+        <v>4.533</v>
       </c>
       <c r="K21" t="n">
-        <v>4.684</v>
+        <v>4.585</v>
       </c>
       <c r="L21" t="n">
-        <v>4.732</v>
+        <v>4.615</v>
       </c>
       <c r="M21" t="n">
-        <v>4.77</v>
+        <v>4.704</v>
       </c>
     </row>
     <row r="22">
@@ -2571,39 +2571,39 @@
         <v>9040208</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.565</v>
+        <v>4.48</v>
       </c>
       <c r="F22" t="n">
-        <v>4.67</v>
+        <v>4.519</v>
       </c>
       <c r="G22" t="n">
-        <v>4.77</v>
+        <v>4.762</v>
       </c>
       <c r="H22" t="n">
-        <v>4.56</v>
+        <v>4.758</v>
       </c>
       <c r="I22" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="J22" t="n">
-        <v>4.564</v>
+        <v>4.509</v>
       </c>
       <c r="K22" t="n">
-        <v>4.641</v>
+        <v>4.63</v>
       </c>
       <c r="L22" t="n">
-        <v>4.695</v>
+        <v>4.759</v>
       </c>
       <c r="M22" t="n">
-        <v>4.77</v>
+        <v>4.762</v>
       </c>
     </row>
     <row r="23">
@@ -2616,39 +2616,39 @@
         <v>9053555</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="F23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="G23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="H23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="I23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="J23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="K23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="L23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="M23" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
     </row>
     <row r="24">
@@ -2661,39 +2661,39 @@
         <v>9053555</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="F24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="G24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="H24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="I24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="J24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="K24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="L24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="M24" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
     </row>
     <row r="25">
@@ -2706,39 +2706,39 @@
         <v>9053555</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="F25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="G25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="H25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="I25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="J25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="K25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="L25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="M25" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
     </row>
     <row r="26">
@@ -2751,39 +2751,39 @@
         <v>9053555</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="F26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="G26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="H26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="I26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="J26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="K26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="L26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="M26" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
     </row>
     <row r="27">
@@ -2796,39 +2796,39 @@
         <v>9053555</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12.09</v>
+        <v>11.983</v>
       </c>
       <c r="F27" t="n">
-        <v>12.089</v>
+        <v>11.984</v>
       </c>
       <c r="G27" t="n">
-        <v>12.09</v>
+        <v>11.982</v>
       </c>
       <c r="H27" t="n">
-        <v>12.089</v>
+        <v>11.982</v>
       </c>
       <c r="I27" t="n">
-        <v>12.089</v>
+        <v>11.982</v>
       </c>
       <c r="J27" t="n">
-        <v>12.089</v>
+        <v>11.982</v>
       </c>
       <c r="K27" t="n">
-        <v>12.089</v>
+        <v>11.983</v>
       </c>
       <c r="L27" t="n">
-        <v>12.09</v>
+        <v>11.984</v>
       </c>
       <c r="M27" t="n">
-        <v>12.09</v>
+        <v>11.984</v>
       </c>
     </row>
     <row r="28">
@@ -2841,39 +2841,39 @@
         <v>9053555</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>11.949</v>
+        <v>11.881</v>
       </c>
       <c r="F28" t="n">
-        <v>11.951</v>
+        <v>11.883</v>
       </c>
       <c r="G28" t="n">
-        <v>11.954</v>
+        <v>11.873</v>
       </c>
       <c r="H28" t="n">
-        <v>11.904</v>
+        <v>11.873</v>
       </c>
       <c r="I28" t="n">
-        <v>11.904</v>
+        <v>11.873</v>
       </c>
       <c r="J28" t="n">
-        <v>11.938</v>
+        <v>11.873</v>
       </c>
       <c r="K28" t="n">
-        <v>11.939</v>
+        <v>11.878</v>
       </c>
       <c r="L28" t="n">
-        <v>11.951</v>
+        <v>11.882</v>
       </c>
       <c r="M28" t="n">
-        <v>11.954</v>
+        <v>11.883</v>
       </c>
     </row>
     <row r="29">
@@ -2886,39 +2886,39 @@
         <v>9053555</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11.83</v>
+        <v>11.785</v>
       </c>
       <c r="F29" t="n">
-        <v>11.83</v>
+        <v>11.789</v>
       </c>
       <c r="G29" t="n">
-        <v>11.83</v>
+        <v>11.773</v>
       </c>
       <c r="H29" t="n">
-        <v>11.828</v>
+        <v>11.774</v>
       </c>
       <c r="I29" t="n">
-        <v>11.828</v>
+        <v>11.773</v>
       </c>
       <c r="J29" t="n">
-        <v>11.829</v>
+        <v>11.774</v>
       </c>
       <c r="K29" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="L29" t="n">
-        <v>11.83</v>
+        <v>11.786</v>
       </c>
       <c r="M29" t="n">
-        <v>11.83</v>
+        <v>11.789</v>
       </c>
     </row>
     <row r="30">
@@ -2931,39 +2931,39 @@
         <v>9038134</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112.08</v>
+        <v>109.219</v>
       </c>
       <c r="F30" t="n">
-        <v>112.08</v>
+        <v>109.3</v>
       </c>
       <c r="G30" t="n">
-        <v>112.08</v>
+        <v>109.216</v>
       </c>
       <c r="H30" t="n">
-        <v>112</v>
+        <v>109.212</v>
       </c>
       <c r="I30" t="n">
-        <v>112</v>
+        <v>109.212</v>
       </c>
       <c r="J30" t="n">
-        <v>112.06</v>
+        <v>109.215</v>
       </c>
       <c r="K30" t="n">
-        <v>112.06</v>
+        <v>109.237</v>
       </c>
       <c r="L30" t="n">
-        <v>112.08</v>
+        <v>109.239</v>
       </c>
       <c r="M30" t="n">
-        <v>112.08</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="31">
@@ -2976,39 +2976,39 @@
         <v>9038134</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>111.9</v>
+        <v>107.729</v>
       </c>
       <c r="F31" t="n">
-        <v>111.9</v>
+        <v>107.963</v>
       </c>
       <c r="G31" t="n">
-        <v>111.93</v>
+        <v>107.378</v>
       </c>
       <c r="H31" t="n">
-        <v>111.69</v>
+        <v>107.363</v>
       </c>
       <c r="I31" t="n">
-        <v>111.69</v>
+        <v>107.363</v>
       </c>
       <c r="J31" t="n">
-        <v>111.848</v>
+        <v>107.374</v>
       </c>
       <c r="K31" t="n">
-        <v>111.855</v>
+        <v>107.608</v>
       </c>
       <c r="L31" t="n">
-        <v>111.908</v>
+        <v>107.787</v>
       </c>
       <c r="M31" t="n">
-        <v>111.93</v>
+        <v>107.963</v>
       </c>
     </row>
     <row r="32">
@@ -3021,39 +3021,39 @@
         <v>9038134</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>111.659</v>
+        <v>107.067</v>
       </c>
       <c r="F32" t="n">
-        <v>111.73</v>
+        <v>107.34</v>
       </c>
       <c r="G32" t="n">
-        <v>111.75</v>
+        <v>105.635</v>
       </c>
       <c r="H32" t="n">
-        <v>111.44</v>
+        <v>105.575</v>
       </c>
       <c r="I32" t="n">
-        <v>111.44</v>
+        <v>105.575</v>
       </c>
       <c r="J32" t="n">
-        <v>111.604</v>
+        <v>105.62</v>
       </c>
       <c r="K32" t="n">
-        <v>111.645</v>
+        <v>106.404</v>
       </c>
       <c r="L32" t="n">
-        <v>111.735</v>
+        <v>107.135</v>
       </c>
       <c r="M32" t="n">
-        <v>111.75</v>
+        <v>107.34</v>
       </c>
     </row>
     <row r="33">
@@ -3066,39 +3066,39 @@
         <v>9038134</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>111.44</v>
+        <v>106.86</v>
       </c>
       <c r="F33" t="n">
-        <v>111.59</v>
+        <v>107.164</v>
       </c>
       <c r="G33" t="n">
-        <v>111.56</v>
+        <v>102.787</v>
       </c>
       <c r="H33" t="n">
-        <v>111.192</v>
+        <v>101.609</v>
       </c>
       <c r="I33" t="n">
-        <v>111.192</v>
+        <v>101.609</v>
       </c>
       <c r="J33" t="n">
-        <v>111.378</v>
+        <v>102.493</v>
       </c>
       <c r="K33" t="n">
-        <v>111.446</v>
+        <v>104.605</v>
       </c>
       <c r="L33" t="n">
-        <v>111.568</v>
+        <v>106.936</v>
       </c>
       <c r="M33" t="n">
-        <v>111.59</v>
+        <v>107.164</v>
       </c>
     </row>
     <row r="34">
@@ -3111,39 +3111,39 @@
         <v>9038134</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>111.2</v>
+        <v>106.345</v>
       </c>
       <c r="F34" t="n">
-        <v>111.44</v>
+        <v>106.891</v>
       </c>
       <c r="G34" t="n">
-        <v>111.324</v>
+        <v>101.778</v>
       </c>
       <c r="H34" t="n">
-        <v>110.81</v>
+        <v>98.149</v>
       </c>
       <c r="I34" t="n">
-        <v>110.81</v>
+        <v>98.149</v>
       </c>
       <c r="J34" t="n">
-        <v>111.102</v>
+        <v>100.871</v>
       </c>
       <c r="K34" t="n">
-        <v>111.193</v>
+        <v>103.291</v>
       </c>
       <c r="L34" t="n">
-        <v>111.353</v>
+        <v>106.481</v>
       </c>
       <c r="M34" t="n">
-        <v>111.44</v>
+        <v>106.891</v>
       </c>
     </row>
     <row r="35">
@@ -3156,39 +3156,39 @@
         <v>9038134</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>110.8</v>
+        <v>105.46</v>
       </c>
       <c r="F35" t="n">
-        <v>111.266</v>
+        <v>106.488</v>
       </c>
       <c r="G35" t="n">
-        <v>111.18</v>
+        <v>101.874</v>
       </c>
       <c r="H35" t="n">
-        <v>110.4</v>
+        <v>95.876</v>
       </c>
       <c r="I35" t="n">
-        <v>110.4</v>
+        <v>95.876</v>
       </c>
       <c r="J35" t="n">
-        <v>110.7</v>
+        <v>100.374</v>
       </c>
       <c r="K35" t="n">
-        <v>110.911</v>
+        <v>102.424</v>
       </c>
       <c r="L35" t="n">
-        <v>111.201</v>
+        <v>105.717</v>
       </c>
       <c r="M35" t="n">
-        <v>111.266</v>
+        <v>106.488</v>
       </c>
     </row>
     <row r="36">
@@ -3201,39 +3201,39 @@
         <v>9038134</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>110.35</v>
+        <v>103.182</v>
       </c>
       <c r="F36" t="n">
-        <v>111</v>
+        <v>106.238</v>
       </c>
       <c r="G36" t="n">
-        <v>110.947</v>
+        <v>102.234</v>
       </c>
       <c r="H36" t="n">
-        <v>110.021</v>
+        <v>102.503</v>
       </c>
       <c r="I36" t="n">
-        <v>110.021</v>
+        <v>102.234</v>
       </c>
       <c r="J36" t="n">
-        <v>110.268</v>
+        <v>102.436</v>
       </c>
       <c r="K36" t="n">
-        <v>110.579</v>
+        <v>103.54</v>
       </c>
       <c r="L36" t="n">
-        <v>110.96</v>
+        <v>103.946</v>
       </c>
       <c r="M36" t="n">
-        <v>111</v>
+        <v>106.238</v>
       </c>
     </row>
     <row r="37">
@@ -3246,39 +3246,39 @@
         <v>9044756</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.652</v>
+        <v>9.853999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="G37" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="H37" t="n">
-        <v>11.652</v>
+        <v>9.853999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>11.652</v>
+        <v>9.853999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>11.652</v>
+        <v>9.853999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="L37" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="M37" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
     </row>
     <row r="38">
@@ -3291,39 +3291,39 @@
         <v>9044756</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="F38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="G38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="H38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="I38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="J38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="K38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="L38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="M38" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
     </row>
     <row r="39">
@@ -3336,39 +3336,39 @@
         <v>9044756</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8.989000000000001</v>
+        <v>9.044</v>
       </c>
       <c r="F39" t="n">
-        <v>8.99</v>
+        <v>9.044</v>
       </c>
       <c r="G39" t="n">
-        <v>8.99</v>
+        <v>9.045</v>
       </c>
       <c r="H39" t="n">
-        <v>8.987</v>
+        <v>9.044</v>
       </c>
       <c r="I39" t="n">
-        <v>8.987</v>
+        <v>9.044</v>
       </c>
       <c r="J39" t="n">
-        <v>8.989000000000001</v>
+        <v>9.044</v>
       </c>
       <c r="K39" t="n">
-        <v>8.989000000000001</v>
+        <v>9.044</v>
       </c>
       <c r="L39" t="n">
-        <v>8.99</v>
+        <v>9.044</v>
       </c>
       <c r="M39" t="n">
-        <v>8.99</v>
+        <v>9.045</v>
       </c>
     </row>
     <row r="40">
@@ -3381,39 +3381,39 @@
         <v>9044756</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.699999999999999</v>
+        <v>8.943</v>
       </c>
       <c r="F40" t="n">
-        <v>8.699999999999999</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>8.699999999999999</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>8.699</v>
+        <v>8.943</v>
       </c>
       <c r="I40" t="n">
-        <v>8.699</v>
+        <v>8.943</v>
       </c>
       <c r="J40" t="n">
-        <v>8.699</v>
+        <v>8.943</v>
       </c>
       <c r="K40" t="n">
-        <v>8.699</v>
+        <v>8.943</v>
       </c>
       <c r="L40" t="n">
-        <v>8.699999999999999</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>8.699999999999999</v>
+        <v>8.944000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3426,39 +3426,39 @@
         <v>9044756</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8.477</v>
+        <v>8.871</v>
       </c>
       <c r="F41" t="n">
-        <v>8.477</v>
+        <v>8.872</v>
       </c>
       <c r="G41" t="n">
-        <v>8.477</v>
+        <v>8.872</v>
       </c>
       <c r="H41" t="n">
-        <v>8.476000000000001</v>
+        <v>8.871</v>
       </c>
       <c r="I41" t="n">
-        <v>8.476000000000001</v>
+        <v>8.871</v>
       </c>
       <c r="J41" t="n">
-        <v>8.477</v>
+        <v>8.871</v>
       </c>
       <c r="K41" t="n">
-        <v>8.477</v>
+        <v>8.871</v>
       </c>
       <c r="L41" t="n">
-        <v>8.477</v>
+        <v>8.872</v>
       </c>
       <c r="M41" t="n">
-        <v>8.477</v>
+        <v>8.872</v>
       </c>
     </row>
     <row r="42">
@@ -3471,39 +3471,39 @@
         <v>9044756</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="F42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="G42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="H42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="J42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="K42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="L42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="M42" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3516,39 +3516,39 @@
         <v>9044756</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="F43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="G43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="H43" t="n">
-        <v>8.397</v>
+        <v>8.776</v>
       </c>
       <c r="I43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="J43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="K43" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
       <c r="L43" t="n">
-        <v>8.397</v>
+        <v>8.776</v>
       </c>
       <c r="M43" t="n">
-        <v>8.397</v>
+        <v>8.776</v>
       </c>
     </row>
     <row r="44">
@@ -3561,39 +3561,39 @@
         <v>9042214</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3606,39 +3606,39 @@
         <v>9042214</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="F45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="G45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="H45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="I45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="J45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="K45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="L45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="M45" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="46">
@@ -3651,39 +3651,39 @@
         <v>9042214</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.827</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>8.827</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>8.827999999999999</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>8.827</v>
+        <v>8.641</v>
       </c>
       <c r="I46" t="n">
-        <v>8.827</v>
+        <v>8.641</v>
       </c>
       <c r="J46" t="n">
-        <v>8.827</v>
+        <v>8.641</v>
       </c>
       <c r="K46" t="n">
-        <v>8.827</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>8.827</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>8.827999999999999</v>
+        <v>8.641999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3696,39 +3696,39 @@
         <v>9042214</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.442</v>
       </c>
       <c r="F47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.443</v>
       </c>
       <c r="G47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.443</v>
       </c>
       <c r="H47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.441000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.441000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.442</v>
       </c>
       <c r="K47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.442</v>
       </c>
       <c r="L47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.443</v>
       </c>
       <c r="M47" t="n">
-        <v>8.744999999999999</v>
+        <v>8.443</v>
       </c>
     </row>
     <row r="48">
@@ -3741,39 +3741,39 @@
         <v>9042214</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.49</v>
+        <v>8.257999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>8.496</v>
+        <v>8.259</v>
       </c>
       <c r="G48" t="n">
-        <v>8.493</v>
+        <v>8.259</v>
       </c>
       <c r="H48" t="n">
-        <v>8.487</v>
+        <v>8.256</v>
       </c>
       <c r="I48" t="n">
-        <v>8.487</v>
+        <v>8.256</v>
       </c>
       <c r="J48" t="n">
-        <v>8.489000000000001</v>
+        <v>8.257</v>
       </c>
       <c r="K48" t="n">
-        <v>8.492000000000001</v>
+        <v>8.257999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>8.494</v>
+        <v>8.259</v>
       </c>
       <c r="M48" t="n">
-        <v>8.496</v>
+        <v>8.259</v>
       </c>
     </row>
     <row r="49">
@@ -3786,39 +3786,39 @@
         <v>9042214</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8.395</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>8.396000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>8.395</v>
+        <v>8.109</v>
       </c>
       <c r="H49" t="n">
-        <v>8.395</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>8.395</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>8.395</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>8.395</v>
+        <v>8.109</v>
       </c>
       <c r="L49" t="n">
-        <v>8.395</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>8.396000000000001</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3831,39 +3831,39 @@
         <v>9042214</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.035</v>
+        <v>7.99</v>
       </c>
       <c r="F50" t="n">
-        <v>8.036</v>
+        <v>7.991</v>
       </c>
       <c r="G50" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="H50" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="I50" t="n">
-        <v>8.035</v>
+        <v>7.99</v>
       </c>
       <c r="J50" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="K50" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="L50" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
       <c r="M50" t="n">
-        <v>8.036</v>
+        <v>7.991</v>
       </c>
     </row>
     <row r="51">
@@ -3876,39 +3876,39 @@
         <v>9043597</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="F51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="G51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="H51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="J51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="K51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="L51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="M51" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
     </row>
     <row r="52">
@@ -3921,39 +3921,39 @@
         <v>9043597</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="F52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="G52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="H52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="I52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="J52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="K52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="L52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="M52" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="53">
@@ -3966,39 +3966,39 @@
         <v>9043597</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="F53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="G53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="H53" t="n">
-        <v>5.543</v>
+        <v>5.391</v>
       </c>
       <c r="I53" t="n">
-        <v>5.543</v>
+        <v>5.391</v>
       </c>
       <c r="J53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="K53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="L53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="M53" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
     </row>
     <row r="54">
@@ -4011,39 +4011,39 @@
         <v>9043597</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="F54" t="n">
-        <v>5.379</v>
+        <v>5.304</v>
       </c>
       <c r="G54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="H54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="I54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="J54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="K54" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="L54" t="n">
-        <v>5.379</v>
+        <v>5.304</v>
       </c>
       <c r="M54" t="n">
-        <v>5.379</v>
+        <v>5.304</v>
       </c>
     </row>
     <row r="55">
@@ -4056,39 +4056,39 @@
         <v>9043597</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="F55" t="n">
-        <v>5.287</v>
+        <v>5.29</v>
       </c>
       <c r="G55" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="H55" t="n">
-        <v>5.285</v>
+        <v>5.289</v>
       </c>
       <c r="I55" t="n">
-        <v>5.285</v>
+        <v>5.289</v>
       </c>
       <c r="J55" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="K55" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="L55" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="M55" t="n">
-        <v>5.287</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="56">
@@ -4101,39 +4101,39 @@
         <v>9043597</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.28</v>
+        <v>5.319</v>
       </c>
       <c r="F56" t="n">
-        <v>5.281</v>
+        <v>5.32</v>
       </c>
       <c r="G56" t="n">
-        <v>5.28</v>
+        <v>5.319</v>
       </c>
       <c r="H56" t="n">
-        <v>5.28</v>
+        <v>5.318</v>
       </c>
       <c r="I56" t="n">
-        <v>5.28</v>
+        <v>5.318</v>
       </c>
       <c r="J56" t="n">
-        <v>5.28</v>
+        <v>5.319</v>
       </c>
       <c r="K56" t="n">
-        <v>5.28</v>
+        <v>5.319</v>
       </c>
       <c r="L56" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="M56" t="n">
-        <v>5.281</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="57">
@@ -4146,39 +4146,39 @@
         <v>9043597</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.298</v>
+        <v>5.339</v>
       </c>
       <c r="F57" t="n">
-        <v>5.313</v>
+        <v>5.342</v>
       </c>
       <c r="G57" t="n">
-        <v>5.299</v>
+        <v>5.341</v>
       </c>
       <c r="H57" t="n">
-        <v>5.296</v>
+        <v>5.334</v>
       </c>
       <c r="I57" t="n">
-        <v>5.296</v>
+        <v>5.334</v>
       </c>
       <c r="J57" t="n">
-        <v>5.298</v>
+        <v>5.338</v>
       </c>
       <c r="K57" t="n">
-        <v>5.302</v>
+        <v>5.339</v>
       </c>
       <c r="L57" t="n">
-        <v>5.302</v>
+        <v>5.342</v>
       </c>
       <c r="M57" t="n">
-        <v>5.313</v>
+        <v>5.342</v>
       </c>
     </row>
     <row r="58">
@@ -4191,39 +4191,39 @@
         <v>9040454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="F58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="G58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="H58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="I58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="J58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="K58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="L58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="M58" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
     </row>
     <row r="59">
@@ -4236,39 +4236,39 @@
         <v>9040454</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="F59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="G59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="H59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="I59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="J59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="K59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="L59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="M59" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
     </row>
     <row r="60">
@@ -4281,39 +4281,39 @@
         <v>9040454</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="F60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="G60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="H60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="I60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="J60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="K60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="L60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="M60" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
     </row>
     <row r="61">
@@ -4326,39 +4326,39 @@
         <v>9040454</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="F61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="G61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="H61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="I61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="J61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="K61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="L61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="M61" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="62">
@@ -4371,39 +4371,39 @@
         <v>9040454</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6.361</v>
+        <v>6.332</v>
       </c>
       <c r="F62" t="n">
-        <v>6.362</v>
+        <v>6.332</v>
       </c>
       <c r="G62" t="n">
-        <v>6.361</v>
+        <v>6.331</v>
       </c>
       <c r="H62" t="n">
-        <v>6.361</v>
+        <v>6.331</v>
       </c>
       <c r="I62" t="n">
-        <v>6.361</v>
+        <v>6.331</v>
       </c>
       <c r="J62" t="n">
-        <v>6.361</v>
+        <v>6.331</v>
       </c>
       <c r="K62" t="n">
-        <v>6.361</v>
+        <v>6.332</v>
       </c>
       <c r="L62" t="n">
-        <v>6.361</v>
+        <v>6.332</v>
       </c>
       <c r="M62" t="n">
-        <v>6.362</v>
+        <v>6.332</v>
       </c>
     </row>
     <row r="63">
@@ -4416,39 +4416,39 @@
         <v>9040454</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="F63" t="n">
-        <v>6.321</v>
+        <v>6.255</v>
       </c>
       <c r="G63" t="n">
-        <v>6.32</v>
+        <v>6.254</v>
       </c>
       <c r="H63" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="I63" t="n">
-        <v>6.32</v>
+        <v>6.254</v>
       </c>
       <c r="J63" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="K63" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="L63" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="M63" t="n">
-        <v>6.321</v>
+        <v>6.255</v>
       </c>
     </row>
     <row r="64">
@@ -4461,39 +4461,39 @@
         <v>9040454</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.232</v>
+        <v>6.143</v>
       </c>
       <c r="F64" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
       <c r="G64" t="n">
-        <v>6.233</v>
+        <v>6.142</v>
       </c>
       <c r="H64" t="n">
-        <v>6.232</v>
+        <v>6.143</v>
       </c>
       <c r="I64" t="n">
-        <v>6.232</v>
+        <v>6.142</v>
       </c>
       <c r="J64" t="n">
-        <v>6.232</v>
+        <v>6.143</v>
       </c>
       <c r="K64" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
       <c r="L64" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
       <c r="M64" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
     </row>
     <row r="65">
@@ -4506,39 +4506,39 @@
         <v>9037610</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.672</v>
+        <v>4.685</v>
       </c>
       <c r="F65" t="n">
-        <v>4.672</v>
+        <v>4.686</v>
       </c>
       <c r="G65" t="n">
-        <v>4.67</v>
+        <v>4.685</v>
       </c>
       <c r="H65" t="n">
-        <v>4.66</v>
+        <v>4.685</v>
       </c>
       <c r="I65" t="n">
-        <v>4.66</v>
+        <v>4.685</v>
       </c>
       <c r="J65" t="n">
-        <v>4.667</v>
+        <v>4.685</v>
       </c>
       <c r="K65" t="n">
-        <v>4.668</v>
+        <v>4.685</v>
       </c>
       <c r="L65" t="n">
-        <v>4.672</v>
+        <v>4.685</v>
       </c>
       <c r="M65" t="n">
-        <v>4.672</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="66">
@@ -4551,39 +4551,39 @@
         <v>9037610</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.818</v>
+        <v>4.76</v>
       </c>
       <c r="F66" t="n">
-        <v>4.823</v>
+        <v>4.77</v>
       </c>
       <c r="G66" t="n">
-        <v>4.816</v>
+        <v>4.746</v>
       </c>
       <c r="H66" t="n">
-        <v>4.802</v>
+        <v>4.745</v>
       </c>
       <c r="I66" t="n">
-        <v>4.802</v>
+        <v>4.745</v>
       </c>
       <c r="J66" t="n">
-        <v>4.812</v>
+        <v>4.746</v>
       </c>
       <c r="K66" t="n">
-        <v>4.815</v>
+        <v>4.755</v>
       </c>
       <c r="L66" t="n">
-        <v>4.819</v>
+        <v>4.763</v>
       </c>
       <c r="M66" t="n">
-        <v>4.823</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="67">
@@ -4596,39 +4596,39 @@
         <v>9037610</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.93</v>
+        <v>4.661</v>
       </c>
       <c r="F67" t="n">
-        <v>4.943</v>
+        <v>4.692</v>
       </c>
       <c r="G67" t="n">
-        <v>4.939</v>
+        <v>4.551</v>
       </c>
       <c r="H67" t="n">
-        <v>4.857</v>
+        <v>4.548</v>
       </c>
       <c r="I67" t="n">
-        <v>4.857</v>
+        <v>4.548</v>
       </c>
       <c r="J67" t="n">
-        <v>4.912</v>
+        <v>4.55</v>
       </c>
       <c r="K67" t="n">
-        <v>4.917</v>
+        <v>4.613</v>
       </c>
       <c r="L67" t="n">
-        <v>4.94</v>
+        <v>4.669</v>
       </c>
       <c r="M67" t="n">
-        <v>4.943</v>
+        <v>4.692</v>
       </c>
     </row>
     <row r="68">
@@ -4641,39 +4641,39 @@
         <v>9037610</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.907</v>
+        <v>4.482</v>
       </c>
       <c r="F68" t="n">
-        <v>4.969</v>
+        <v>4.561</v>
       </c>
       <c r="G68" t="n">
-        <v>4.955</v>
+        <v>4.19</v>
       </c>
       <c r="H68" t="n">
-        <v>4.761</v>
+        <v>4.164</v>
       </c>
       <c r="I68" t="n">
-        <v>4.761</v>
+        <v>4.164</v>
       </c>
       <c r="J68" t="n">
-        <v>4.871</v>
+        <v>4.183</v>
       </c>
       <c r="K68" t="n">
-        <v>4.898</v>
+        <v>4.349</v>
       </c>
       <c r="L68" t="n">
-        <v>4.959</v>
+        <v>4.502</v>
       </c>
       <c r="M68" t="n">
-        <v>4.969</v>
+        <v>4.561</v>
       </c>
     </row>
     <row r="69">
@@ -4686,39 +4686,39 @@
         <v>9037610</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.757</v>
+        <v>4.353</v>
       </c>
       <c r="F69" t="n">
-        <v>4.943</v>
+        <v>4.52</v>
       </c>
       <c r="G69" t="n">
-        <v>4.882</v>
+        <v>3.889</v>
       </c>
       <c r="H69" t="n">
-        <v>4.535</v>
+        <v>3.714</v>
       </c>
       <c r="I69" t="n">
-        <v>4.535</v>
+        <v>3.714</v>
       </c>
       <c r="J69" t="n">
-        <v>4.702</v>
+        <v>3.846</v>
       </c>
       <c r="K69" t="n">
-        <v>4.779</v>
+        <v>4.119</v>
       </c>
       <c r="L69" t="n">
-        <v>4.897</v>
+        <v>4.394</v>
       </c>
       <c r="M69" t="n">
-        <v>4.943</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="70">
@@ -4731,39 +4731,39 @@
         <v>9037610</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.475</v>
+        <v>4.341</v>
       </c>
       <c r="F70" t="n">
-        <v>4.861</v>
+        <v>4.633</v>
       </c>
       <c r="G70" t="n">
-        <v>4.629</v>
+        <v>4.047</v>
       </c>
       <c r="H70" t="n">
-        <v>4.258</v>
+        <v>3.462</v>
       </c>
       <c r="I70" t="n">
-        <v>4.258</v>
+        <v>3.462</v>
       </c>
       <c r="J70" t="n">
-        <v>4.421</v>
+        <v>3.901</v>
       </c>
       <c r="K70" t="n">
-        <v>4.556</v>
+        <v>4.121</v>
       </c>
       <c r="L70" t="n">
-        <v>4.687</v>
+        <v>4.414</v>
       </c>
       <c r="M70" t="n">
-        <v>4.861</v>
+        <v>4.633</v>
       </c>
     </row>
     <row r="71">
@@ -4776,39 +4776,39 @@
         <v>9037610</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.243</v>
+        <v>4.491</v>
       </c>
       <c r="F71" t="n">
-        <v>4.785</v>
+        <v>4.906</v>
       </c>
       <c r="G71" t="n">
-        <v>4.378</v>
+        <v>4.481</v>
       </c>
       <c r="H71" t="n">
-        <v>3.846</v>
+        <v>3.666</v>
       </c>
       <c r="I71" t="n">
-        <v>3.846</v>
+        <v>3.666</v>
       </c>
       <c r="J71" t="n">
-        <v>4.144</v>
+        <v>4.277</v>
       </c>
       <c r="K71" t="n">
-        <v>4.313</v>
+        <v>4.386</v>
       </c>
       <c r="L71" t="n">
-        <v>4.48</v>
+        <v>4.595</v>
       </c>
       <c r="M71" t="n">
-        <v>4.785</v>
+        <v>4.906</v>
       </c>
     </row>
     <row r="72">
@@ -4821,39 +4821,39 @@
         <v>9043425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="F72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="G72" t="n">
-        <v>6.75</v>
+        <v>6.774</v>
       </c>
       <c r="H72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="I72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="J72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="K72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="L72" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="M72" t="n">
-        <v>6.75</v>
+        <v>6.774</v>
       </c>
     </row>
     <row r="73">
@@ -4866,39 +4866,39 @@
         <v>9043425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="F73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="G73" t="n">
-        <v>6.72</v>
+        <v>6.741</v>
       </c>
       <c r="H73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="I73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="J73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="K73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="L73" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="M73" t="n">
-        <v>6.72</v>
+        <v>6.741</v>
       </c>
     </row>
     <row r="74">
@@ -4911,39 +4911,39 @@
         <v>9043425</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.69</v>
+        <v>6.707</v>
       </c>
       <c r="F74" t="n">
-        <v>6.69</v>
+        <v>6.707</v>
       </c>
       <c r="G74" t="n">
-        <v>6.691</v>
+        <v>6.707</v>
       </c>
       <c r="H74" t="n">
-        <v>6.69</v>
+        <v>6.706</v>
       </c>
       <c r="I74" t="n">
-        <v>6.69</v>
+        <v>6.706</v>
       </c>
       <c r="J74" t="n">
-        <v>6.69</v>
+        <v>6.707</v>
       </c>
       <c r="K74" t="n">
-        <v>6.69</v>
+        <v>6.707</v>
       </c>
       <c r="L74" t="n">
-        <v>6.691</v>
+        <v>6.707</v>
       </c>
       <c r="M74" t="n">
-        <v>6.691</v>
+        <v>6.707</v>
       </c>
     </row>
     <row r="75">
@@ -4956,39 +4956,39 @@
         <v>9043425</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6.64</v>
+        <v>6.672</v>
       </c>
       <c r="F75" t="n">
-        <v>6.64</v>
+        <v>6.672</v>
       </c>
       <c r="G75" t="n">
-        <v>6.64</v>
+        <v>6.672</v>
       </c>
       <c r="H75" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="I75" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="J75" t="n">
-        <v>6.64</v>
+        <v>6.671</v>
       </c>
       <c r="K75" t="n">
-        <v>6.64</v>
+        <v>6.671</v>
       </c>
       <c r="L75" t="n">
-        <v>6.64</v>
+        <v>6.672</v>
       </c>
       <c r="M75" t="n">
-        <v>6.64</v>
+        <v>6.672</v>
       </c>
     </row>
     <row r="76">
@@ -5001,39 +5001,39 @@
         <v>9043425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.61</v>
+        <v>6.634</v>
       </c>
       <c r="F76" t="n">
-        <v>6.61</v>
+        <v>6.635</v>
       </c>
       <c r="G76" t="n">
-        <v>6.609</v>
+        <v>6.635</v>
       </c>
       <c r="H76" t="n">
-        <v>6.609</v>
+        <v>6.633</v>
       </c>
       <c r="I76" t="n">
-        <v>6.609</v>
+        <v>6.633</v>
       </c>
       <c r="J76" t="n">
-        <v>6.609</v>
+        <v>6.634</v>
       </c>
       <c r="K76" t="n">
-        <v>6.61</v>
+        <v>6.634</v>
       </c>
       <c r="L76" t="n">
-        <v>6.61</v>
+        <v>6.635</v>
       </c>
       <c r="M76" t="n">
-        <v>6.61</v>
+        <v>6.635</v>
       </c>
     </row>
     <row r="77">
@@ -5046,39 +5046,39 @@
         <v>9043425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.55</v>
+        <v>6.597</v>
       </c>
       <c r="F77" t="n">
-        <v>6.55</v>
+        <v>6.598</v>
       </c>
       <c r="G77" t="n">
-        <v>6.549</v>
+        <v>6.598</v>
       </c>
       <c r="H77" t="n">
-        <v>6.55</v>
+        <v>6.597</v>
       </c>
       <c r="I77" t="n">
-        <v>6.549</v>
+        <v>6.597</v>
       </c>
       <c r="J77" t="n">
-        <v>6.55</v>
+        <v>6.597</v>
       </c>
       <c r="K77" t="n">
-        <v>6.55</v>
+        <v>6.597</v>
       </c>
       <c r="L77" t="n">
-        <v>6.55</v>
+        <v>6.598</v>
       </c>
       <c r="M77" t="n">
-        <v>6.55</v>
+        <v>6.598</v>
       </c>
     </row>
     <row r="78">
@@ -5091,39 +5091,39 @@
         <v>9043425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6.51</v>
+        <v>6.559</v>
       </c>
       <c r="F78" t="n">
-        <v>6.514</v>
+        <v>6.561</v>
       </c>
       <c r="G78" t="n">
-        <v>6.5</v>
+        <v>6.561</v>
       </c>
       <c r="H78" t="n">
-        <v>6.513</v>
+        <v>6.562</v>
       </c>
       <c r="I78" t="n">
-        <v>6.5</v>
+        <v>6.559</v>
       </c>
       <c r="J78" t="n">
-        <v>6.508</v>
+        <v>6.561</v>
       </c>
       <c r="K78" t="n">
-        <v>6.509</v>
+        <v>6.561</v>
       </c>
       <c r="L78" t="n">
-        <v>6.513</v>
+        <v>6.561</v>
       </c>
       <c r="M78" t="n">
-        <v>6.514</v>
+        <v>6.562</v>
       </c>
     </row>
     <row r="79">
@@ -5136,39 +5136,39 @@
         <v>9042153</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="F79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="G79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="H79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="I79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="J79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="K79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="L79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="M79" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
     </row>
     <row r="80">
@@ -5181,39 +5181,39 @@
         <v>9042153</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="F80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="G80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="H80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="I80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="J80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="K80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="L80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="M80" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
     </row>
     <row r="81">
@@ -5226,39 +5226,39 @@
         <v>9042153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="F81" t="n">
-        <v>10.868</v>
+        <v>10.666</v>
       </c>
       <c r="G81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="H81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="I81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="J81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="K81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="L81" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="M81" t="n">
-        <v>10.868</v>
+        <v>10.666</v>
       </c>
     </row>
     <row r="82">
@@ -5271,39 +5271,39 @@
         <v>9042153</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10.715</v>
+        <v>10.502</v>
       </c>
       <c r="F82" t="n">
-        <v>10.716</v>
+        <v>10.504</v>
       </c>
       <c r="G82" t="n">
-        <v>10.716</v>
+        <v>10.502</v>
       </c>
       <c r="H82" t="n">
-        <v>10.703</v>
+        <v>10.498</v>
       </c>
       <c r="I82" t="n">
-        <v>10.703</v>
+        <v>10.498</v>
       </c>
       <c r="J82" t="n">
-        <v>10.712</v>
+        <v>10.501</v>
       </c>
       <c r="K82" t="n">
-        <v>10.712</v>
+        <v>10.502</v>
       </c>
       <c r="L82" t="n">
-        <v>10.716</v>
+        <v>10.503</v>
       </c>
       <c r="M82" t="n">
-        <v>10.716</v>
+        <v>10.504</v>
       </c>
     </row>
     <row r="83">
@@ -5316,39 +5316,39 @@
         <v>9042153</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10.546</v>
+        <v>10.391</v>
       </c>
       <c r="F83" t="n">
-        <v>10.58</v>
+        <v>10.396</v>
       </c>
       <c r="G83" t="n">
-        <v>10.576</v>
+        <v>10.395</v>
       </c>
       <c r="H83" t="n">
-        <v>10.525</v>
+        <v>10.384</v>
       </c>
       <c r="I83" t="n">
-        <v>10.525</v>
+        <v>10.384</v>
       </c>
       <c r="J83" t="n">
-        <v>10.541</v>
+        <v>10.39</v>
       </c>
       <c r="K83" t="n">
-        <v>10.557</v>
+        <v>10.392</v>
       </c>
       <c r="L83" t="n">
-        <v>10.577</v>
+        <v>10.395</v>
       </c>
       <c r="M83" t="n">
-        <v>10.58</v>
+        <v>10.396</v>
       </c>
     </row>
     <row r="84">
@@ -5361,39 +5361,39 @@
         <v>9042153</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>10.445</v>
+        <v>10.306</v>
       </c>
       <c r="F84" t="n">
-        <v>10.453</v>
+        <v>10.316</v>
       </c>
       <c r="G84" t="n">
-        <v>10.453</v>
+        <v>10.326</v>
       </c>
       <c r="H84" t="n">
-        <v>10.4</v>
+        <v>10.291</v>
       </c>
       <c r="I84" t="n">
-        <v>10.4</v>
+        <v>10.291</v>
       </c>
       <c r="J84" t="n">
-        <v>10.433</v>
+        <v>10.302</v>
       </c>
       <c r="K84" t="n">
-        <v>10.438</v>
+        <v>10.31</v>
       </c>
       <c r="L84" t="n">
-        <v>10.453</v>
+        <v>10.318</v>
       </c>
       <c r="M84" t="n">
-        <v>10.453</v>
+        <v>10.326</v>
       </c>
     </row>
     <row r="85">
@@ -5406,39 +5406,39 @@
         <v>9042153</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10.353</v>
+        <v>10.194</v>
       </c>
       <c r="F85" t="n">
-        <v>10.383</v>
+        <v>10.22</v>
       </c>
       <c r="G85" t="n">
-        <v>10.383</v>
+        <v>10.281</v>
       </c>
       <c r="H85" t="n">
-        <v>10.271</v>
+        <v>10.185</v>
       </c>
       <c r="I85" t="n">
-        <v>10.271</v>
+        <v>10.185</v>
       </c>
       <c r="J85" t="n">
-        <v>10.333</v>
+        <v>10.192</v>
       </c>
       <c r="K85" t="n">
-        <v>10.348</v>
+        <v>10.22</v>
       </c>
       <c r="L85" t="n">
-        <v>10.383</v>
+        <v>10.235</v>
       </c>
       <c r="M85" t="n">
-        <v>10.383</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="86">
@@ -5451,39 +5451,39 @@
         <v>9040439</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="F86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="G86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="H86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="I86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="J86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="K86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="L86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="M86" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
     </row>
     <row r="87">
@@ -5496,39 +5496,39 @@
         <v>9040439</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="F87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="G87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="H87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="I87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="J87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="K87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="L87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="M87" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
     </row>
     <row r="88">
@@ -5541,39 +5541,39 @@
         <v>9040439</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="F88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="G88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="H88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="I88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="J88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="K88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="L88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="M88" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
     </row>
     <row r="89">
@@ -5586,39 +5586,39 @@
         <v>9040439</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="F89" t="n">
-        <v>7.205</v>
+        <v>7.099</v>
       </c>
       <c r="G89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="H89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="I89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="J89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="K89" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="L89" t="n">
-        <v>7.205</v>
+        <v>7.099</v>
       </c>
       <c r="M89" t="n">
-        <v>7.205</v>
+        <v>7.099</v>
       </c>
     </row>
     <row r="90">
@@ -5631,39 +5631,39 @@
         <v>9040439</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="F90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="G90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="H90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="I90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="J90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="K90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="L90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="M90" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
     </row>
     <row r="91">
@@ -5676,39 +5676,39 @@
         <v>9040439</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="F91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="G91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="H91" t="n">
-        <v>7.056</v>
+        <v>6.81</v>
       </c>
       <c r="I91" t="n">
-        <v>7.056</v>
+        <v>6.81</v>
       </c>
       <c r="J91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="K91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="L91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="M91" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="92">
@@ -5721,39 +5721,39 @@
         <v>9040439</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="F92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="H92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="I92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="J92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="K92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="L92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
       <c r="M92" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="93">
@@ -5766,39 +5766,39 @@
         <v>9032282</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="F93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="G93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="H93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="I93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="J93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="K93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="L93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="M93" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
     </row>
     <row r="94">
@@ -5811,39 +5811,39 @@
         <v>9032282</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="F94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="G94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="H94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="I94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="J94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="K94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="L94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="M94" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
     </row>
     <row r="95">
@@ -5856,39 +5856,39 @@
         <v>9032282</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.156</v>
+        <v>7.177</v>
       </c>
       <c r="F95" t="n">
-        <v>7.157</v>
+        <v>7.177</v>
       </c>
       <c r="G95" t="n">
-        <v>7.155</v>
+        <v>7.177</v>
       </c>
       <c r="H95" t="n">
-        <v>7.155</v>
+        <v>7.177</v>
       </c>
       <c r="I95" t="n">
-        <v>7.155</v>
+        <v>7.177</v>
       </c>
       <c r="J95" t="n">
-        <v>7.155</v>
+        <v>7.177</v>
       </c>
       <c r="K95" t="n">
-        <v>7.156</v>
+        <v>7.177</v>
       </c>
       <c r="L95" t="n">
-        <v>7.156</v>
+        <v>7.177</v>
       </c>
       <c r="M95" t="n">
-        <v>7.157</v>
+        <v>7.177</v>
       </c>
     </row>
     <row r="96">
@@ -5901,39 +5901,39 @@
         <v>9032282</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7.113</v>
+        <v>7.128</v>
       </c>
       <c r="F96" t="n">
-        <v>7.114</v>
+        <v>7.128</v>
       </c>
       <c r="G96" t="n">
-        <v>7.113</v>
+        <v>7.128</v>
       </c>
       <c r="H96" t="n">
-        <v>7.112</v>
+        <v>7.127</v>
       </c>
       <c r="I96" t="n">
-        <v>7.112</v>
+        <v>7.127</v>
       </c>
       <c r="J96" t="n">
-        <v>7.112</v>
+        <v>7.127</v>
       </c>
       <c r="K96" t="n">
-        <v>7.113</v>
+        <v>7.128</v>
       </c>
       <c r="L96" t="n">
-        <v>7.113</v>
+        <v>7.128</v>
       </c>
       <c r="M96" t="n">
-        <v>7.114</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="97">
@@ -5946,39 +5946,39 @@
         <v>9032282</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="F97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="G97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="H97" t="n">
-        <v>7.04</v>
+        <v>7.067</v>
       </c>
       <c r="I97" t="n">
-        <v>7.04</v>
+        <v>7.067</v>
       </c>
       <c r="J97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="K97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="L97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="M97" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="98">
@@ -5991,39 +5991,39 @@
         <v>9032282</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6.968</v>
+        <v>7.007</v>
       </c>
       <c r="F98" t="n">
-        <v>6.968</v>
+        <v>7.007</v>
       </c>
       <c r="G98" t="n">
-        <v>6.968</v>
+        <v>7.007</v>
       </c>
       <c r="H98" t="n">
-        <v>6.967</v>
+        <v>7.004</v>
       </c>
       <c r="I98" t="n">
-        <v>6.967</v>
+        <v>7.004</v>
       </c>
       <c r="J98" t="n">
-        <v>6.968</v>
+        <v>7.006</v>
       </c>
       <c r="K98" t="n">
-        <v>6.968</v>
+        <v>7.006</v>
       </c>
       <c r="L98" t="n">
-        <v>6.968</v>
+        <v>7.007</v>
       </c>
       <c r="M98" t="n">
-        <v>6.968</v>
+        <v>7.007</v>
       </c>
     </row>
     <row r="99">
@@ -6036,39 +6036,39 @@
         <v>9032282</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6.899</v>
+        <v>6.95</v>
       </c>
       <c r="F99" t="n">
-        <v>6.9</v>
+        <v>6.951</v>
       </c>
       <c r="G99" t="n">
-        <v>6.898</v>
+        <v>6.949</v>
       </c>
       <c r="H99" t="n">
-        <v>6.898</v>
+        <v>6.946</v>
       </c>
       <c r="I99" t="n">
-        <v>6.898</v>
+        <v>6.946</v>
       </c>
       <c r="J99" t="n">
-        <v>6.898</v>
+        <v>6.948</v>
       </c>
       <c r="K99" t="n">
-        <v>6.899</v>
+        <v>6.949</v>
       </c>
       <c r="L99" t="n">
-        <v>6.899</v>
+        <v>6.95</v>
       </c>
       <c r="M99" t="n">
-        <v>6.9</v>
+        <v>6.951</v>
       </c>
     </row>
     <row r="100">
@@ -6081,39 +6081,39 @@
         <v>9037738</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5.726</v>
+        <v>5.728</v>
       </c>
       <c r="F100" t="n">
-        <v>5.728</v>
+        <v>5.739</v>
       </c>
       <c r="G100" t="n">
-        <v>5.726</v>
+        <v>5.717</v>
       </c>
       <c r="H100" t="n">
-        <v>5.687</v>
+        <v>5.715</v>
       </c>
       <c r="I100" t="n">
-        <v>5.687</v>
+        <v>5.715</v>
       </c>
       <c r="J100" t="n">
         <v>5.716</v>
       </c>
       <c r="K100" t="n">
-        <v>5.717</v>
+        <v>5.725</v>
       </c>
       <c r="L100" t="n">
-        <v>5.726</v>
+        <v>5.731</v>
       </c>
       <c r="M100" t="n">
-        <v>5.728</v>
+        <v>5.739</v>
       </c>
     </row>
     <row r="101">
@@ -6126,39 +6126,39 @@
         <v>9037738</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5.935</v>
+        <v>5.688</v>
       </c>
       <c r="F101" t="n">
-        <v>5.973</v>
+        <v>5.719</v>
       </c>
       <c r="G101" t="n">
-        <v>5.974</v>
+        <v>5.563</v>
       </c>
       <c r="H101" t="n">
-        <v>5.803</v>
+        <v>5.562</v>
       </c>
       <c r="I101" t="n">
-        <v>5.803</v>
+        <v>5.562</v>
       </c>
       <c r="J101" t="n">
-        <v>5.902</v>
+        <v>5.563</v>
       </c>
       <c r="K101" t="n">
-        <v>5.921</v>
+        <v>5.633</v>
       </c>
       <c r="L101" t="n">
-        <v>5.974</v>
+        <v>5.696</v>
       </c>
       <c r="M101" t="n">
-        <v>5.974</v>
+        <v>5.719</v>
       </c>
     </row>
     <row r="102">
@@ -6171,39 +6171,39 @@
         <v>9037738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5.962</v>
+        <v>5.531</v>
       </c>
       <c r="F102" t="n">
-        <v>6.037</v>
+        <v>5.599</v>
       </c>
       <c r="G102" t="n">
-        <v>6.036</v>
+        <v>5.19</v>
       </c>
       <c r="H102" t="n">
-        <v>5.776</v>
+        <v>5.175</v>
       </c>
       <c r="I102" t="n">
-        <v>5.776</v>
+        <v>5.175</v>
       </c>
       <c r="J102" t="n">
-        <v>5.915</v>
+        <v>5.186</v>
       </c>
       <c r="K102" t="n">
-        <v>5.953</v>
+        <v>5.374</v>
       </c>
       <c r="L102" t="n">
-        <v>6.036</v>
+        <v>5.548</v>
       </c>
       <c r="M102" t="n">
-        <v>6.037</v>
+        <v>5.599</v>
       </c>
     </row>
     <row r="103">
@@ -6216,39 +6216,39 @@
         <v>9037738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5.788</v>
+        <v>5.451</v>
       </c>
       <c r="F103" t="n">
-        <v>6.026</v>
+        <v>5.593</v>
       </c>
       <c r="G103" t="n">
-        <v>5.946</v>
+        <v>4.94</v>
       </c>
       <c r="H103" t="n">
-        <v>5.519</v>
+        <v>4.761</v>
       </c>
       <c r="I103" t="n">
-        <v>5.519</v>
+        <v>4.761</v>
       </c>
       <c r="J103" t="n">
-        <v>5.721</v>
+        <v>4.895</v>
       </c>
       <c r="K103" t="n">
-        <v>5.82</v>
+        <v>5.186</v>
       </c>
       <c r="L103" t="n">
-        <v>5.966</v>
+        <v>5.487</v>
       </c>
       <c r="M103" t="n">
-        <v>6.026</v>
+        <v>5.593</v>
       </c>
     </row>
     <row r="104">
@@ -6261,39 +6261,39 @@
         <v>9037738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5.555</v>
+        <v>5.482</v>
       </c>
       <c r="F104" t="n">
-        <v>5.936</v>
+        <v>5.752</v>
       </c>
       <c r="G104" t="n">
-        <v>5.728</v>
+        <v>5.211</v>
       </c>
       <c r="H104" t="n">
-        <v>5.113</v>
+        <v>4.554</v>
       </c>
       <c r="I104" t="n">
-        <v>5.113</v>
+        <v>4.554</v>
       </c>
       <c r="J104" t="n">
-        <v>5.444</v>
+        <v>5.046</v>
       </c>
       <c r="K104" t="n">
-        <v>5.583</v>
+        <v>5.25</v>
       </c>
       <c r="L104" t="n">
-        <v>5.78</v>
+        <v>5.549</v>
       </c>
       <c r="M104" t="n">
-        <v>5.936</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="105">
@@ -6306,39 +6306,39 @@
         <v>9037738</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5.357</v>
+        <v>5.662</v>
       </c>
       <c r="F105" t="n">
-        <v>5.859</v>
+        <v>6.025</v>
       </c>
       <c r="G105" t="n">
-        <v>5.454</v>
+        <v>5.622</v>
       </c>
       <c r="H105" t="n">
-        <v>4.807</v>
+        <v>4.882</v>
       </c>
       <c r="I105" t="n">
-        <v>4.807</v>
+        <v>4.882</v>
       </c>
       <c r="J105" t="n">
-        <v>5.22</v>
+        <v>5.437</v>
       </c>
       <c r="K105" t="n">
-        <v>5.369</v>
+        <v>5.548</v>
       </c>
       <c r="L105" t="n">
-        <v>5.556</v>
+        <v>5.753</v>
       </c>
       <c r="M105" t="n">
-        <v>5.859</v>
+        <v>6.025</v>
       </c>
     </row>
     <row r="106">
@@ -6351,39 +6351,39 @@
         <v>9037738</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.171</v>
+        <v>5.969</v>
       </c>
       <c r="F106" t="n">
-        <v>5.795</v>
+        <v>6.248</v>
       </c>
       <c r="G106" t="n">
-        <v>5.265</v>
+        <v>5.837</v>
       </c>
       <c r="H106" t="n">
-        <v>4.642</v>
+        <v>5.769</v>
       </c>
       <c r="I106" t="n">
-        <v>4.642</v>
+        <v>5.769</v>
       </c>
       <c r="J106" t="n">
-        <v>5.039</v>
+        <v>5.82</v>
       </c>
       <c r="K106" t="n">
-        <v>5.218</v>
+        <v>5.956</v>
       </c>
       <c r="L106" t="n">
-        <v>5.397</v>
+        <v>6.039</v>
       </c>
       <c r="M106" t="n">
-        <v>5.795</v>
+        <v>6.248</v>
       </c>
     </row>
     <row r="107">
@@ -6396,39 +6396,39 @@
         <v>9039635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="F107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="G107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="H107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="I107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="J107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="K107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="L107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="M107" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
     </row>
     <row r="108">
@@ -6441,39 +6441,39 @@
         <v>9039635</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="F108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="G108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="H108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="I108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="J108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="K108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="L108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="M108" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
     </row>
     <row r="109">
@@ -6486,39 +6486,39 @@
         <v>9039635</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5.196</v>
+        <v>5.132</v>
       </c>
       <c r="F109" t="n">
-        <v>5.197</v>
+        <v>5.132</v>
       </c>
       <c r="G109" t="n">
-        <v>5.194</v>
+        <v>5.132</v>
       </c>
       <c r="H109" t="n">
-        <v>5.193</v>
+        <v>5.132</v>
       </c>
       <c r="I109" t="n">
-        <v>5.193</v>
+        <v>5.132</v>
       </c>
       <c r="J109" t="n">
-        <v>5.194</v>
+        <v>5.132</v>
       </c>
       <c r="K109" t="n">
-        <v>5.195</v>
+        <v>5.132</v>
       </c>
       <c r="L109" t="n">
-        <v>5.196</v>
+        <v>5.132</v>
       </c>
       <c r="M109" t="n">
-        <v>5.197</v>
+        <v>5.132</v>
       </c>
     </row>
     <row r="110">
@@ -6531,39 +6531,39 @@
         <v>9039635</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5.081</v>
+        <v>4.959</v>
       </c>
       <c r="F110" t="n">
-        <v>5.081</v>
+        <v>4.962</v>
       </c>
       <c r="G110" t="n">
-        <v>5.073</v>
+        <v>4.959</v>
       </c>
       <c r="H110" t="n">
-        <v>5.072</v>
+        <v>4.958</v>
       </c>
       <c r="I110" t="n">
-        <v>5.072</v>
+        <v>4.958</v>
       </c>
       <c r="J110" t="n">
-        <v>5.073</v>
+        <v>4.958</v>
       </c>
       <c r="K110" t="n">
-        <v>5.077</v>
+        <v>4.96</v>
       </c>
       <c r="L110" t="n">
-        <v>5.081</v>
+        <v>4.96</v>
       </c>
       <c r="M110" t="n">
-        <v>5.081</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="111">
@@ -6576,39 +6576,39 @@
         <v>9039635</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.93</v>
+        <v>4.821</v>
       </c>
       <c r="F111" t="n">
-        <v>4.93</v>
+        <v>4.821</v>
       </c>
       <c r="G111" t="n">
-        <v>4.93</v>
+        <v>4.812</v>
       </c>
       <c r="H111" t="n">
-        <v>4.929</v>
+        <v>4.811</v>
       </c>
       <c r="I111" t="n">
-        <v>4.929</v>
+        <v>4.811</v>
       </c>
       <c r="J111" t="n">
-        <v>4.93</v>
+        <v>4.812</v>
       </c>
       <c r="K111" t="n">
-        <v>4.93</v>
+        <v>4.816</v>
       </c>
       <c r="L111" t="n">
-        <v>4.93</v>
+        <v>4.821</v>
       </c>
       <c r="M111" t="n">
-        <v>4.93</v>
+        <v>4.821</v>
       </c>
     </row>
     <row r="112">
@@ -6621,39 +6621,39 @@
         <v>9039635</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4.78</v>
+        <v>4.743</v>
       </c>
       <c r="F112" t="n">
-        <v>4.78</v>
+        <v>4.729</v>
       </c>
       <c r="G112" t="n">
-        <v>4.761</v>
+        <v>4.723</v>
       </c>
       <c r="H112" t="n">
-        <v>4.761</v>
+        <v>4.711</v>
       </c>
       <c r="I112" t="n">
-        <v>4.761</v>
+        <v>4.711</v>
       </c>
       <c r="J112" t="n">
-        <v>4.761</v>
+        <v>4.72</v>
       </c>
       <c r="K112" t="n">
-        <v>4.77</v>
+        <v>4.726</v>
       </c>
       <c r="L112" t="n">
-        <v>4.78</v>
+        <v>4.732</v>
       </c>
       <c r="M112" t="n">
-        <v>4.78</v>
+        <v>4.743</v>
       </c>
     </row>
     <row r="113">
@@ -6666,39 +6666,39 @@
         <v>9039635</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4.633</v>
+        <v>4.71</v>
       </c>
       <c r="F113" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="G113" t="n">
-        <v>4.622</v>
+        <v>4.673</v>
       </c>
       <c r="H113" t="n">
-        <v>4.622</v>
+        <v>4.672</v>
       </c>
       <c r="I113" t="n">
-        <v>4.622</v>
+        <v>4.672</v>
       </c>
       <c r="J113" t="n">
-        <v>4.622</v>
+        <v>4.673</v>
       </c>
       <c r="K113" t="n">
-        <v>4.629</v>
+        <v>4.686</v>
       </c>
       <c r="L113" t="n">
-        <v>4.634</v>
+        <v>4.695</v>
       </c>
       <c r="M113" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="114">
@@ -6711,39 +6711,39 @@
         <v>9038269</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="F114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="G114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="H114" t="n">
-        <v>3.317</v>
+        <v>3.431</v>
       </c>
       <c r="I114" t="n">
-        <v>3.317</v>
+        <v>3.431</v>
       </c>
       <c r="J114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="K114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="L114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="M114" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
     </row>
     <row r="115">
@@ -6756,39 +6756,39 @@
         <v>9038269</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3.462</v>
+        <v>3.592</v>
       </c>
       <c r="F115" t="n">
-        <v>3.462</v>
+        <v>3.593</v>
       </c>
       <c r="G115" t="n">
-        <v>3.462</v>
+        <v>3.592</v>
       </c>
       <c r="H115" t="n">
-        <v>3.462</v>
+        <v>3.591</v>
       </c>
       <c r="I115" t="n">
-        <v>3.462</v>
+        <v>3.591</v>
       </c>
       <c r="J115" t="n">
-        <v>3.462</v>
+        <v>3.591</v>
       </c>
       <c r="K115" t="n">
-        <v>3.462</v>
+        <v>3.592</v>
       </c>
       <c r="L115" t="n">
-        <v>3.462</v>
+        <v>3.592</v>
       </c>
       <c r="M115" t="n">
-        <v>3.462</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="116">
@@ -6801,39 +6801,39 @@
         <v>9038269</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="F116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="G116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="H116" t="n">
-        <v>3.674</v>
+        <v>3.659</v>
       </c>
       <c r="I116" t="n">
-        <v>3.674</v>
+        <v>3.659</v>
       </c>
       <c r="J116" t="n">
-        <v>3.675</v>
+        <v>3.659</v>
       </c>
       <c r="K116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="L116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="M116" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
     </row>
     <row r="117">
@@ -6846,39 +6846,39 @@
         <v>9038269</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="F117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="G117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="H117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="I117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="J117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="K117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="L117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="M117" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
     </row>
     <row r="118">
@@ -6891,39 +6891,39 @@
         <v>9038269</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3.759</v>
+        <v>3.72</v>
       </c>
       <c r="F118" t="n">
-        <v>3.76</v>
+        <v>3.721</v>
       </c>
       <c r="G118" t="n">
-        <v>3.759</v>
+        <v>3.717</v>
       </c>
       <c r="H118" t="n">
-        <v>3.758</v>
+        <v>3.716</v>
       </c>
       <c r="I118" t="n">
-        <v>3.758</v>
+        <v>3.716</v>
       </c>
       <c r="J118" t="n">
-        <v>3.759</v>
+        <v>3.717</v>
       </c>
       <c r="K118" t="n">
-        <v>3.759</v>
+        <v>3.718</v>
       </c>
       <c r="L118" t="n">
-        <v>3.759</v>
+        <v>3.72</v>
       </c>
       <c r="M118" t="n">
-        <v>3.76</v>
+        <v>3.721</v>
       </c>
     </row>
     <row r="119">
@@ -6936,39 +6936,39 @@
         <v>9038269</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3.763</v>
+        <v>3.675</v>
       </c>
       <c r="F119" t="n">
-        <v>3.764</v>
+        <v>3.676</v>
       </c>
       <c r="G119" t="n">
-        <v>3.763</v>
+        <v>3.673</v>
       </c>
       <c r="H119" t="n">
-        <v>3.763</v>
+        <v>3.671</v>
       </c>
       <c r="I119" t="n">
-        <v>3.763</v>
+        <v>3.671</v>
       </c>
       <c r="J119" t="n">
-        <v>3.763</v>
+        <v>3.673</v>
       </c>
       <c r="K119" t="n">
-        <v>3.763</v>
+        <v>3.674</v>
       </c>
       <c r="L119" t="n">
-        <v>3.763</v>
+        <v>3.675</v>
       </c>
       <c r="M119" t="n">
-        <v>3.764</v>
+        <v>3.676</v>
       </c>
     </row>
     <row r="120">
@@ -6981,39 +6981,39 @@
         <v>9038269</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3.742</v>
+        <v>3.618</v>
       </c>
       <c r="F120" t="n">
-        <v>3.743</v>
+        <v>3.62</v>
       </c>
       <c r="G120" t="n">
-        <v>3.742</v>
+        <v>3.615</v>
       </c>
       <c r="H120" t="n">
-        <v>3.741</v>
+        <v>3.614</v>
       </c>
       <c r="I120" t="n">
-        <v>3.741</v>
+        <v>3.614</v>
       </c>
       <c r="J120" t="n">
-        <v>3.742</v>
+        <v>3.615</v>
       </c>
       <c r="K120" t="n">
-        <v>3.742</v>
+        <v>3.617</v>
       </c>
       <c r="L120" t="n">
-        <v>3.742</v>
+        <v>3.619</v>
       </c>
       <c r="M120" t="n">
-        <v>3.743</v>
+        <v>3.62</v>
       </c>
     </row>
   </sheetData>
@@ -7043,37 +7043,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -7087,25 +7087,25 @@
         <v>9043370</v>
       </c>
       <c r="C2" t="n">
-        <v>8.122999999999999</v>
+        <v>8.234</v>
       </c>
       <c r="D2" t="n">
-        <v>8.112</v>
+        <v>8.211</v>
       </c>
       <c r="E2" t="n">
-        <v>8.085000000000001</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>8.048</v>
+        <v>8.166</v>
       </c>
       <c r="G2" t="n">
-        <v>8.029</v>
+        <v>8.147</v>
       </c>
       <c r="H2" t="n">
-        <v>8.016999999999999</v>
+        <v>8.128</v>
       </c>
       <c r="I2" t="n">
-        <v>8.010999999999999</v>
+        <v>8.113</v>
       </c>
     </row>
     <row r="3">
@@ -7118,25 +7118,25 @@
         <v>9036028</v>
       </c>
       <c r="C3" t="n">
-        <v>6.136</v>
+        <v>6.144</v>
       </c>
       <c r="D3" t="n">
-        <v>6.16</v>
+        <v>6.182</v>
       </c>
       <c r="E3" t="n">
-        <v>6.183</v>
+        <v>6.222</v>
       </c>
       <c r="F3" t="n">
-        <v>6.218</v>
+        <v>6.238</v>
       </c>
       <c r="G3" t="n">
-        <v>6.22</v>
+        <v>6.226</v>
       </c>
       <c r="H3" t="n">
-        <v>6.22</v>
+        <v>6.193</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2</v>
+        <v>6.128</v>
       </c>
     </row>
     <row r="4">
@@ -7149,25 +7149,25 @@
         <v>9040208</v>
       </c>
       <c r="C4" t="n">
-        <v>5.147</v>
+        <v>4.978</v>
       </c>
       <c r="D4" t="n">
-        <v>4.982</v>
+        <v>4.836</v>
       </c>
       <c r="E4" t="n">
-        <v>4.881</v>
+        <v>4.736</v>
       </c>
       <c r="F4" t="n">
-        <v>4.815</v>
+        <v>4.653</v>
       </c>
       <c r="G4" t="n">
-        <v>4.758</v>
+        <v>4.588</v>
       </c>
       <c r="H4" t="n">
-        <v>4.684</v>
+        <v>4.585</v>
       </c>
       <c r="I4" t="n">
-        <v>4.641</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="5">
@@ -7180,25 +7180,25 @@
         <v>9053555</v>
       </c>
       <c r="C5" t="n">
-        <v>12.283</v>
+        <v>12.248</v>
       </c>
       <c r="D5" t="n">
-        <v>12.23</v>
+        <v>12.193</v>
       </c>
       <c r="E5" t="n">
-        <v>12.195</v>
+        <v>12.125</v>
       </c>
       <c r="F5" t="n">
-        <v>12.137</v>
+        <v>12.052</v>
       </c>
       <c r="G5" t="n">
-        <v>12.089</v>
+        <v>11.983</v>
       </c>
       <c r="H5" t="n">
-        <v>11.939</v>
+        <v>11.878</v>
       </c>
       <c r="I5" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="6">
@@ -7211,25 +7211,25 @@
         <v>9038134</v>
       </c>
       <c r="C6" t="n">
-        <v>112.06</v>
+        <v>109.237</v>
       </c>
       <c r="D6" t="n">
-        <v>111.855</v>
+        <v>107.608</v>
       </c>
       <c r="E6" t="n">
-        <v>111.645</v>
+        <v>106.404</v>
       </c>
       <c r="F6" t="n">
-        <v>111.446</v>
+        <v>104.605</v>
       </c>
       <c r="G6" t="n">
-        <v>111.193</v>
+        <v>103.291</v>
       </c>
       <c r="H6" t="n">
-        <v>110.911</v>
+        <v>102.424</v>
       </c>
       <c r="I6" t="n">
-        <v>110.579</v>
+        <v>103.54</v>
       </c>
     </row>
     <row r="7">
@@ -7242,25 +7242,25 @@
         <v>9044756</v>
       </c>
       <c r="C7" t="n">
-        <v>11.652</v>
+        <v>9.855</v>
       </c>
       <c r="D7" t="n">
-        <v>9.335000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="E7" t="n">
-        <v>8.989000000000001</v>
+        <v>9.044</v>
       </c>
       <c r="F7" t="n">
-        <v>8.699</v>
+        <v>8.943</v>
       </c>
       <c r="G7" t="n">
-        <v>8.477</v>
+        <v>8.871</v>
       </c>
       <c r="H7" t="n">
-        <v>8.462999999999999</v>
+        <v>8.821</v>
       </c>
       <c r="I7" t="n">
-        <v>8.397</v>
+        <v>8.775</v>
       </c>
     </row>
     <row r="8">
@@ -7273,25 +7273,25 @@
         <v>9042214</v>
       </c>
       <c r="C8" t="n">
-        <v>8.928000000000001</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>8.861000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="E8" t="n">
-        <v>8.827</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>8.744999999999999</v>
+        <v>8.442</v>
       </c>
       <c r="G8" t="n">
-        <v>8.492000000000001</v>
+        <v>8.257999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>8.395</v>
+        <v>8.109</v>
       </c>
       <c r="I8" t="n">
-        <v>8.035</v>
+        <v>7.991</v>
       </c>
     </row>
     <row r="9">
@@ -7304,25 +7304,25 @@
         <v>9043597</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8</v>
+        <v>5.717</v>
       </c>
       <c r="D9" t="n">
-        <v>5.701</v>
+        <v>5.53</v>
       </c>
       <c r="E9" t="n">
-        <v>5.544</v>
+        <v>5.391</v>
       </c>
       <c r="F9" t="n">
-        <v>5.378</v>
+        <v>5.304</v>
       </c>
       <c r="G9" t="n">
-        <v>5.286</v>
+        <v>5.289</v>
       </c>
       <c r="H9" t="n">
-        <v>5.28</v>
+        <v>5.319</v>
       </c>
       <c r="I9" t="n">
-        <v>5.302</v>
+        <v>5.339</v>
       </c>
     </row>
     <row r="10">
@@ -7335,25 +7335,25 @@
         <v>9040454</v>
       </c>
       <c r="C10" t="n">
-        <v>6.078</v>
+        <v>6.171</v>
       </c>
       <c r="D10" t="n">
-        <v>6.165</v>
+        <v>6.271</v>
       </c>
       <c r="E10" t="n">
-        <v>6.24</v>
+        <v>6.338</v>
       </c>
       <c r="F10" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="G10" t="n">
-        <v>6.361</v>
+        <v>6.332</v>
       </c>
       <c r="H10" t="n">
-        <v>6.32</v>
+        <v>6.255</v>
       </c>
       <c r="I10" t="n">
-        <v>6.233</v>
+        <v>6.143</v>
       </c>
     </row>
     <row r="11">
@@ -7366,25 +7366,25 @@
         <v>9037610</v>
       </c>
       <c r="C11" t="n">
-        <v>4.668</v>
+        <v>4.685</v>
       </c>
       <c r="D11" t="n">
-        <v>4.815</v>
+        <v>4.755</v>
       </c>
       <c r="E11" t="n">
-        <v>4.917</v>
+        <v>4.613</v>
       </c>
       <c r="F11" t="n">
-        <v>4.898</v>
+        <v>4.349</v>
       </c>
       <c r="G11" t="n">
-        <v>4.779</v>
+        <v>4.119</v>
       </c>
       <c r="H11" t="n">
-        <v>4.556</v>
+        <v>4.121</v>
       </c>
       <c r="I11" t="n">
-        <v>4.313</v>
+        <v>4.386</v>
       </c>
     </row>
     <row r="12">
@@ -7397,25 +7397,25 @@
         <v>9043425</v>
       </c>
       <c r="C12" t="n">
-        <v>6.75</v>
+        <v>6.773</v>
       </c>
       <c r="D12" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="E12" t="n">
-        <v>6.69</v>
+        <v>6.707</v>
       </c>
       <c r="F12" t="n">
-        <v>6.64</v>
+        <v>6.671</v>
       </c>
       <c r="G12" t="n">
-        <v>6.61</v>
+        <v>6.634</v>
       </c>
       <c r="H12" t="n">
-        <v>6.55</v>
+        <v>6.597</v>
       </c>
       <c r="I12" t="n">
-        <v>6.509</v>
+        <v>6.561</v>
       </c>
     </row>
     <row r="13">
@@ -7428,25 +7428,25 @@
         <v>9042153</v>
       </c>
       <c r="C13" t="n">
-        <v>11.369</v>
+        <v>11.092</v>
       </c>
       <c r="D13" t="n">
-        <v>11.098</v>
+        <v>10.858</v>
       </c>
       <c r="E13" t="n">
-        <v>10.868</v>
+        <v>10.665</v>
       </c>
       <c r="F13" t="n">
-        <v>10.712</v>
+        <v>10.502</v>
       </c>
       <c r="G13" t="n">
-        <v>10.557</v>
+        <v>10.392</v>
       </c>
       <c r="H13" t="n">
-        <v>10.438</v>
+        <v>10.31</v>
       </c>
       <c r="I13" t="n">
-        <v>10.348</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="14">
@@ -7459,25 +7459,25 @@
         <v>9040439</v>
       </c>
       <c r="C14" t="n">
-        <v>6.876</v>
+        <v>7.003</v>
       </c>
       <c r="D14" t="n">
-        <v>7.079</v>
+        <v>7.105</v>
       </c>
       <c r="E14" t="n">
-        <v>7.15</v>
+        <v>7.132</v>
       </c>
       <c r="F14" t="n">
-        <v>7.205</v>
+        <v>7.098</v>
       </c>
       <c r="G14" t="n">
-        <v>7.15</v>
+        <v>6.989</v>
       </c>
       <c r="H14" t="n">
-        <v>7.057</v>
+        <v>6.81</v>
       </c>
       <c r="I14" t="n">
-        <v>6.85</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="15">
@@ -7490,25 +7490,25 @@
         <v>9032282</v>
       </c>
       <c r="C15" t="n">
-        <v>7.09</v>
+        <v>7.216</v>
       </c>
       <c r="D15" t="n">
-        <v>7.138</v>
+        <v>7.223</v>
       </c>
       <c r="E15" t="n">
-        <v>7.156</v>
+        <v>7.177</v>
       </c>
       <c r="F15" t="n">
-        <v>7.113</v>
+        <v>7.128</v>
       </c>
       <c r="G15" t="n">
-        <v>7.04</v>
+        <v>7.068</v>
       </c>
       <c r="H15" t="n">
-        <v>6.968</v>
+        <v>7.006</v>
       </c>
       <c r="I15" t="n">
-        <v>6.899</v>
+        <v>6.949</v>
       </c>
     </row>
     <row r="16">
@@ -7521,25 +7521,25 @@
         <v>9037738</v>
       </c>
       <c r="C16" t="n">
-        <v>5.717</v>
+        <v>5.725</v>
       </c>
       <c r="D16" t="n">
-        <v>5.921</v>
+        <v>5.633</v>
       </c>
       <c r="E16" t="n">
-        <v>5.953</v>
+        <v>5.374</v>
       </c>
       <c r="F16" t="n">
-        <v>5.82</v>
+        <v>5.186</v>
       </c>
       <c r="G16" t="n">
-        <v>5.583</v>
+        <v>5.25</v>
       </c>
       <c r="H16" t="n">
-        <v>5.369</v>
+        <v>5.548</v>
       </c>
       <c r="I16" t="n">
-        <v>5.218</v>
+        <v>5.956</v>
       </c>
     </row>
     <row r="17">
@@ -7552,25 +7552,25 @@
         <v>9039635</v>
       </c>
       <c r="C17" t="n">
-        <v>5.452</v>
+        <v>5.409</v>
       </c>
       <c r="D17" t="n">
-        <v>5.355</v>
+        <v>5.258</v>
       </c>
       <c r="E17" t="n">
-        <v>5.195</v>
+        <v>5.132</v>
       </c>
       <c r="F17" t="n">
-        <v>5.077</v>
+        <v>4.96</v>
       </c>
       <c r="G17" t="n">
-        <v>4.93</v>
+        <v>4.816</v>
       </c>
       <c r="H17" t="n">
-        <v>4.77</v>
+        <v>4.726</v>
       </c>
       <c r="I17" t="n">
-        <v>4.629</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="18">
@@ -7583,25 +7583,25 @@
         <v>9038269</v>
       </c>
       <c r="C18" t="n">
-        <v>3.318</v>
+        <v>3.432</v>
       </c>
       <c r="D18" t="n">
-        <v>3.462</v>
+        <v>3.592</v>
       </c>
       <c r="E18" t="n">
-        <v>3.676</v>
+        <v>3.659</v>
       </c>
       <c r="F18" t="n">
-        <v>3.73</v>
+        <v>3.706</v>
       </c>
       <c r="G18" t="n">
-        <v>3.759</v>
+        <v>3.718</v>
       </c>
       <c r="H18" t="n">
-        <v>3.763</v>
+        <v>3.674</v>
       </c>
       <c r="I18" t="n">
-        <v>3.742</v>
+        <v>3.617</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -10,6 +10,7 @@
     <sheet name="resumen_estaciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="pronostico_7dias" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="pivot_nivel_prom_ajustado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="diagnostico_ajuste" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14037,4 +14038,816 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>estacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>comid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fecha_inicio_pronostico</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fecha_obs_usada</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nivel_obs_usado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>primer_nivel_bruto</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>offset_aplicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>primer_nivel_ajustado</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>diferencia_control_m</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dias_desde_obs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ajuste_continuidad</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>advertencia_ajuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santa Clotilde</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9032282</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.087999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.216</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.087999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bellavista</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9036028</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.284</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Puerto Almendra</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9037610</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.632</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Observado muy antiguo para ajuste: 36 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Santa María de Nanay</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9037738</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.725</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ENAPU</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9038134</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="F6" t="n">
+        <v>109.237</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-102.817</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Offset alto: -102.82 m. Revisar estación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tamshiyacu</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9038269</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.432</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Santa Rosa</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9039635</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.409</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Borja</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9040208</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.978</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Regis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9040439</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.003</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.373</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nauta</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9040454</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.171</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Offset alto: 2.04 m. Revisar estación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9042153</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.092</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>11.092</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>309</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Observado muy antiguo para ajuste: 309 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Genaro Herrera</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9042214</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.843999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Angamos</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9043370</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-6.064</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Offset alto: -6.06 m. Revisar estación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Requena</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9043425</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.773</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lagunas</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9043597</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.717</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.637</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Flor de Punga</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9044756</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E17" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.855</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>9.855</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>83</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Observado muy antiguo para ajuste: 83 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Contamana</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9053555</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.248</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-5.648</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Offset alto: -5.65 m. Revisar estación.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.946</v>
+        <v>2.116</v>
       </c>
       <c r="H2" t="n">
-        <v>2.015</v>
+        <v>2.185</v>
       </c>
       <c r="I2" t="n">
-        <v>2.387</v>
+        <v>2.557</v>
       </c>
       <c r="J2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="K2" t="n">
-        <v>2.058</v>
+        <v>2.228</v>
       </c>
       <c r="L2" t="n">
         <v>0.008</v>
@@ -614,25 +614,25 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5.419</v>
+        <v>5.379</v>
       </c>
       <c r="H3" t="n">
-        <v>5.559</v>
+        <v>5.519</v>
       </c>
       <c r="I3" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="J3" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="K3" t="n">
-        <v>5.421</v>
+        <v>5.381</v>
       </c>
       <c r="L3" t="n">
         <v>-0.209</v>
@@ -715,21 +715,21 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.832</v>
+        <v>3.584</v>
       </c>
       <c r="H4" t="n">
-        <v>4.005</v>
+        <v>3.757</v>
       </c>
       <c r="I4" t="n">
-        <v>4.584</v>
+        <v>4.336</v>
       </c>
       <c r="J4" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.125</v>
+        <v>3.877</v>
       </c>
       <c r="L4" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6.428</v>
+        <v>6.298</v>
       </c>
       <c r="H5" t="n">
-        <v>6.721</v>
+        <v>6.591</v>
       </c>
       <c r="I5" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="J5" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="K5" t="n">
-        <v>6.439</v>
+        <v>6.309</v>
       </c>
       <c r="L5" t="n">
         <v>-0.541</v>
@@ -917,25 +917,25 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -990,19 +990,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-7.67</v>
+        <v>-7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.064</v>
+        <v>-1.194</v>
       </c>
       <c r="I6" t="n">
-        <v>6.116</v>
+        <v>5.986</v>
       </c>
       <c r="J6" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.872</v>
+        <v>-4.002</v>
       </c>
       <c r="L6" t="n">
         <v>-9.932</v>
@@ -1018,25 +1018,25 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5.434</v>
+        <v>5.382</v>
       </c>
       <c r="H9" t="n">
-        <v>5.52</v>
+        <v>5.468</v>
       </c>
       <c r="I9" t="n">
-        <v>5.603</v>
+        <v>5.55</v>
       </c>
       <c r="J9" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="K9" t="n">
-        <v>5.435</v>
+        <v>5.382</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.167</v>
+        <v>-0.168</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1319,21 +1319,21 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7.449</v>
+        <v>7.509</v>
       </c>
       <c r="H10" t="n">
-        <v>7.774</v>
+        <v>7.834</v>
       </c>
       <c r="I10" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="J10" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="K10" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="L10" t="n">
         <v>-0.48</v>
@@ -1420,25 +1420,25 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7.228</v>
+        <v>7.148</v>
       </c>
       <c r="H12" t="n">
-        <v>7.342</v>
+        <v>7.262</v>
       </c>
       <c r="I12" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="J12" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="K12" t="n">
-        <v>7.235</v>
+        <v>7.155</v>
       </c>
       <c r="L12" t="n">
         <v>-0.215</v>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,19 +1792,19 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="H14" t="n">
-        <v>6.152</v>
+        <v>6.222</v>
       </c>
       <c r="I14" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="J14" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="K14" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="L14" t="n">
         <v>-0.73</v>
@@ -1820,21 +1820,21 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1893,22 +1893,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7.716</v>
+        <v>7.623</v>
       </c>
       <c r="H15" t="n">
-        <v>7.876</v>
+        <v>7.783</v>
       </c>
       <c r="I15" t="n">
-        <v>8.042999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="J15" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="K15" t="n">
-        <v>7.719</v>
+        <v>7.626</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.323</v>
+        <v>-0.324</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1921,21 +1921,21 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1994,19 +1994,19 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3.836</v>
+        <v>3.816</v>
       </c>
       <c r="H16" t="n">
-        <v>4.516</v>
+        <v>4.496</v>
       </c>
       <c r="I16" t="n">
-        <v>6.038</v>
+        <v>6.018</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="K16" t="n">
-        <v>5.155</v>
+        <v>5.135</v>
       </c>
       <c r="L16" t="n">
         <v>0.755</v>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5.292</v>
+        <v>5.144</v>
       </c>
       <c r="H17" t="n">
-        <v>5.427</v>
+        <v>5.28</v>
       </c>
       <c r="I17" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="J17" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="K17" t="n">
-        <v>5.379</v>
+        <v>5.231</v>
       </c>
       <c r="L17" t="n">
         <v>-0.329</v>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="H18" t="n">
-        <v>3.568</v>
+        <v>3.548</v>
       </c>
       <c r="I18" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="J18" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="K18" t="n">
-        <v>3.203</v>
+        <v>3.183</v>
       </c>
       <c r="L18" t="n">
         <v>-0.457</v>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="F2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>8.179</v>
@@ -2480,16 +2480,16 @@
         <v>8.179</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
         <v>8.179</v>
@@ -2509,25 +2509,25 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2549,19 +2549,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="F3" t="n">
-        <v>2.026</v>
+        <v>2.196</v>
       </c>
       <c r="G3" t="n">
-        <v>2.028</v>
+        <v>2.198</v>
       </c>
       <c r="H3" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="I3" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="J3" t="n">
         <v>8.156000000000001</v>
@@ -2579,16 +2579,16 @@
         <v>8.156000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="P3" t="n">
-        <v>2.028</v>
+        <v>2.198</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="R3" t="n">
-        <v>2.026</v>
+        <v>2.196</v>
       </c>
       <c r="S3" t="n">
         <v>8.156000000000001</v>
@@ -2608,25 +2608,25 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2648,19 +2648,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.005</v>
+        <v>2.175</v>
       </c>
       <c r="F4" t="n">
-        <v>2.003</v>
+        <v>2.173</v>
       </c>
       <c r="G4" t="n">
-        <v>2.007</v>
+        <v>2.177</v>
       </c>
       <c r="H4" t="n">
-        <v>2.003</v>
+        <v>2.173</v>
       </c>
       <c r="I4" t="n">
-        <v>2.006</v>
+        <v>2.176</v>
       </c>
       <c r="J4" t="n">
         <v>8.134</v>
@@ -2678,16 +2678,16 @@
         <v>8.135</v>
       </c>
       <c r="O4" t="n">
-        <v>2.006</v>
+        <v>2.176</v>
       </c>
       <c r="P4" t="n">
-        <v>2.007</v>
+        <v>2.177</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.003</v>
+        <v>2.173</v>
       </c>
       <c r="R4" t="n">
-        <v>2.003</v>
+        <v>2.173</v>
       </c>
       <c r="S4" t="n">
         <v>8.135</v>
@@ -2707,25 +2707,25 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2747,19 +2747,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.983</v>
+        <v>2.153</v>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="G5" t="n">
-        <v>1.986</v>
+        <v>2.156</v>
       </c>
       <c r="H5" t="n">
-        <v>1.982</v>
+        <v>2.152</v>
       </c>
       <c r="I5" t="n">
-        <v>1.985</v>
+        <v>2.155</v>
       </c>
       <c r="J5" t="n">
         <v>8.112</v>
@@ -2777,16 +2777,16 @@
         <v>8.114000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1.985</v>
+        <v>2.155</v>
       </c>
       <c r="P5" t="n">
-        <v>1.986</v>
+        <v>2.156</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>1.983</v>
+        <v>2.153</v>
       </c>
       <c r="S5" t="n">
         <v>8.113</v>
@@ -2806,25 +2806,25 @@
         </is>
       </c>
       <c r="X5" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2846,19 +2846,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.963</v>
+        <v>2.133</v>
       </c>
       <c r="F6" t="n">
-        <v>1.961</v>
+        <v>2.131</v>
       </c>
       <c r="G6" t="n">
-        <v>1.966</v>
+        <v>2.136</v>
       </c>
       <c r="H6" t="n">
-        <v>1.963</v>
+        <v>2.133</v>
       </c>
       <c r="I6" t="n">
-        <v>1.964</v>
+        <v>2.134</v>
       </c>
       <c r="J6" t="n">
         <v>8.092000000000001</v>
@@ -2876,16 +2876,16 @@
         <v>8.093</v>
       </c>
       <c r="O6" t="n">
-        <v>1.963</v>
+        <v>2.133</v>
       </c>
       <c r="P6" t="n">
-        <v>1.966</v>
+        <v>2.136</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.961</v>
+        <v>2.131</v>
       </c>
       <c r="R6" t="n">
-        <v>1.963</v>
+        <v>2.133</v>
       </c>
       <c r="S6" t="n">
         <v>8.092000000000001</v>
@@ -2905,25 +2905,25 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.016</v>
+        <v>2.186</v>
       </c>
       <c r="F7" t="n">
-        <v>1.948</v>
+        <v>2.118</v>
       </c>
       <c r="G7" t="n">
-        <v>2.216</v>
+        <v>2.386</v>
       </c>
       <c r="H7" t="n">
-        <v>1.949</v>
+        <v>2.119</v>
       </c>
       <c r="I7" t="n">
-        <v>2.018</v>
+        <v>2.188</v>
       </c>
       <c r="J7" t="n">
         <v>8.145</v>
@@ -2975,16 +2975,16 @@
         <v>8.147</v>
       </c>
       <c r="O7" t="n">
-        <v>1.948</v>
+        <v>2.118</v>
       </c>
       <c r="P7" t="n">
-        <v>1.952</v>
+        <v>2.122</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>2.216</v>
+        <v>2.386</v>
       </c>
       <c r="S7" t="n">
         <v>8.077</v>
@@ -3004,25 +3004,25 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.058</v>
+        <v>2.228</v>
       </c>
       <c r="F8" t="n">
-        <v>1.946</v>
+        <v>2.116</v>
       </c>
       <c r="G8" t="n">
-        <v>2.387</v>
+        <v>2.557</v>
       </c>
       <c r="H8" t="n">
-        <v>1.946</v>
+        <v>2.116</v>
       </c>
       <c r="I8" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="J8" t="n">
         <v>8.186999999999999</v>
@@ -3074,16 +3074,16 @@
         <v>8.189</v>
       </c>
       <c r="O8" t="n">
-        <v>1.946</v>
+        <v>2.116</v>
       </c>
       <c r="P8" t="n">
-        <v>1.951</v>
+        <v>2.121</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.946</v>
+        <v>2.116</v>
       </c>
       <c r="R8" t="n">
-        <v>2.387</v>
+        <v>2.557</v>
       </c>
       <c r="S8" t="n">
         <v>8.074999999999999</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="F9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="G9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="H9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="I9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="J9" t="n">
         <v>6.22</v>
@@ -3173,16 +3173,16 @@
         <v>6.22</v>
       </c>
       <c r="O9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="P9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="R9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="S9" t="n">
         <v>6.22</v>
@@ -3202,21 +3202,21 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="F10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="G10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="H10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="I10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="J10" t="n">
         <v>6.236</v>
@@ -3272,16 +3272,16 @@
         <v>6.236</v>
       </c>
       <c r="O10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="P10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="R10" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="S10" t="n">
         <v>6.236</v>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="F11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="G11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="H11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="I11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="J11" t="n">
         <v>6.224</v>
@@ -3371,16 +3371,16 @@
         <v>6.224</v>
       </c>
       <c r="O11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="P11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="R11" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="S11" t="n">
         <v>6.224</v>
@@ -3400,21 +3400,21 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3440,19 +3440,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.597</v>
+        <v>5.557</v>
       </c>
       <c r="F12" t="n">
-        <v>5.596</v>
+        <v>5.556</v>
       </c>
       <c r="G12" t="n">
-        <v>5.602</v>
+        <v>5.562</v>
       </c>
       <c r="H12" t="n">
-        <v>5.596</v>
+        <v>5.556</v>
       </c>
       <c r="I12" t="n">
-        <v>5.597</v>
+        <v>5.557</v>
       </c>
       <c r="J12" t="n">
         <v>6.187</v>
@@ -3470,16 +3470,16 @@
         <v>6.187</v>
       </c>
       <c r="O12" t="n">
-        <v>5.596</v>
+        <v>5.556</v>
       </c>
       <c r="P12" t="n">
-        <v>5.602</v>
+        <v>5.562</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.596</v>
+        <v>5.556</v>
       </c>
       <c r="R12" t="n">
-        <v>5.596</v>
+        <v>5.556</v>
       </c>
       <c r="S12" t="n">
         <v>6.186</v>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3539,19 +3539,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="F13" t="n">
-        <v>5.534</v>
+        <v>5.494</v>
       </c>
       <c r="G13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="H13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="I13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="J13" t="n">
         <v>6.125</v>
@@ -3569,16 +3569,16 @@
         <v>6.125</v>
       </c>
       <c r="O13" t="n">
-        <v>5.534</v>
+        <v>5.494</v>
       </c>
       <c r="P13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="R13" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="S13" t="n">
         <v>6.123</v>
@@ -3598,21 +3598,21 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3638,19 +3638,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="F14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="G14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="H14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="I14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="J14" t="n">
         <v>6.04</v>
@@ -3668,16 +3668,16 @@
         <v>6.04</v>
       </c>
       <c r="O14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="R14" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="S14" t="n">
         <v>6.039</v>
@@ -3697,21 +3697,21 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3737,19 +3737,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.421</v>
+        <v>5.381</v>
       </c>
       <c r="F15" t="n">
-        <v>5.419</v>
+        <v>5.379</v>
       </c>
       <c r="G15" t="n">
-        <v>5.423</v>
+        <v>5.383</v>
       </c>
       <c r="H15" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="I15" t="n">
-        <v>5.421</v>
+        <v>5.381</v>
       </c>
       <c r="J15" t="n">
         <v>6.01</v>
@@ -3767,16 +3767,16 @@
         <v>6.011</v>
       </c>
       <c r="O15" t="n">
-        <v>5.419</v>
+        <v>5.379</v>
       </c>
       <c r="P15" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.421</v>
+        <v>5.381</v>
       </c>
       <c r="R15" t="n">
-        <v>5.423</v>
+        <v>5.383</v>
       </c>
       <c r="S15" t="n">
         <v>6.009</v>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3836,19 +3836,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="F16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>4.098</v>
+        <v>3.85</v>
       </c>
       <c r="H16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
-        <v>4.098</v>
+        <v>3.85</v>
       </c>
       <c r="J16" t="n">
         <v>4.724</v>
@@ -3866,16 +3866,16 @@
         <v>4.724</v>
       </c>
       <c r="O16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>4.098</v>
+        <v>3.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.098</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="S16" t="n">
         <v>4.723</v>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3935,19 +3935,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3.753</v>
       </c>
       <c r="F17" t="n">
-        <v>3.994</v>
+        <v>3.746</v>
       </c>
       <c r="G17" t="n">
-        <v>4.006</v>
+        <v>3.758</v>
       </c>
       <c r="H17" t="n">
-        <v>3.998</v>
+        <v>3.751</v>
       </c>
       <c r="I17" t="n">
-        <v>4.003</v>
+        <v>3.755</v>
       </c>
       <c r="J17" t="n">
         <v>4.626</v>
@@ -3965,16 +3965,16 @@
         <v>4.629</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.752</v>
       </c>
       <c r="P17" t="n">
-        <v>4.001</v>
+        <v>3.754</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.006</v>
+        <v>3.758</v>
       </c>
       <c r="R17" t="n">
-        <v>3.994</v>
+        <v>3.746</v>
       </c>
       <c r="S17" t="n">
         <v>4.626</v>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -4034,19 +4034,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.92</v>
+        <v>3.673</v>
       </c>
       <c r="F18" t="n">
-        <v>3.911</v>
+        <v>3.664</v>
       </c>
       <c r="G18" t="n">
-        <v>3.936</v>
+        <v>3.689</v>
       </c>
       <c r="H18" t="n">
-        <v>3.911</v>
+        <v>3.664</v>
       </c>
       <c r="I18" t="n">
-        <v>3.925</v>
+        <v>3.677</v>
       </c>
       <c r="J18" t="n">
         <v>4.546</v>
@@ -4064,16 +4064,16 @@
         <v>4.551</v>
       </c>
       <c r="O18" t="n">
-        <v>3.911</v>
+        <v>3.664</v>
       </c>
       <c r="P18" t="n">
-        <v>3.921</v>
+        <v>3.673</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.936</v>
+        <v>3.689</v>
       </c>
       <c r="R18" t="n">
-        <v>3.911</v>
+        <v>3.664</v>
       </c>
       <c r="S18" t="n">
         <v>4.537</v>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4133,19 +4133,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.905</v>
+        <v>3.658</v>
       </c>
       <c r="F19" t="n">
-        <v>3.864</v>
+        <v>3.617</v>
       </c>
       <c r="G19" t="n">
-        <v>3.99</v>
+        <v>3.743</v>
       </c>
       <c r="H19" t="n">
-        <v>3.876</v>
+        <v>3.628</v>
       </c>
       <c r="I19" t="n">
-        <v>3.913</v>
+        <v>3.665</v>
       </c>
       <c r="J19" t="n">
         <v>4.531</v>
@@ -4163,16 +4163,16 @@
         <v>4.539</v>
       </c>
       <c r="O19" t="n">
-        <v>3.864</v>
+        <v>3.617</v>
       </c>
       <c r="P19" t="n">
-        <v>3.879</v>
+        <v>3.632</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.99</v>
+        <v>3.743</v>
       </c>
       <c r="R19" t="n">
-        <v>3.887</v>
+        <v>3.64</v>
       </c>
       <c r="S19" t="n">
         <v>4.49</v>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -4232,19 +4232,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.947</v>
+        <v>3.699</v>
       </c>
       <c r="F20" t="n">
-        <v>3.843</v>
+        <v>3.596</v>
       </c>
       <c r="G20" t="n">
-        <v>4.155</v>
+        <v>3.907</v>
       </c>
       <c r="H20" t="n">
-        <v>3.854</v>
+        <v>3.607</v>
       </c>
       <c r="I20" t="n">
-        <v>3.987</v>
+        <v>3.74</v>
       </c>
       <c r="J20" t="n">
         <v>4.573</v>
@@ -4262,16 +4262,16 @@
         <v>4.613</v>
       </c>
       <c r="O20" t="n">
-        <v>3.843</v>
+        <v>3.596</v>
       </c>
       <c r="P20" t="n">
-        <v>3.858</v>
+        <v>3.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.155</v>
+        <v>3.907</v>
       </c>
       <c r="R20" t="n">
-        <v>3.931</v>
+        <v>3.684</v>
       </c>
       <c r="S20" t="n">
         <v>4.469</v>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -4331,19 +4331,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.038</v>
+        <v>3.791</v>
       </c>
       <c r="F21" t="n">
-        <v>3.836</v>
+        <v>3.588</v>
       </c>
       <c r="G21" t="n">
-        <v>4.398</v>
+        <v>4.15</v>
       </c>
       <c r="H21" t="n">
-        <v>3.852</v>
+        <v>3.605</v>
       </c>
       <c r="I21" t="n">
-        <v>4.145</v>
+        <v>3.897</v>
       </c>
       <c r="J21" t="n">
         <v>4.664</v>
@@ -4361,16 +4361,16 @@
         <v>4.771</v>
       </c>
       <c r="O21" t="n">
-        <v>3.836</v>
+        <v>3.588</v>
       </c>
       <c r="P21" t="n">
-        <v>3.858</v>
+        <v>3.611</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.398</v>
+        <v>4.15</v>
       </c>
       <c r="R21" t="n">
-        <v>4.061</v>
+        <v>3.813</v>
       </c>
       <c r="S21" t="n">
         <v>4.462</v>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -4430,19 +4430,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.125</v>
+        <v>3.877</v>
       </c>
       <c r="F22" t="n">
-        <v>3.832</v>
+        <v>3.584</v>
       </c>
       <c r="G22" t="n">
-        <v>4.584</v>
+        <v>4.336</v>
       </c>
       <c r="H22" t="n">
-        <v>3.864</v>
+        <v>3.617</v>
       </c>
       <c r="I22" t="n">
-        <v>4.303</v>
+        <v>4.055</v>
       </c>
       <c r="J22" t="n">
         <v>4.751</v>
@@ -4460,16 +4460,16 @@
         <v>4.929</v>
       </c>
       <c r="O22" t="n">
-        <v>3.832</v>
+        <v>3.584</v>
       </c>
       <c r="P22" t="n">
-        <v>3.875</v>
+        <v>3.627</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.584</v>
+        <v>4.336</v>
       </c>
       <c r="R22" t="n">
-        <v>4.209</v>
+        <v>3.961</v>
       </c>
       <c r="S22" t="n">
         <v>4.458</v>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4529,19 +4529,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="F23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="G23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="H23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="I23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="J23" t="n">
         <v>12.117</v>
@@ -4559,16 +4559,16 @@
         <v>12.117</v>
       </c>
       <c r="O23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="P23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="R23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="S23" t="n">
         <v>12.117</v>
@@ -4588,25 +4588,25 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4628,19 +4628,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="F24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="G24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="H24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="I24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="J24" t="n">
         <v>12.043</v>
@@ -4658,16 +4658,16 @@
         <v>12.043</v>
       </c>
       <c r="O24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="P24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="R24" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="S24" t="n">
         <v>12.043</v>
@@ -4687,25 +4687,25 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4727,19 +4727,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="F25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="G25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="H25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="I25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="J25" t="n">
         <v>11.972</v>
@@ -4757,16 +4757,16 @@
         <v>11.972</v>
       </c>
       <c r="O25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="P25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="R25" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="S25" t="n">
         <v>11.972</v>
@@ -4786,25 +4786,25 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4826,19 +4826,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="F26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="G26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="H26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="I26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="J26" t="n">
         <v>11.864</v>
@@ -4856,16 +4856,16 @@
         <v>11.864</v>
       </c>
       <c r="O26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="P26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="R26" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="S26" t="n">
         <v>11.864</v>
@@ -4885,25 +4885,25 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4925,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="F27" t="n">
-        <v>6.626</v>
+        <v>6.496</v>
       </c>
       <c r="G27" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="H27" t="n">
-        <v>6.626</v>
+        <v>6.496</v>
       </c>
       <c r="I27" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="J27" t="n">
         <v>11.764</v>
@@ -4955,16 +4955,16 @@
         <v>11.765</v>
       </c>
       <c r="O27" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="P27" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.626</v>
+        <v>6.496</v>
       </c>
       <c r="R27" t="n">
-        <v>6.626</v>
+        <v>6.496</v>
       </c>
       <c r="S27" t="n">
         <v>11.765</v>
@@ -4984,25 +4984,25 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5024,19 +5024,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.535</v>
+        <v>6.405</v>
       </c>
       <c r="F28" t="n">
-        <v>6.531</v>
+        <v>6.401</v>
       </c>
       <c r="G28" t="n">
-        <v>6.538</v>
+        <v>6.408</v>
       </c>
       <c r="H28" t="n">
-        <v>6.533</v>
+        <v>6.403</v>
       </c>
       <c r="I28" t="n">
-        <v>6.537</v>
+        <v>6.407</v>
       </c>
       <c r="J28" t="n">
         <v>11.672</v>
@@ -5054,16 +5054,16 @@
         <v>11.674</v>
       </c>
       <c r="O28" t="n">
-        <v>6.536</v>
+        <v>6.406</v>
       </c>
       <c r="P28" t="n">
-        <v>6.538</v>
+        <v>6.408</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.533</v>
+        <v>6.403</v>
       </c>
       <c r="R28" t="n">
-        <v>6.531</v>
+        <v>6.401</v>
       </c>
       <c r="S28" t="n">
         <v>11.674</v>
@@ -5083,25 +5083,25 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5123,19 +5123,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.439</v>
+        <v>6.309</v>
       </c>
       <c r="F29" t="n">
-        <v>6.428</v>
+        <v>6.298</v>
       </c>
       <c r="G29" t="n">
-        <v>6.445</v>
+        <v>6.315</v>
       </c>
       <c r="H29" t="n">
-        <v>6.438</v>
+        <v>6.308</v>
       </c>
       <c r="I29" t="n">
-        <v>6.442</v>
+        <v>6.312</v>
       </c>
       <c r="J29" t="n">
         <v>11.576</v>
@@ -5153,16 +5153,16 @@
         <v>11.58</v>
       </c>
       <c r="O29" t="n">
-        <v>6.441</v>
+        <v>6.311</v>
       </c>
       <c r="P29" t="n">
-        <v>6.445</v>
+        <v>6.315</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.442</v>
+        <v>6.312</v>
       </c>
       <c r="R29" t="n">
-        <v>6.428</v>
+        <v>6.298</v>
       </c>
       <c r="S29" t="n">
         <v>11.578</v>
@@ -5182,25 +5182,25 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA29" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F30" t="n">
-        <v>6.032</v>
+        <v>5.902</v>
       </c>
       <c r="G30" t="n">
-        <v>6.116</v>
+        <v>5.986</v>
       </c>
       <c r="H30" t="n">
-        <v>6.041</v>
+        <v>5.911</v>
       </c>
       <c r="I30" t="n">
-        <v>6.065</v>
+        <v>5.935</v>
       </c>
       <c r="J30" t="n">
         <v>105.501</v>
@@ -5252,16 +5252,16 @@
         <v>105.506</v>
       </c>
       <c r="O30" t="n">
-        <v>6.048</v>
+        <v>5.918</v>
       </c>
       <c r="P30" t="n">
-        <v>6.116</v>
+        <v>5.986</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.044</v>
+        <v>5.914</v>
       </c>
       <c r="R30" t="n">
-        <v>6.032</v>
+        <v>5.902</v>
       </c>
       <c r="S30" t="n">
         <v>105.489</v>
@@ -5281,25 +5281,25 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5321,19 +5321,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.155</v>
+        <v>2.025</v>
       </c>
       <c r="F31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>2.822</v>
+        <v>2.692</v>
       </c>
       <c r="H31" t="n">
-        <v>1.924</v>
+        <v>1.794</v>
       </c>
       <c r="I31" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="J31" t="n">
         <v>101.596</v>
@@ -5351,16 +5351,16 @@
         <v>101.681</v>
       </c>
       <c r="O31" t="n">
-        <v>1.972</v>
+        <v>1.842</v>
       </c>
       <c r="P31" t="n">
-        <v>2.822</v>
+        <v>2.692</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.047</v>
+        <v>1.917</v>
       </c>
       <c r="R31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="S31" t="n">
         <v>101.413</v>
@@ -5380,25 +5380,25 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.916</v>
+        <v>-1.046</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.796</v>
+        <v>-1.926</v>
       </c>
       <c r="G32" t="n">
-        <v>0.607</v>
+        <v>0.477</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.514</v>
+        <v>-1.644</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.641</v>
+        <v>-0.771</v>
       </c>
       <c r="J32" t="n">
         <v>98.524</v>
@@ -5450,16 +5450,16 @@
         <v>98.8</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.42</v>
+        <v>-1.55</v>
       </c>
       <c r="P32" t="n">
-        <v>0.607</v>
+        <v>0.477</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.057</v>
+        <v>-1.187</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.796</v>
+        <v>-1.926</v>
       </c>
       <c r="S32" t="n">
         <v>98.021</v>
@@ -5479,25 +5479,25 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5519,19 +5519,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-2.995</v>
+        <v>-3.125</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.297</v>
+        <v>-4.427</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.612</v>
+        <v>-0.742</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.107</v>
+        <v>-4.237</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.424</v>
+        <v>-2.554</v>
       </c>
       <c r="J33" t="n">
         <v>96.446</v>
@@ -5549,16 +5549,16 @@
         <v>97.017</v>
       </c>
       <c r="O33" t="n">
-        <v>-4.043</v>
+        <v>-4.173</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.612</v>
+        <v>-0.742</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3.028</v>
+        <v>-3.158</v>
       </c>
       <c r="R33" t="n">
-        <v>-4.297</v>
+        <v>-4.427</v>
       </c>
       <c r="S33" t="n">
         <v>95.39700000000001</v>
@@ -5578,25 +5578,25 @@
         </is>
       </c>
       <c r="X33" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-3.95</v>
+        <v>-4.08</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.863</v>
+        <v>-5.993</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.126</v>
+        <v>-1.256</v>
       </c>
       <c r="H34" t="n">
-        <v>-5.114</v>
+        <v>-5.244</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.242</v>
+        <v>-3.372</v>
       </c>
       <c r="J34" t="n">
         <v>95.48999999999999</v>
@@ -5648,16 +5648,16 @@
         <v>96.199</v>
       </c>
       <c r="O34" t="n">
-        <v>-5.863</v>
+        <v>-5.993</v>
       </c>
       <c r="P34" t="n">
-        <v>-1.126</v>
+        <v>-1.256</v>
       </c>
       <c r="Q34" t="n">
-        <v>-3.948</v>
+        <v>-4.078</v>
       </c>
       <c r="R34" t="n">
-        <v>-4.865</v>
+        <v>-4.995</v>
       </c>
       <c r="S34" t="n">
         <v>93.578</v>
@@ -5677,25 +5677,25 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA34" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5717,19 +5717,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-3.927</v>
+        <v>-4.057</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.862</v>
+        <v>-6.992</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.138</v>
+        <v>-1.268</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.012</v>
+        <v>-5.142</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.769</v>
+        <v>-2.899</v>
       </c>
       <c r="J35" t="n">
         <v>95.514</v>
@@ -5747,16 +5747,16 @@
         <v>96.672</v>
       </c>
       <c r="O35" t="n">
-        <v>-6.862</v>
+        <v>-6.992</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.138</v>
+        <v>-1.268</v>
       </c>
       <c r="Q35" t="n">
-        <v>-4.396</v>
+        <v>-4.526</v>
       </c>
       <c r="R35" t="n">
-        <v>-3.312</v>
+        <v>-3.442</v>
       </c>
       <c r="S35" t="n">
         <v>92.57899999999999</v>
@@ -5776,25 +5776,25 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5816,19 +5816,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-3.872</v>
+        <v>-4.002</v>
       </c>
       <c r="F36" t="n">
-        <v>-7.67</v>
+        <v>-7.8</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.502</v>
+        <v>-1.632</v>
       </c>
       <c r="H36" t="n">
-        <v>-5.307</v>
+        <v>-5.437</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.723</v>
+        <v>-1.853</v>
       </c>
       <c r="J36" t="n">
         <v>95.569</v>
@@ -5846,16 +5846,16 @@
         <v>97.718</v>
       </c>
       <c r="O36" t="n">
-        <v>-7.67</v>
+        <v>-7.8</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.502</v>
+        <v>-1.632</v>
       </c>
       <c r="Q36" t="n">
-        <v>-4.519</v>
+        <v>-4.649</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.796</v>
+        <v>-1.926</v>
       </c>
       <c r="S36" t="n">
         <v>91.771</v>
@@ -5875,25 +5875,25 @@
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7287,19 +7287,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="F51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="G51" t="n">
-        <v>5.603</v>
+        <v>5.55</v>
       </c>
       <c r="H51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="I51" t="n">
-        <v>5.603</v>
+        <v>5.55</v>
       </c>
       <c r="J51" t="n">
         <v>5.401</v>
@@ -7317,16 +7317,16 @@
         <v>5.401</v>
       </c>
       <c r="O51" t="n">
-        <v>5.603</v>
+        <v>5.55</v>
       </c>
       <c r="P51" t="n">
-        <v>5.603</v>
+        <v>5.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="R51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="S51" t="n">
         <v>5.401</v>
@@ -7346,21 +7346,21 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA51" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -7386,19 +7386,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="F52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="G52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="H52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="I52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="J52" t="n">
         <v>5.314</v>
@@ -7416,16 +7416,16 @@
         <v>5.314</v>
       </c>
       <c r="O52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="P52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="R52" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="S52" t="n">
         <v>5.314</v>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA52" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -7485,19 +7485,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="F53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="G53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="H53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="I53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="J53" t="n">
         <v>5.299</v>
@@ -7515,16 +7515,16 @@
         <v>5.299</v>
       </c>
       <c r="O53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="P53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="R53" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="S53" t="n">
         <v>5.299</v>
@@ -7544,21 +7544,21 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA53" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -7584,19 +7584,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="F54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="G54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="H54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="I54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="J54" t="n">
         <v>5.328</v>
@@ -7614,16 +7614,16 @@
         <v>5.328</v>
       </c>
       <c r="O54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="P54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="R54" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="S54" t="n">
         <v>5.328</v>
@@ -7643,21 +7643,21 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA54" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -7683,19 +7683,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="F55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="G55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="H55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="I55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="J55" t="n">
         <v>5.345</v>
@@ -7713,16 +7713,16 @@
         <v>5.345</v>
       </c>
       <c r="O55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="P55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="R55" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="S55" t="n">
         <v>5.345</v>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA55" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -7782,19 +7782,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="F56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="G56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="H56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="I56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="J56" t="n">
         <v>5.313</v>
@@ -7812,16 +7812,16 @@
         <v>5.313</v>
       </c>
       <c r="O56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="P56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="R56" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="S56" t="n">
         <v>5.313</v>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -7881,19 +7881,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.435</v>
+        <v>5.382</v>
       </c>
       <c r="F57" t="n">
-        <v>5.434</v>
+        <v>5.382</v>
       </c>
       <c r="G57" t="n">
-        <v>5.436</v>
+        <v>5.383</v>
       </c>
       <c r="H57" t="n">
-        <v>5.434</v>
+        <v>5.382</v>
       </c>
       <c r="I57" t="n">
-        <v>5.435</v>
+        <v>5.383</v>
       </c>
       <c r="J57" t="n">
         <v>5.234</v>
@@ -7911,16 +7911,16 @@
         <v>5.234</v>
       </c>
       <c r="O57" t="n">
-        <v>5.434</v>
+        <v>5.382</v>
       </c>
       <c r="P57" t="n">
-        <v>5.436</v>
+        <v>5.383</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.435</v>
+        <v>5.383</v>
       </c>
       <c r="R57" t="n">
-        <v>5.434</v>
+        <v>5.382</v>
       </c>
       <c r="S57" t="n">
         <v>5.233</v>
@@ -7940,21 +7940,21 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA57" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -7980,19 +7980,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="F58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="G58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="H58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="I58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="J58" t="n">
         <v>6.347</v>
@@ -8010,16 +8010,16 @@
         <v>6.347</v>
       </c>
       <c r="O58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="P58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="Q58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="R58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="S58" t="n">
         <v>6.347</v>
@@ -8039,25 +8039,25 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA58" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8079,19 +8079,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="F59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="G59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="H59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="I59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="J59" t="n">
         <v>6.369</v>
@@ -8109,16 +8109,16 @@
         <v>6.37</v>
       </c>
       <c r="O59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="P59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="Q59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="R59" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="S59" t="n">
         <v>6.369</v>
@@ -8138,25 +8138,25 @@
         </is>
       </c>
       <c r="X59" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA59" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8178,19 +8178,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="F60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="G60" t="n">
-        <v>7.924</v>
+        <v>7.984</v>
       </c>
       <c r="H60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="I60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="J60" t="n">
         <v>6.341</v>
@@ -8208,16 +8208,16 @@
         <v>6.341</v>
       </c>
       <c r="O60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="P60" t="n">
-        <v>7.924</v>
+        <v>7.984</v>
       </c>
       <c r="Q60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="R60" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="S60" t="n">
         <v>6.341</v>
@@ -8237,25 +8237,25 @@
         </is>
       </c>
       <c r="X60" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA60" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8277,19 +8277,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="F61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="G61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="H61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="I61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="J61" t="n">
         <v>6.263</v>
@@ -8307,16 +8307,16 @@
         <v>6.263</v>
       </c>
       <c r="O61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="P61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="R61" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="S61" t="n">
         <v>6.263</v>
@@ -8336,25 +8336,25 @@
         </is>
       </c>
       <c r="X61" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA61" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8376,19 +8376,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="F62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="G62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="H62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="I62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="J62" t="n">
         <v>6.149</v>
@@ -8406,16 +8406,16 @@
         <v>6.149</v>
       </c>
       <c r="O62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="P62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="R62" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="S62" t="n">
         <v>6.149</v>
@@ -8435,25 +8435,25 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA62" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8475,19 +8475,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="F63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="G63" t="n">
-        <v>7.587</v>
+        <v>7.647</v>
       </c>
       <c r="H63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="I63" t="n">
-        <v>7.586</v>
+        <v>7.646</v>
       </c>
       <c r="J63" t="n">
         <v>6.003</v>
@@ -8505,16 +8505,16 @@
         <v>6.003</v>
       </c>
       <c r="O63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="P63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="R63" t="n">
-        <v>7.587</v>
+        <v>7.647</v>
       </c>
       <c r="S63" t="n">
         <v>6.002</v>
@@ -8534,25 +8534,25 @@
         </is>
       </c>
       <c r="X63" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA63" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8574,19 +8574,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="F64" t="n">
-        <v>7.449</v>
+        <v>7.509</v>
       </c>
       <c r="G64" t="n">
-        <v>7.451</v>
+        <v>7.511</v>
       </c>
       <c r="H64" t="n">
-        <v>7.449</v>
+        <v>7.509</v>
       </c>
       <c r="I64" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="J64" t="n">
         <v>5.867</v>
@@ -8604,16 +8604,16 @@
         <v>5.867</v>
       </c>
       <c r="O64" t="n">
-        <v>7.449</v>
+        <v>7.509</v>
       </c>
       <c r="P64" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
       <c r="R64" t="n">
-        <v>7.451</v>
+        <v>7.511</v>
       </c>
       <c r="S64" t="n">
         <v>5.866</v>
@@ -8633,25 +8633,25 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA64" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="AB64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -9352,19 +9352,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="F72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="G72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="H72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="I72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="J72" t="n">
         <v>6.723</v>
@@ -9382,16 +9382,16 @@
         <v>6.723</v>
       </c>
       <c r="O72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="P72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="R72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="S72" t="n">
         <v>6.723</v>
@@ -9411,21 +9411,21 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y72" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA72" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -9451,19 +9451,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="F73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="G73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="H73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="I73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="J73" t="n">
         <v>6.688</v>
@@ -9481,16 +9481,16 @@
         <v>6.688</v>
       </c>
       <c r="O73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="P73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="R73" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="S73" t="n">
         <v>6.688</v>
@@ -9510,21 +9510,21 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y73" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA73" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -9550,19 +9550,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="F74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="G74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="H74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="I74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="J74" t="n">
         <v>6.649</v>
@@ -9580,16 +9580,16 @@
         <v>6.65</v>
       </c>
       <c r="O74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="P74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="R74" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="S74" t="n">
         <v>6.65</v>
@@ -9609,21 +9609,21 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y74" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA74" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -9649,19 +9649,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="F75" t="n">
-        <v>7.338</v>
+        <v>7.258</v>
       </c>
       <c r="G75" t="n">
-        <v>7.34</v>
+        <v>7.26</v>
       </c>
       <c r="H75" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="I75" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="J75" t="n">
         <v>6.612</v>
@@ -9679,16 +9679,16 @@
         <v>6.612</v>
       </c>
       <c r="O75" t="n">
-        <v>7.338</v>
+        <v>7.258</v>
       </c>
       <c r="P75" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="Q75" t="n">
-        <v>7.34</v>
+        <v>7.26</v>
       </c>
       <c r="R75" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="S75" t="n">
         <v>6.611</v>
@@ -9708,21 +9708,21 @@
         </is>
       </c>
       <c r="X75" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y75" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA75" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -9748,19 +9748,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.304</v>
+        <v>7.224</v>
       </c>
       <c r="F76" t="n">
-        <v>7.301</v>
+        <v>7.221</v>
       </c>
       <c r="G76" t="n">
-        <v>7.312</v>
+        <v>7.232</v>
       </c>
       <c r="H76" t="n">
-        <v>7.301</v>
+        <v>7.221</v>
       </c>
       <c r="I76" t="n">
-        <v>7.305</v>
+        <v>7.225</v>
       </c>
       <c r="J76" t="n">
         <v>6.577</v>
@@ -9778,16 +9778,16 @@
         <v>6.578</v>
       </c>
       <c r="O76" t="n">
-        <v>7.301</v>
+        <v>7.221</v>
       </c>
       <c r="P76" t="n">
-        <v>7.301</v>
+        <v>7.221</v>
       </c>
       <c r="Q76" t="n">
-        <v>7.303</v>
+        <v>7.223</v>
       </c>
       <c r="R76" t="n">
-        <v>7.312</v>
+        <v>7.232</v>
       </c>
       <c r="S76" t="n">
         <v>6.574</v>
@@ -9807,21 +9807,21 @@
         </is>
       </c>
       <c r="X76" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y76" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA76" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
@@ -9847,19 +9847,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.271</v>
+        <v>7.191</v>
       </c>
       <c r="F77" t="n">
-        <v>7.264</v>
+        <v>7.184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.288</v>
+        <v>7.208</v>
       </c>
       <c r="H77" t="n">
-        <v>7.265</v>
+        <v>7.185</v>
       </c>
       <c r="I77" t="n">
-        <v>7.271</v>
+        <v>7.191</v>
       </c>
       <c r="J77" t="n">
         <v>6.543</v>
@@ -9877,16 +9877,16 @@
         <v>6.544</v>
       </c>
       <c r="O77" t="n">
-        <v>7.265</v>
+        <v>7.185</v>
       </c>
       <c r="P77" t="n">
-        <v>7.264</v>
+        <v>7.184</v>
       </c>
       <c r="Q77" t="n">
-        <v>7.265</v>
+        <v>7.185</v>
       </c>
       <c r="R77" t="n">
-        <v>7.288</v>
+        <v>7.208</v>
       </c>
       <c r="S77" t="n">
         <v>6.538</v>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y77" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA77" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -9946,19 +9946,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7.235</v>
+        <v>7.155</v>
       </c>
       <c r="F78" t="n">
-        <v>7.228</v>
+        <v>7.148</v>
       </c>
       <c r="G78" t="n">
-        <v>7.253</v>
+        <v>7.173</v>
       </c>
       <c r="H78" t="n">
-        <v>7.228</v>
+        <v>7.148</v>
       </c>
       <c r="I78" t="n">
-        <v>7.235</v>
+        <v>7.155</v>
       </c>
       <c r="J78" t="n">
         <v>6.507</v>
@@ -9976,16 +9976,16 @@
         <v>6.508</v>
       </c>
       <c r="O78" t="n">
-        <v>7.229</v>
+        <v>7.149</v>
       </c>
       <c r="P78" t="n">
-        <v>7.228</v>
+        <v>7.148</v>
       </c>
       <c r="Q78" t="n">
-        <v>7.229</v>
+        <v>7.149</v>
       </c>
       <c r="R78" t="n">
-        <v>7.253</v>
+        <v>7.173</v>
       </c>
       <c r="S78" t="n">
         <v>6.501</v>
@@ -10005,21 +10005,21 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="Y78" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA78" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="AB78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -10724,19 +10724,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="F86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="G86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="H86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="I86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="J86" t="n">
         <v>7.132</v>
@@ -10754,16 +10754,16 @@
         <v>7.132</v>
       </c>
       <c r="O86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="P86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="R86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="S86" t="n">
         <v>7.132</v>
@@ -10783,21 +10783,21 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y86" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA86" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -10823,19 +10823,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="F87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="G87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="H87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="I87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="J87" t="n">
         <v>7.098</v>
@@ -10853,16 +10853,16 @@
         <v>7.098</v>
       </c>
       <c r="O87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="P87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="Q87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="R87" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="S87" t="n">
         <v>7.098</v>
@@ -10882,21 +10882,21 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y87" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA87" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -10922,19 +10922,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="F88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="G88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="H88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="I88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="J88" t="n">
         <v>6.986</v>
@@ -10952,16 +10952,16 @@
         <v>6.986</v>
       </c>
       <c r="O88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="P88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="Q88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="R88" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="S88" t="n">
         <v>6.986</v>
@@ -10981,21 +10981,21 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y88" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA88" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -11021,19 +11021,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="F89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="G89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="H89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="I89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="J89" t="n">
         <v>6.805</v>
@@ -11051,16 +11051,16 @@
         <v>6.805</v>
       </c>
       <c r="O89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="P89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="Q89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="R89" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="S89" t="n">
         <v>6.805</v>
@@ -11080,21 +11080,21 @@
         </is>
       </c>
       <c r="X89" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y89" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA89" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -11120,19 +11120,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="F90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="G90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="H90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="I90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="J90" t="n">
         <v>6.671</v>
@@ -11150,16 +11150,16 @@
         <v>6.671</v>
       </c>
       <c r="O90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="P90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="Q90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="R90" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="S90" t="n">
         <v>6.671</v>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="X90" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y90" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA90" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -11219,19 +11219,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="F91" t="n">
-        <v>5.881</v>
+        <v>5.951</v>
       </c>
       <c r="G91" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="H91" t="n">
-        <v>5.881</v>
+        <v>5.951</v>
       </c>
       <c r="I91" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="J91" t="n">
         <v>6.533</v>
@@ -11249,16 +11249,16 @@
         <v>6.533</v>
       </c>
       <c r="O91" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="P91" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.881</v>
+        <v>5.951</v>
       </c>
       <c r="R91" t="n">
-        <v>5.881</v>
+        <v>5.951</v>
       </c>
       <c r="S91" t="n">
         <v>6.533</v>
@@ -11278,21 +11278,21 @@
         </is>
       </c>
       <c r="X91" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y91" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA91" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -11318,19 +11318,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="F92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="G92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="H92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="I92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="J92" t="n">
         <v>6.402</v>
@@ -11348,16 +11348,16 @@
         <v>6.402</v>
       </c>
       <c r="O92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="P92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="R92" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="S92" t="n">
         <v>6.402</v>
@@ -11377,21 +11377,21 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="Y92" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA92" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="AB92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -11417,19 +11417,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="F93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="G93" t="n">
-        <v>8.042999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="H93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="I93" t="n">
-        <v>8.042999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="J93" t="n">
         <v>7.184</v>
@@ -11447,16 +11447,16 @@
         <v>7.184</v>
       </c>
       <c r="O93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="P93" t="n">
-        <v>8.042999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="Q93" t="n">
-        <v>8.042999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="R93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="S93" t="n">
         <v>7.184</v>
@@ -11476,21 +11476,21 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y93" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA93" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -11516,19 +11516,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="F94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="G94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="H94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="I94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="J94" t="n">
         <v>7.135</v>
@@ -11546,16 +11546,16 @@
         <v>7.135</v>
       </c>
       <c r="O94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="P94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="Q94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="R94" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="S94" t="n">
         <v>7.135</v>
@@ -11575,21 +11575,21 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y94" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA94" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -11615,19 +11615,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="F95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="G95" t="n">
-        <v>7.933</v>
+        <v>7.84</v>
       </c>
       <c r="H95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="I95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="J95" t="n">
         <v>7.074</v>
@@ -11645,16 +11645,16 @@
         <v>7.074</v>
       </c>
       <c r="O95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="P95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="Q95" t="n">
-        <v>7.933</v>
+        <v>7.84</v>
       </c>
       <c r="R95" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="S95" t="n">
         <v>7.074</v>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y95" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA95" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7.87</v>
+        <v>7.777</v>
       </c>
       <c r="F96" t="n">
-        <v>7.869</v>
+        <v>7.777</v>
       </c>
       <c r="G96" t="n">
-        <v>7.871</v>
+        <v>7.778</v>
       </c>
       <c r="H96" t="n">
-        <v>7.87</v>
+        <v>7.777</v>
       </c>
       <c r="I96" t="n">
-        <v>7.87</v>
+        <v>7.778</v>
       </c>
       <c r="J96" t="n">
         <v>7.012</v>
@@ -11744,16 +11744,16 @@
         <v>7.012</v>
       </c>
       <c r="O96" t="n">
-        <v>7.869</v>
+        <v>7.777</v>
       </c>
       <c r="P96" t="n">
-        <v>7.87</v>
+        <v>7.777</v>
       </c>
       <c r="Q96" t="n">
-        <v>7.871</v>
+        <v>7.778</v>
       </c>
       <c r="R96" t="n">
-        <v>7.87</v>
+        <v>7.778</v>
       </c>
       <c r="S96" t="n">
         <v>7.011</v>
@@ -11773,21 +11773,21 @@
         </is>
       </c>
       <c r="X96" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y96" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA96" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -11813,19 +11813,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>7.812</v>
+        <v>7.72</v>
       </c>
       <c r="F97" t="n">
-        <v>7.811</v>
+        <v>7.718</v>
       </c>
       <c r="G97" t="n">
-        <v>7.813</v>
+        <v>7.721</v>
       </c>
       <c r="H97" t="n">
-        <v>7.811</v>
+        <v>7.719</v>
       </c>
       <c r="I97" t="n">
-        <v>7.813</v>
+        <v>7.72</v>
       </c>
       <c r="J97" t="n">
         <v>6.954</v>
@@ -11843,16 +11843,16 @@
         <v>6.954</v>
       </c>
       <c r="O97" t="n">
-        <v>7.811</v>
+        <v>7.718</v>
       </c>
       <c r="P97" t="n">
-        <v>7.811</v>
+        <v>7.719</v>
       </c>
       <c r="Q97" t="n">
-        <v>7.813</v>
+        <v>7.721</v>
       </c>
       <c r="R97" t="n">
-        <v>7.813</v>
+        <v>7.72</v>
       </c>
       <c r="S97" t="n">
         <v>6.952</v>
@@ -11872,21 +11872,21 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y97" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA97" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -11912,19 +11912,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>7.762</v>
+        <v>7.669</v>
       </c>
       <c r="F98" t="n">
-        <v>7.76</v>
+        <v>7.667</v>
       </c>
       <c r="G98" t="n">
-        <v>7.764</v>
+        <v>7.671</v>
       </c>
       <c r="H98" t="n">
-        <v>7.761</v>
+        <v>7.668</v>
       </c>
       <c r="I98" t="n">
-        <v>7.764</v>
+        <v>7.671</v>
       </c>
       <c r="J98" t="n">
         <v>6.904</v>
@@ -11942,16 +11942,16 @@
         <v>6.905</v>
       </c>
       <c r="O98" t="n">
-        <v>7.76</v>
+        <v>7.667</v>
       </c>
       <c r="P98" t="n">
-        <v>7.761</v>
+        <v>7.668</v>
       </c>
       <c r="Q98" t="n">
-        <v>7.764</v>
+        <v>7.671</v>
       </c>
       <c r="R98" t="n">
-        <v>7.763</v>
+        <v>7.671</v>
       </c>
       <c r="S98" t="n">
         <v>6.902</v>
@@ -11971,21 +11971,21 @@
         </is>
       </c>
       <c r="X98" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y98" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA98" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -12011,19 +12011,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7.719</v>
+        <v>7.626</v>
       </c>
       <c r="F99" t="n">
-        <v>7.716</v>
+        <v>7.623</v>
       </c>
       <c r="G99" t="n">
-        <v>7.722</v>
+        <v>7.63</v>
       </c>
       <c r="H99" t="n">
-        <v>7.717</v>
+        <v>7.624</v>
       </c>
       <c r="I99" t="n">
-        <v>7.721</v>
+        <v>7.629</v>
       </c>
       <c r="J99" t="n">
         <v>6.861</v>
@@ -12041,16 +12041,16 @@
         <v>6.863</v>
       </c>
       <c r="O99" t="n">
-        <v>7.716</v>
+        <v>7.623</v>
       </c>
       <c r="P99" t="n">
-        <v>7.717</v>
+        <v>7.624</v>
       </c>
       <c r="Q99" t="n">
-        <v>7.721</v>
+        <v>7.628</v>
       </c>
       <c r="R99" t="n">
-        <v>7.722</v>
+        <v>7.63</v>
       </c>
       <c r="S99" t="n">
         <v>6.857</v>
@@ -12070,21 +12070,21 @@
         </is>
       </c>
       <c r="X99" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="Y99" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA99" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="AB99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -12110,19 +12110,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="F100" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="G100" t="n">
-        <v>4.412</v>
+        <v>4.392</v>
       </c>
       <c r="H100" t="n">
-        <v>4.394</v>
+        <v>4.374</v>
       </c>
       <c r="I100" t="n">
-        <v>4.405</v>
+        <v>4.385</v>
       </c>
       <c r="J100" t="n">
         <v>5.231</v>
@@ -12140,16 +12140,16 @@
         <v>5.236</v>
       </c>
       <c r="O100" t="n">
-        <v>4.403</v>
+        <v>4.383</v>
       </c>
       <c r="P100" t="n">
-        <v>4.412</v>
+        <v>4.392</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.396</v>
+        <v>4.376</v>
       </c>
       <c r="R100" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="S100" t="n">
         <v>5.234</v>
@@ -12169,21 +12169,21 @@
         </is>
       </c>
       <c r="X100" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y100" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA100" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -12209,19 +12209,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4.126</v>
+        <v>4.106</v>
       </c>
       <c r="F101" t="n">
-        <v>4.052</v>
+        <v>4.032</v>
       </c>
       <c r="G101" t="n">
-        <v>4.197</v>
+        <v>4.177</v>
       </c>
       <c r="H101" t="n">
-        <v>4.098</v>
+        <v>4.078</v>
       </c>
       <c r="I101" t="n">
-        <v>4.155</v>
+        <v>4.135</v>
       </c>
       <c r="J101" t="n">
         <v>4.957</v>
@@ -12239,16 +12239,16 @@
         <v>4.986</v>
       </c>
       <c r="O101" t="n">
-        <v>4.141</v>
+        <v>4.121</v>
       </c>
       <c r="P101" t="n">
-        <v>4.197</v>
+        <v>4.177</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.114</v>
+        <v>4.094</v>
       </c>
       <c r="R101" t="n">
-        <v>4.052</v>
+        <v>4.032</v>
       </c>
       <c r="S101" t="n">
         <v>4.972</v>
@@ -12268,21 +12268,21 @@
         </is>
       </c>
       <c r="X101" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y101" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA101" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
@@ -12308,19 +12308,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.058</v>
+        <v>4.038</v>
       </c>
       <c r="F102" t="n">
-        <v>3.853</v>
+        <v>3.833</v>
       </c>
       <c r="G102" t="n">
-        <v>4.242</v>
+        <v>4.222</v>
       </c>
       <c r="H102" t="n">
-        <v>3.996</v>
+        <v>3.976</v>
       </c>
       <c r="I102" t="n">
-        <v>4.131</v>
+        <v>4.111</v>
       </c>
       <c r="J102" t="n">
         <v>4.89</v>
@@ -12338,16 +12338,16 @@
         <v>4.963</v>
       </c>
       <c r="O102" t="n">
-        <v>4.094</v>
+        <v>4.074</v>
       </c>
       <c r="P102" t="n">
-        <v>4.242</v>
+        <v>4.222</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.043</v>
+        <v>4.023</v>
       </c>
       <c r="R102" t="n">
-        <v>3.853</v>
+        <v>3.833</v>
       </c>
       <c r="S102" t="n">
         <v>4.926</v>
@@ -12367,21 +12367,21 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y102" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA102" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -12407,19 +12407,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4.196</v>
+        <v>4.176</v>
       </c>
       <c r="F103" t="n">
-        <v>3.836</v>
+        <v>3.816</v>
       </c>
       <c r="G103" t="n">
-        <v>4.448</v>
+        <v>4.428</v>
       </c>
       <c r="H103" t="n">
-        <v>4.103</v>
+        <v>4.083</v>
       </c>
       <c r="I103" t="n">
-        <v>4.345</v>
+        <v>4.325</v>
       </c>
       <c r="J103" t="n">
         <v>5.028</v>
@@ -12437,16 +12437,16 @@
         <v>5.176</v>
       </c>
       <c r="O103" t="n">
-        <v>4.192</v>
+        <v>4.172</v>
       </c>
       <c r="P103" t="n">
-        <v>4.448</v>
+        <v>4.428</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="R103" t="n">
-        <v>3.836</v>
+        <v>3.816</v>
       </c>
       <c r="S103" t="n">
         <v>5.023</v>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y103" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA103" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -12506,19 +12506,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4.624</v>
+        <v>4.604</v>
       </c>
       <c r="F104" t="n">
-        <v>4.333</v>
+        <v>4.313</v>
       </c>
       <c r="G104" t="n">
-        <v>4.778</v>
+        <v>4.758</v>
       </c>
       <c r="H104" t="n">
-        <v>4.601</v>
+        <v>4.581</v>
       </c>
       <c r="I104" t="n">
-        <v>4.716</v>
+        <v>4.696</v>
       </c>
       <c r="J104" t="n">
         <v>5.456</v>
@@ -12536,16 +12536,16 @@
         <v>5.547</v>
       </c>
       <c r="O104" t="n">
-        <v>4.333</v>
+        <v>4.313</v>
       </c>
       <c r="P104" t="n">
-        <v>4.696</v>
+        <v>4.676</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.778</v>
+        <v>4.758</v>
       </c>
       <c r="R104" t="n">
-        <v>4.691</v>
+        <v>4.671</v>
       </c>
       <c r="S104" t="n">
         <v>5.165</v>
@@ -12565,21 +12565,21 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y104" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA104" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
@@ -12605,19 +12605,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5.053</v>
+        <v>5.033</v>
       </c>
       <c r="F105" t="n">
-        <v>4.445</v>
+        <v>4.425</v>
       </c>
       <c r="G105" t="n">
-        <v>5.724</v>
+        <v>5.704</v>
       </c>
       <c r="H105" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="I105" t="n">
-        <v>5.286</v>
+        <v>5.266</v>
       </c>
       <c r="J105" t="n">
         <v>5.885</v>
@@ -12635,16 +12635,16 @@
         <v>6.117</v>
       </c>
       <c r="O105" t="n">
-        <v>4.445</v>
+        <v>4.425</v>
       </c>
       <c r="P105" t="n">
-        <v>4.905</v>
+        <v>4.885</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="R105" t="n">
-        <v>5.724</v>
+        <v>5.704</v>
       </c>
       <c r="S105" t="n">
         <v>5.277</v>
@@ -12664,21 +12664,21 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y105" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA105" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
@@ -12704,19 +12704,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.155</v>
+        <v>5.135</v>
       </c>
       <c r="F106" t="n">
-        <v>4.397</v>
+        <v>4.377</v>
       </c>
       <c r="G106" t="n">
-        <v>6.038</v>
+        <v>6.018</v>
       </c>
       <c r="H106" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="I106" t="n">
-        <v>5.478</v>
+        <v>5.458</v>
       </c>
       <c r="J106" t="n">
         <v>5.987</v>
@@ -12734,16 +12734,16 @@
         <v>6.31</v>
       </c>
       <c r="O106" t="n">
-        <v>4.397</v>
+        <v>4.377</v>
       </c>
       <c r="P106" t="n">
-        <v>4.894</v>
+        <v>4.874</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.292</v>
+        <v>5.272</v>
       </c>
       <c r="R106" t="n">
-        <v>6.038</v>
+        <v>6.018</v>
       </c>
       <c r="S106" t="n">
         <v>5.228</v>
@@ -12763,21 +12763,21 @@
         </is>
       </c>
       <c r="X106" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="Y106" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA106" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="AB106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -12803,19 +12803,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="F107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="G107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="H107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="I107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="J107" t="n">
         <v>5.144</v>
@@ -12833,16 +12833,16 @@
         <v>5.144</v>
       </c>
       <c r="O107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="P107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="Q107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="R107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="S107" t="n">
         <v>5.144</v>
@@ -12862,21 +12862,21 @@
         </is>
       </c>
       <c r="X107" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y107" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA107" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
@@ -12902,19 +12902,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="F108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="G108" t="n">
-        <v>5.558</v>
+        <v>5.411</v>
       </c>
       <c r="H108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="I108" t="n">
-        <v>5.558</v>
+        <v>5.411</v>
       </c>
       <c r="J108" t="n">
         <v>4.994</v>
@@ -12932,16 +12932,16 @@
         <v>4.994</v>
       </c>
       <c r="O108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="P108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.558</v>
+        <v>5.411</v>
       </c>
       <c r="R108" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="S108" t="n">
         <v>4.994</v>
@@ -12961,21 +12961,21 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y108" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA108" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -13001,19 +13001,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="F109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="G109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="H109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="I109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="J109" t="n">
         <v>4.846</v>
@@ -13031,16 +13031,16 @@
         <v>4.846</v>
       </c>
       <c r="O109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="P109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="R109" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="S109" t="n">
         <v>4.846</v>
@@ -13060,21 +13060,21 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y109" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA109" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -13100,19 +13100,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5.331</v>
+        <v>5.184</v>
       </c>
       <c r="F110" t="n">
-        <v>5.326</v>
+        <v>5.178</v>
       </c>
       <c r="G110" t="n">
-        <v>5.334</v>
+        <v>5.187</v>
       </c>
       <c r="H110" t="n">
-        <v>5.33</v>
+        <v>5.183</v>
       </c>
       <c r="I110" t="n">
-        <v>5.334</v>
+        <v>5.186</v>
       </c>
       <c r="J110" t="n">
         <v>4.768</v>
@@ -13130,16 +13130,16 @@
         <v>4.77</v>
       </c>
       <c r="O110" t="n">
-        <v>5.332</v>
+        <v>5.184</v>
       </c>
       <c r="P110" t="n">
-        <v>5.334</v>
+        <v>5.187</v>
       </c>
       <c r="Q110" t="n">
-        <v>5.334</v>
+        <v>5.186</v>
       </c>
       <c r="R110" t="n">
-        <v>5.326</v>
+        <v>5.178</v>
       </c>
       <c r="S110" t="n">
         <v>4.768</v>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y110" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA110" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -13199,19 +13199,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5.295</v>
+        <v>5.147</v>
       </c>
       <c r="F111" t="n">
-        <v>5.292</v>
+        <v>5.144</v>
       </c>
       <c r="G111" t="n">
-        <v>5.299</v>
+        <v>5.151</v>
       </c>
       <c r="H111" t="n">
-        <v>5.292</v>
+        <v>5.144</v>
       </c>
       <c r="I111" t="n">
-        <v>5.297</v>
+        <v>5.149</v>
       </c>
       <c r="J111" t="n">
         <v>4.731</v>
@@ -13229,16 +13229,16 @@
         <v>4.733</v>
       </c>
       <c r="O111" t="n">
-        <v>5.292</v>
+        <v>5.144</v>
       </c>
       <c r="P111" t="n">
-        <v>5.296</v>
+        <v>5.149</v>
       </c>
       <c r="Q111" t="n">
-        <v>5.299</v>
+        <v>5.151</v>
       </c>
       <c r="R111" t="n">
-        <v>5.292</v>
+        <v>5.144</v>
       </c>
       <c r="S111" t="n">
         <v>4.728</v>
@@ -13258,21 +13258,21 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y111" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA111" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
@@ -13298,19 +13298,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5.311</v>
+        <v>5.163</v>
       </c>
       <c r="F112" t="n">
-        <v>5.299</v>
+        <v>5.151</v>
       </c>
       <c r="G112" t="n">
-        <v>5.315</v>
+        <v>5.167</v>
       </c>
       <c r="H112" t="n">
-        <v>5.311</v>
+        <v>5.163</v>
       </c>
       <c r="I112" t="n">
-        <v>5.315</v>
+        <v>5.167</v>
       </c>
       <c r="J112" t="n">
         <v>4.747</v>
@@ -13328,16 +13328,16 @@
         <v>4.751</v>
       </c>
       <c r="O112" t="n">
-        <v>5.315</v>
+        <v>5.167</v>
       </c>
       <c r="P112" t="n">
-        <v>5.315</v>
+        <v>5.167</v>
       </c>
       <c r="Q112" t="n">
-        <v>5.315</v>
+        <v>5.167</v>
       </c>
       <c r="R112" t="n">
-        <v>5.299</v>
+        <v>5.151</v>
       </c>
       <c r="S112" t="n">
         <v>4.751</v>
@@ -13357,21 +13357,21 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y112" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA112" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -13397,19 +13397,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5.379</v>
+        <v>5.231</v>
       </c>
       <c r="F113" t="n">
-        <v>5.335</v>
+        <v>5.187</v>
       </c>
       <c r="G113" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="H113" t="n">
-        <v>5.369</v>
+        <v>5.222</v>
       </c>
       <c r="I113" t="n">
-        <v>5.395</v>
+        <v>5.247</v>
       </c>
       <c r="J113" t="n">
         <v>4.815</v>
@@ -13427,16 +13427,16 @@
         <v>4.831</v>
       </c>
       <c r="O113" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="P113" t="n">
-        <v>5.381</v>
+        <v>5.234</v>
       </c>
       <c r="Q113" t="n">
-        <v>5.39</v>
+        <v>5.242</v>
       </c>
       <c r="R113" t="n">
-        <v>5.335</v>
+        <v>5.187</v>
       </c>
       <c r="S113" t="n">
         <v>4.846</v>
@@ -13456,21 +13456,21 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="Y113" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA113" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -13496,19 +13496,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="F114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="G114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="H114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="I114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="J114" t="n">
         <v>3.665</v>
@@ -13526,16 +13526,16 @@
         <v>3.665</v>
       </c>
       <c r="O114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="P114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="R114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="S114" t="n">
         <v>3.665</v>
@@ -13555,21 +13555,21 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y114" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA114" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -13595,19 +13595,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="F115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="G115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="H115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="I115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="J115" t="n">
         <v>3.711</v>
@@ -13625,16 +13625,16 @@
         <v>3.711</v>
       </c>
       <c r="O115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="P115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="R115" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="S115" t="n">
         <v>3.711</v>
@@ -13654,21 +13654,21 @@
         </is>
       </c>
       <c r="X115" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y115" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA115" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -13694,19 +13694,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="F116" t="n">
-        <v>3.716</v>
+        <v>3.696</v>
       </c>
       <c r="G116" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="H116" t="n">
-        <v>3.716</v>
+        <v>3.696</v>
       </c>
       <c r="I116" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="J116" t="n">
         <v>3.722</v>
@@ -13724,16 +13724,16 @@
         <v>3.722</v>
       </c>
       <c r="O116" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="P116" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.716</v>
+        <v>3.696</v>
       </c>
       <c r="R116" t="n">
-        <v>3.716</v>
+        <v>3.696</v>
       </c>
       <c r="S116" t="n">
         <v>3.722</v>
@@ -13753,21 +13753,21 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y116" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA116" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -13793,19 +13793,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="F117" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="G117" t="n">
-        <v>3.674</v>
+        <v>3.654</v>
       </c>
       <c r="H117" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="I117" t="n">
-        <v>3.674</v>
+        <v>3.654</v>
       </c>
       <c r="J117" t="n">
         <v>3.679</v>
@@ -13823,16 +13823,16 @@
         <v>3.679</v>
       </c>
       <c r="O117" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="P117" t="n">
-        <v>3.674</v>
+        <v>3.654</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.674</v>
+        <v>3.654</v>
       </c>
       <c r="R117" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="S117" t="n">
         <v>3.679</v>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y117" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA117" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -13892,19 +13892,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="F118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="G118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="H118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="I118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="J118" t="n">
         <v>3.622</v>
@@ -13922,16 +13922,16 @@
         <v>3.622</v>
       </c>
       <c r="O118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="P118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="R118" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="S118" t="n">
         <v>3.622</v>
@@ -13951,21 +13951,21 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y118" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA118" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
@@ -13991,19 +13991,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3.397</v>
+        <v>3.377</v>
       </c>
       <c r="F119" t="n">
-        <v>3.393</v>
+        <v>3.373</v>
       </c>
       <c r="G119" t="n">
-        <v>3.398</v>
+        <v>3.378</v>
       </c>
       <c r="H119" t="n">
-        <v>3.397</v>
+        <v>3.377</v>
       </c>
       <c r="I119" t="n">
-        <v>3.398</v>
+        <v>3.378</v>
       </c>
       <c r="J119" t="n">
         <v>3.402</v>
@@ -14021,16 +14021,16 @@
         <v>3.403</v>
       </c>
       <c r="O119" t="n">
-        <v>3.393</v>
+        <v>3.373</v>
       </c>
       <c r="P119" t="n">
-        <v>3.398</v>
+        <v>3.378</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.398</v>
+        <v>3.378</v>
       </c>
       <c r="R119" t="n">
-        <v>3.398</v>
+        <v>3.378</v>
       </c>
       <c r="S119" t="n">
         <v>3.398</v>
@@ -14050,21 +14050,21 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y119" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA119" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
@@ -14090,19 +14090,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3.203</v>
+        <v>3.183</v>
       </c>
       <c r="F120" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="G120" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="H120" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="I120" t="n">
-        <v>3.203</v>
+        <v>3.183</v>
       </c>
       <c r="J120" t="n">
         <v>3.208</v>
@@ -14120,16 +14120,16 @@
         <v>3.208</v>
       </c>
       <c r="O120" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="P120" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.201</v>
+        <v>3.181</v>
       </c>
       <c r="R120" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="S120" t="n">
         <v>3.206</v>
@@ -14149,21 +14149,21 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="Y120" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="AA120" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="AB120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
@@ -14242,25 +14242,25 @@
         <v>9043370</v>
       </c>
       <c r="C2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="D2" t="n">
-        <v>2.027</v>
+        <v>2.197</v>
       </c>
       <c r="E2" t="n">
-        <v>2.005</v>
+        <v>2.175</v>
       </c>
       <c r="F2" t="n">
-        <v>1.983</v>
+        <v>2.153</v>
       </c>
       <c r="G2" t="n">
-        <v>1.963</v>
+        <v>2.133</v>
       </c>
       <c r="H2" t="n">
-        <v>2.016</v>
+        <v>2.186</v>
       </c>
       <c r="I2" t="n">
-        <v>2.058</v>
+        <v>2.228</v>
       </c>
     </row>
     <row r="3">
@@ -14273,25 +14273,25 @@
         <v>9036028</v>
       </c>
       <c r="C3" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="D3" t="n">
-        <v>5.646</v>
+        <v>5.606</v>
       </c>
       <c r="E3" t="n">
-        <v>5.634</v>
+        <v>5.594</v>
       </c>
       <c r="F3" t="n">
-        <v>5.597</v>
+        <v>5.557</v>
       </c>
       <c r="G3" t="n">
-        <v>5.535</v>
+        <v>5.495</v>
       </c>
       <c r="H3" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="I3" t="n">
-        <v>5.421</v>
+        <v>5.381</v>
       </c>
     </row>
     <row r="4">
@@ -14304,25 +14304,25 @@
         <v>9040208</v>
       </c>
       <c r="C4" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3.753</v>
       </c>
       <c r="E4" t="n">
-        <v>3.92</v>
+        <v>3.673</v>
       </c>
       <c r="F4" t="n">
-        <v>3.905</v>
+        <v>3.658</v>
       </c>
       <c r="G4" t="n">
-        <v>3.947</v>
+        <v>3.699</v>
       </c>
       <c r="H4" t="n">
-        <v>4.038</v>
+        <v>3.791</v>
       </c>
       <c r="I4" t="n">
-        <v>4.125</v>
+        <v>3.877</v>
       </c>
     </row>
     <row r="5">
@@ -14335,25 +14335,25 @@
         <v>9053555</v>
       </c>
       <c r="C5" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="D5" t="n">
-        <v>6.906</v>
+        <v>6.776</v>
       </c>
       <c r="E5" t="n">
-        <v>6.834</v>
+        <v>6.704</v>
       </c>
       <c r="F5" t="n">
-        <v>6.726</v>
+        <v>6.596</v>
       </c>
       <c r="G5" t="n">
-        <v>6.627</v>
+        <v>6.497</v>
       </c>
       <c r="H5" t="n">
-        <v>6.535</v>
+        <v>6.405</v>
       </c>
       <c r="I5" t="n">
-        <v>6.439</v>
+        <v>6.309</v>
       </c>
     </row>
     <row r="6">
@@ -14366,25 +14366,25 @@
         <v>9038134</v>
       </c>
       <c r="C6" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="D6" t="n">
-        <v>2.155</v>
+        <v>2.025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.916</v>
+        <v>-1.046</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.995</v>
+        <v>-3.125</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.95</v>
+        <v>-4.08</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.927</v>
+        <v>-4.057</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.872</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="7">
@@ -14459,25 +14459,25 @@
         <v>9043597</v>
       </c>
       <c r="C9" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="D9" t="n">
-        <v>5.515</v>
+        <v>5.463</v>
       </c>
       <c r="E9" t="n">
-        <v>5.501</v>
+        <v>5.448</v>
       </c>
       <c r="F9" t="n">
-        <v>5.529</v>
+        <v>5.477</v>
       </c>
       <c r="G9" t="n">
-        <v>5.546</v>
+        <v>5.494</v>
       </c>
       <c r="H9" t="n">
-        <v>5.514</v>
+        <v>5.462</v>
       </c>
       <c r="I9" t="n">
-        <v>5.435</v>
+        <v>5.382</v>
       </c>
     </row>
     <row r="10">
@@ -14490,25 +14490,25 @@
         <v>9040454</v>
       </c>
       <c r="C10" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="D10" t="n">
-        <v>7.952</v>
+        <v>8.012</v>
       </c>
       <c r="E10" t="n">
-        <v>7.923</v>
+        <v>7.983</v>
       </c>
       <c r="F10" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
       <c r="G10" t="n">
-        <v>7.732</v>
+        <v>7.792</v>
       </c>
       <c r="H10" t="n">
-        <v>7.585</v>
+        <v>7.645</v>
       </c>
       <c r="I10" t="n">
-        <v>7.45</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="11">
@@ -14552,25 +14552,25 @@
         <v>9043425</v>
       </c>
       <c r="C12" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="D12" t="n">
-        <v>7.415</v>
+        <v>7.335</v>
       </c>
       <c r="E12" t="n">
-        <v>7.377</v>
+        <v>7.297</v>
       </c>
       <c r="F12" t="n">
-        <v>7.339</v>
+        <v>7.259</v>
       </c>
       <c r="G12" t="n">
-        <v>7.304</v>
+        <v>7.224</v>
       </c>
       <c r="H12" t="n">
-        <v>7.271</v>
+        <v>7.191</v>
       </c>
       <c r="I12" t="n">
-        <v>7.235</v>
+        <v>7.155</v>
       </c>
     </row>
     <row r="13">
@@ -14614,25 +14614,25 @@
         <v>9040439</v>
       </c>
       <c r="C14" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="D14" t="n">
-        <v>6.446</v>
+        <v>6.516</v>
       </c>
       <c r="E14" t="n">
-        <v>6.335</v>
+        <v>6.405</v>
       </c>
       <c r="F14" t="n">
-        <v>6.154</v>
+        <v>6.224</v>
       </c>
       <c r="G14" t="n">
-        <v>6.019</v>
+        <v>6.089</v>
       </c>
       <c r="H14" t="n">
-        <v>5.882</v>
+        <v>5.952</v>
       </c>
       <c r="I14" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="15">
@@ -14645,25 +14645,25 @@
         <v>9032282</v>
       </c>
       <c r="C15" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="D15" t="n">
-        <v>7.993</v>
+        <v>7.9</v>
       </c>
       <c r="E15" t="n">
-        <v>7.932</v>
+        <v>7.84</v>
       </c>
       <c r="F15" t="n">
-        <v>7.87</v>
+        <v>7.777</v>
       </c>
       <c r="G15" t="n">
-        <v>7.812</v>
+        <v>7.72</v>
       </c>
       <c r="H15" t="n">
-        <v>7.762</v>
+        <v>7.669</v>
       </c>
       <c r="I15" t="n">
-        <v>7.719</v>
+        <v>7.626</v>
       </c>
     </row>
     <row r="16">
@@ -14676,25 +14676,25 @@
         <v>9037738</v>
       </c>
       <c r="C16" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="D16" t="n">
-        <v>4.126</v>
+        <v>4.106</v>
       </c>
       <c r="E16" t="n">
-        <v>4.058</v>
+        <v>4.038</v>
       </c>
       <c r="F16" t="n">
-        <v>4.196</v>
+        <v>4.176</v>
       </c>
       <c r="G16" t="n">
-        <v>4.624</v>
+        <v>4.604</v>
       </c>
       <c r="H16" t="n">
-        <v>5.053</v>
+        <v>5.033</v>
       </c>
       <c r="I16" t="n">
-        <v>5.155</v>
+        <v>5.135</v>
       </c>
     </row>
     <row r="17">
@@ -14707,25 +14707,25 @@
         <v>9039635</v>
       </c>
       <c r="C17" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="D17" t="n">
-        <v>5.558</v>
+        <v>5.41</v>
       </c>
       <c r="E17" t="n">
-        <v>5.41</v>
+        <v>5.262</v>
       </c>
       <c r="F17" t="n">
-        <v>5.331</v>
+        <v>5.184</v>
       </c>
       <c r="G17" t="n">
-        <v>5.295</v>
+        <v>5.147</v>
       </c>
       <c r="H17" t="n">
-        <v>5.311</v>
+        <v>5.163</v>
       </c>
       <c r="I17" t="n">
-        <v>5.379</v>
+        <v>5.231</v>
       </c>
     </row>
     <row r="18">
@@ -14738,25 +14738,25 @@
         <v>9038269</v>
       </c>
       <c r="C18" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="D18" t="n">
-        <v>3.706</v>
+        <v>3.686</v>
       </c>
       <c r="E18" t="n">
-        <v>3.717</v>
+        <v>3.697</v>
       </c>
       <c r="F18" t="n">
-        <v>3.673</v>
+        <v>3.653</v>
       </c>
       <c r="G18" t="n">
-        <v>3.617</v>
+        <v>3.597</v>
       </c>
       <c r="H18" t="n">
-        <v>3.397</v>
+        <v>3.377</v>
       </c>
       <c r="I18" t="n">
-        <v>3.203</v>
+        <v>3.183</v>
       </c>
     </row>
   </sheetData>
@@ -14848,25 +14848,25 @@
         <v>46241</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E2" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="F2" t="n">
         <v>7.184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.858</v>
+        <v>0.766</v>
       </c>
       <c r="H2" t="n">
-        <v>8.042</v>
+        <v>7.95</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -14892,25 +14892,25 @@
         <v>46241</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E3" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="F3" t="n">
         <v>6.22</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="H3" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -14976,25 +14976,25 @@
         <v>46241</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="F5" t="n">
         <v>5.231</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.831</v>
+        <v>-0.851</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -15020,25 +15020,25 @@
         <v>46241</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E6" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F6" t="n">
         <v>105.501</v>
       </c>
       <c r="G6" t="n">
-        <v>-99.441</v>
+        <v>-99.571</v>
       </c>
       <c r="H6" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Offset alto: -99.44 m. Revisar estación.</t>
+          <t>Offset alto: -99.57 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -15064,25 +15064,25 @@
         <v>46241</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="F7" t="n">
         <v>3.665</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="H7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -15108,25 +15108,25 @@
         <v>46241</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E8" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="F8" t="n">
         <v>5.144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="H8" t="n">
-        <v>5.708</v>
+        <v>5.56</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -15152,25 +15152,25 @@
         <v>46241</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E9" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="F9" t="n">
         <v>4.724</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.626</v>
+        <v>-0.874</v>
       </c>
       <c r="H9" t="n">
-        <v>4.097</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -15196,25 +15196,25 @@
         <v>46241</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E10" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="F10" t="n">
         <v>7.132</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.652</v>
+        <v>-0.582</v>
       </c>
       <c r="H10" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -15240,25 +15240,25 @@
         <v>46241</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E11" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="F11" t="n">
         <v>6.347</v>
       </c>
       <c r="G11" t="n">
-        <v>1.583</v>
+        <v>1.643</v>
       </c>
       <c r="H11" t="n">
-        <v>7.93</v>
+        <v>7.99</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Offset alto: 1.58 m. Revisar estación.</t>
+          <t>Offset alto: 1.64 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -15368,25 +15368,25 @@
         <v>46241</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E14" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="F14" t="n">
         <v>8.179</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.129</v>
+        <v>-5.959</v>
       </c>
       <c r="H14" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Offset alto: -6.13 m. Revisar estación.</t>
+          <t>Offset alto: -5.96 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -15412,25 +15412,25 @@
         <v>46241</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E15" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="F15" t="n">
         <v>6.723</v>
       </c>
       <c r="G15" t="n">
-        <v>0.727</v>
+        <v>0.647</v>
       </c>
       <c r="H15" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -15456,25 +15456,25 @@
         <v>46241</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E16" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="F16" t="n">
         <v>5.401</v>
       </c>
       <c r="G16" t="n">
-        <v>0.201</v>
+        <v>0.149</v>
       </c>
       <c r="H16" t="n">
-        <v>5.602</v>
+        <v>5.55</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -15540,25 +15540,25 @@
         <v>46241</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E18" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="F18" t="n">
         <v>12.117</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.137</v>
+        <v>-5.267</v>
       </c>
       <c r="H18" t="n">
-        <v>6.98</v>
+        <v>6.85</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Offset alto: -5.14 m. Revisar estación.</t>
+          <t>Offset alto: -5.27 m. Revisar estación.</t>
         </is>
       </c>
     </row>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1493,22 +1493,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.667</v>
+        <v>0.266</v>
       </c>
       <c r="H11" t="n">
-        <v>4.301</v>
+        <v>1.742</v>
       </c>
       <c r="I11" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="J11" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.284</v>
+        <v>0.793</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.078</v>
+        <v>-1.957</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1517,43 +1517,45 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="P11" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="S11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>2305</v>
+        <v>2349</v>
       </c>
       <c r="V11" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.518</v>
       </c>
-      <c r="W11" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.515</v>
-      </c>
       <c r="Y11" t="n">
-        <v>2.58</v>
+        <v>2.566</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -2266,6 +2268,107 @@
         </is>
       </c>
       <c r="AA18" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>5.795</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.821</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.919</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>2690</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Buena</t>
         </is>
@@ -2282,7 +2385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC120"/>
+  <dimension ref="A1:AC127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8673,82 +8776,84 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="F65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="G65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="H65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="I65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="J65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="K65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="L65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="M65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="N65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="O65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="P65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="R65" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="S65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="T65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="U65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="V65" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y65" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA65" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB65" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8770,82 +8875,84 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.18</v>
+        <v>2.618</v>
       </c>
       <c r="F66" t="n">
-        <v>5.176</v>
+        <v>2.616</v>
       </c>
       <c r="G66" t="n">
-        <v>5.187</v>
+        <v>2.622</v>
       </c>
       <c r="H66" t="n">
-        <v>5.177</v>
+        <v>2.617</v>
       </c>
       <c r="I66" t="n">
-        <v>5.181</v>
+        <v>2.619</v>
       </c>
       <c r="J66" t="n">
-        <v>5.18</v>
+        <v>5.069</v>
       </c>
       <c r="K66" t="n">
-        <v>5.176</v>
+        <v>5.068</v>
       </c>
       <c r="L66" t="n">
-        <v>5.187</v>
+        <v>5.073</v>
       </c>
       <c r="M66" t="n">
-        <v>5.177</v>
+        <v>5.068</v>
       </c>
       <c r="N66" t="n">
-        <v>5.181</v>
+        <v>5.07</v>
       </c>
       <c r="O66" t="n">
-        <v>5.18</v>
+        <v>2.618</v>
       </c>
       <c r="P66" t="n">
-        <v>5.187</v>
+        <v>2.622</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.177</v>
+        <v>2.617</v>
       </c>
       <c r="R66" t="n">
-        <v>5.176</v>
+        <v>2.616</v>
       </c>
       <c r="S66" t="n">
-        <v>5.18</v>
+        <v>5.069</v>
       </c>
       <c r="T66" t="n">
-        <v>5.187</v>
+        <v>5.073</v>
       </c>
       <c r="U66" t="n">
-        <v>5.177</v>
+        <v>5.068</v>
       </c>
       <c r="V66" t="n">
-        <v>5.176</v>
+        <v>5.068</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y66" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA66" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8867,82 +8974,84 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.878</v>
+        <v>2.36</v>
       </c>
       <c r="F67" t="n">
-        <v>4.861</v>
+        <v>2.332</v>
       </c>
       <c r="G67" t="n">
-        <v>4.896</v>
+        <v>2.381</v>
       </c>
       <c r="H67" t="n">
-        <v>4.866</v>
+        <v>2.354</v>
       </c>
       <c r="I67" t="n">
-        <v>4.889</v>
+        <v>2.37</v>
       </c>
       <c r="J67" t="n">
-        <v>4.878</v>
+        <v>4.811</v>
       </c>
       <c r="K67" t="n">
-        <v>4.861</v>
+        <v>4.783</v>
       </c>
       <c r="L67" t="n">
-        <v>4.896</v>
+        <v>4.832</v>
       </c>
       <c r="M67" t="n">
-        <v>4.866</v>
+        <v>4.805</v>
       </c>
       <c r="N67" t="n">
-        <v>4.889</v>
+        <v>4.821</v>
       </c>
       <c r="O67" t="n">
-        <v>4.886</v>
+        <v>2.366</v>
       </c>
       <c r="P67" t="n">
-        <v>4.896</v>
+        <v>2.381</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.868</v>
+        <v>2.361</v>
       </c>
       <c r="R67" t="n">
-        <v>4.861</v>
+        <v>2.332</v>
       </c>
       <c r="S67" t="n">
-        <v>4.886</v>
+        <v>4.817</v>
       </c>
       <c r="T67" t="n">
-        <v>4.896</v>
+        <v>4.832</v>
       </c>
       <c r="U67" t="n">
-        <v>4.868</v>
+        <v>4.812</v>
       </c>
       <c r="V67" t="n">
-        <v>4.861</v>
+        <v>4.783</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y67" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA67" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB67" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -8964,82 +9073,84 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.296</v>
+        <v>1.665</v>
       </c>
       <c r="F68" t="n">
-        <v>4.166</v>
+        <v>1.539</v>
       </c>
       <c r="G68" t="n">
-        <v>4.419</v>
+        <v>1.807</v>
       </c>
       <c r="H68" t="n">
-        <v>4.23</v>
+        <v>1.585</v>
       </c>
       <c r="I68" t="n">
-        <v>4.365</v>
+        <v>1.738</v>
       </c>
       <c r="J68" t="n">
-        <v>4.296</v>
+        <v>4.117</v>
       </c>
       <c r="K68" t="n">
-        <v>4.166</v>
+        <v>3.99</v>
       </c>
       <c r="L68" t="n">
-        <v>4.419</v>
+        <v>4.258</v>
       </c>
       <c r="M68" t="n">
-        <v>4.23</v>
+        <v>4.036</v>
       </c>
       <c r="N68" t="n">
-        <v>4.365</v>
+        <v>4.19</v>
       </c>
       <c r="O68" t="n">
-        <v>4.347</v>
+        <v>1.715</v>
       </c>
       <c r="P68" t="n">
-        <v>4.419</v>
+        <v>1.807</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.251</v>
+        <v>1.6</v>
       </c>
       <c r="R68" t="n">
-        <v>4.166</v>
+        <v>1.539</v>
       </c>
       <c r="S68" t="n">
-        <v>4.347</v>
+        <v>4.167</v>
       </c>
       <c r="T68" t="n">
-        <v>4.419</v>
+        <v>4.258</v>
       </c>
       <c r="U68" t="n">
-        <v>4.251</v>
+        <v>4.051</v>
       </c>
       <c r="V68" t="n">
-        <v>4.166</v>
+        <v>3.99</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y68" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA68" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB68" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -9061,82 +9172,84 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3.731</v>
+        <v>1.17</v>
       </c>
       <c r="F69" t="n">
-        <v>3.519</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>3.979</v>
+        <v>1.387</v>
       </c>
       <c r="H69" t="n">
-        <v>3.593</v>
+        <v>1.051</v>
       </c>
       <c r="I69" t="n">
-        <v>3.851</v>
+        <v>1.298</v>
       </c>
       <c r="J69" t="n">
-        <v>3.731</v>
+        <v>3.621</v>
       </c>
       <c r="K69" t="n">
-        <v>3.519</v>
+        <v>3.387</v>
       </c>
       <c r="L69" t="n">
-        <v>3.979</v>
+        <v>3.838</v>
       </c>
       <c r="M69" t="n">
-        <v>3.593</v>
+        <v>3.502</v>
       </c>
       <c r="N69" t="n">
-        <v>3.851</v>
+        <v>3.749</v>
       </c>
       <c r="O69" t="n">
-        <v>3.808</v>
+        <v>1.268</v>
       </c>
       <c r="P69" t="n">
-        <v>3.979</v>
+        <v>1.387</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.617</v>
+        <v>1.09</v>
       </c>
       <c r="R69" t="n">
-        <v>3.519</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="S69" t="n">
-        <v>3.808</v>
+        <v>3.719</v>
       </c>
       <c r="T69" t="n">
-        <v>3.979</v>
+        <v>3.838</v>
       </c>
       <c r="U69" t="n">
-        <v>3.617</v>
+        <v>3.541</v>
       </c>
       <c r="V69" t="n">
-        <v>3.519</v>
+        <v>3.387</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y69" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA69" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB69" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -9158,82 +9271,84 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3.373</v>
+        <v>0.84</v>
       </c>
       <c r="F70" t="n">
-        <v>2.875</v>
+        <v>0.374</v>
       </c>
       <c r="G70" t="n">
-        <v>3.812</v>
+        <v>1.296</v>
       </c>
       <c r="H70" t="n">
-        <v>3.046</v>
+        <v>0.513</v>
       </c>
       <c r="I70" t="n">
-        <v>3.729</v>
+        <v>1.173</v>
       </c>
       <c r="J70" t="n">
-        <v>3.373</v>
+        <v>3.291</v>
       </c>
       <c r="K70" t="n">
-        <v>2.875</v>
+        <v>2.825</v>
       </c>
       <c r="L70" t="n">
-        <v>3.812</v>
+        <v>3.747</v>
       </c>
       <c r="M70" t="n">
-        <v>3.046</v>
+        <v>2.964</v>
       </c>
       <c r="N70" t="n">
-        <v>3.729</v>
+        <v>3.624</v>
       </c>
       <c r="O70" t="n">
-        <v>3.701</v>
+        <v>1.132</v>
       </c>
       <c r="P70" t="n">
-        <v>3.812</v>
+        <v>1.296</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.103</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="R70" t="n">
-        <v>2.875</v>
+        <v>0.374</v>
       </c>
       <c r="S70" t="n">
-        <v>3.701</v>
+        <v>3.583</v>
       </c>
       <c r="T70" t="n">
-        <v>3.812</v>
+        <v>3.747</v>
       </c>
       <c r="U70" t="n">
-        <v>3.103</v>
+        <v>3.011</v>
       </c>
       <c r="V70" t="n">
-        <v>2.875</v>
+        <v>2.825</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y70" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA70" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB70" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -9255,82 +9370,84 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.284</v>
+        <v>0.793</v>
       </c>
       <c r="F71" t="n">
-        <v>2.667</v>
+        <v>0.266</v>
       </c>
       <c r="G71" t="n">
-        <v>3.87</v>
+        <v>1.333</v>
       </c>
       <c r="H71" t="n">
-        <v>2.776</v>
+        <v>0.327</v>
       </c>
       <c r="I71" t="n">
-        <v>3.806</v>
+        <v>1.253</v>
       </c>
       <c r="J71" t="n">
-        <v>3.284</v>
+        <v>3.244</v>
       </c>
       <c r="K71" t="n">
-        <v>2.667</v>
+        <v>2.717</v>
       </c>
       <c r="L71" t="n">
-        <v>3.87</v>
+        <v>3.784</v>
       </c>
       <c r="M71" t="n">
-        <v>2.776</v>
+        <v>2.778</v>
       </c>
       <c r="N71" t="n">
-        <v>3.806</v>
+        <v>3.704</v>
       </c>
       <c r="O71" t="n">
-        <v>3.785</v>
+        <v>1.226</v>
       </c>
       <c r="P71" t="n">
-        <v>3.87</v>
+        <v>1.333</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.812</v>
+        <v>0.347</v>
       </c>
       <c r="R71" t="n">
-        <v>2.667</v>
+        <v>0.266</v>
       </c>
       <c r="S71" t="n">
-        <v>3.785</v>
+        <v>3.677</v>
       </c>
       <c r="T71" t="n">
-        <v>3.87</v>
+        <v>3.784</v>
       </c>
       <c r="U71" t="n">
-        <v>2.812</v>
+        <v>2.798</v>
       </c>
       <c r="V71" t="n">
-        <v>2.667</v>
+        <v>2.717</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>-2.451</v>
+      </c>
       <c r="Y71" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="AA71" t="n">
-        <v>4.632</v>
+        <v>2.75</v>
       </c>
       <c r="AB71" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14166,6 +14283,699 @@
         <v>0</v>
       </c>
       <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="G121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="I121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="J121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="K121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="M121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="N121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="O121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="S121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="T121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="U121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="V121" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X121" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y121" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA121" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="F122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="G122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="H122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="I122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="K122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="L122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="N122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="O122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="P122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="S122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="T122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="U122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="V122" t="n">
+        <v>7.682</v>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y122" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA122" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6.727</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.722</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6.732</v>
+      </c>
+      <c r="H123" t="n">
+        <v>6.725</v>
+      </c>
+      <c r="I123" t="n">
+        <v>6.728</v>
+      </c>
+      <c r="J123" t="n">
+        <v>6.807</v>
+      </c>
+      <c r="K123" t="n">
+        <v>6.803</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6.813</v>
+      </c>
+      <c r="M123" t="n">
+        <v>6.806</v>
+      </c>
+      <c r="N123" t="n">
+        <v>6.809</v>
+      </c>
+      <c r="O123" t="n">
+        <v>6.726</v>
+      </c>
+      <c r="P123" t="n">
+        <v>6.732</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>6.727</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6.722</v>
+      </c>
+      <c r="S123" t="n">
+        <v>6.807</v>
+      </c>
+      <c r="T123" t="n">
+        <v>6.813</v>
+      </c>
+      <c r="U123" t="n">
+        <v>6.807</v>
+      </c>
+      <c r="V123" t="n">
+        <v>6.803</v>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X123" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y123" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA123" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.129</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6.132</v>
+      </c>
+      <c r="H124" t="n">
+        <v>6.129</v>
+      </c>
+      <c r="I124" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="J124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="L124" t="n">
+        <v>6.212</v>
+      </c>
+      <c r="M124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="N124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="O124" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="P124" t="n">
+        <v>6.132</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6.129</v>
+      </c>
+      <c r="S124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="T124" t="n">
+        <v>6.212</v>
+      </c>
+      <c r="U124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="V124" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X124" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y124" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA124" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6.022</v>
+      </c>
+      <c r="H125" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="I125" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="J125" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="K125" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6.103</v>
+      </c>
+      <c r="M125" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="O125" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="P125" t="n">
+        <v>6.022</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="T125" t="n">
+        <v>6.103</v>
+      </c>
+      <c r="U125" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="V125" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X125" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y125" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA125" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5.967</v>
+      </c>
+      <c r="H126" t="n">
+        <v>5.936</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5.965</v>
+      </c>
+      <c r="J126" t="n">
+        <v>6.031</v>
+      </c>
+      <c r="K126" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6.047</v>
+      </c>
+      <c r="M126" t="n">
+        <v>6.016</v>
+      </c>
+      <c r="N126" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="O126" t="n">
+        <v>5.964</v>
+      </c>
+      <c r="P126" t="n">
+        <v>5.967</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>5.937</v>
+      </c>
+      <c r="R126" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="S126" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6.047</v>
+      </c>
+      <c r="U126" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="V126" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y126" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA126" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ajuste aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5.821</v>
+      </c>
+      <c r="F127" t="n">
+        <v>5.795</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5.849</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5.797</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.844</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5.901</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="L127" t="n">
+        <v>5.929</v>
+      </c>
+      <c r="M127" t="n">
+        <v>5.877</v>
+      </c>
+      <c r="N127" t="n">
+        <v>5.924</v>
+      </c>
+      <c r="O127" t="n">
+        <v>5.842</v>
+      </c>
+      <c r="P127" t="n">
+        <v>5.849</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>5.798</v>
+      </c>
+      <c r="R127" t="n">
+        <v>5.795</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5.923</v>
+      </c>
+      <c r="T127" t="n">
+        <v>5.929</v>
+      </c>
+      <c r="U127" t="n">
+        <v>5.878</v>
+      </c>
+      <c r="V127" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y127" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="AA127" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC127" t="inlineStr">
         <is>
           <t>Ajuste aplicado</t>
         </is>
@@ -14182,7 +14992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14521,25 +15331,25 @@
         <v>9037610</v>
       </c>
       <c r="C11" t="n">
-        <v>5.362</v>
+        <v>2.75</v>
       </c>
       <c r="D11" t="n">
-        <v>5.18</v>
+        <v>2.618</v>
       </c>
       <c r="E11" t="n">
-        <v>4.878</v>
+        <v>2.36</v>
       </c>
       <c r="F11" t="n">
-        <v>4.296</v>
+        <v>1.665</v>
       </c>
       <c r="G11" t="n">
-        <v>3.731</v>
+        <v>1.17</v>
       </c>
       <c r="H11" t="n">
-        <v>3.373</v>
+        <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>3.284</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="12">
@@ -14757,6 +15567,37 @@
       </c>
       <c r="I18" t="n">
         <v>2.678</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.727</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.821</v>
       </c>
     </row>
   </sheetData>
@@ -14770,7 +15611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14926,51 +15767,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Puerto Almendra</t>
+          <t>Timicurillo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9037610</v>
+        <v>9036459</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46203</v>
+        <v>46246</v>
       </c>
       <c r="E4" t="n">
-        <v>4.632</v>
+        <v>7.74</v>
       </c>
       <c r="F4" t="n">
-        <v>5.362</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>7.82</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.08</v>
+      </c>
       <c r="H4" t="n">
-        <v>5.362</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>7.74</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 45 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Santa María de Nanay</t>
+          <t>Puerto Almendra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9037738</v>
+        <v>9037610</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46248</v>
@@ -14979,16 +15824,16 @@
         <v>46248</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="F5" t="n">
-        <v>6.293</v>
+        <v>5.201</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.193</v>
+        <v>-2.451</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15003,42 +15848,42 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Offset alto: -2.19 m. Revisar estación.</t>
+          <t>Offset alto: -2.45 m. Revisar estación.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENAPU</t>
+          <t>Santa María de Nanay</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9038134</v>
+        <v>9037738</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E6" t="n">
-        <v>5.32</v>
+        <v>4.1</v>
       </c>
       <c r="F6" t="n">
-        <v>108.064</v>
+        <v>6.293</v>
       </c>
       <c r="G6" t="n">
-        <v>-102.744</v>
+        <v>-2.193</v>
       </c>
       <c r="H6" t="n">
-        <v>5.32</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -15047,42 +15892,42 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Offset alto: -102.74 m. Revisar estación.</t>
+          <t>Offset alto: -2.19 m. Revisar estación.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tamshiyacu</t>
+          <t>ENAPU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9038269</v>
+        <v>9038134</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>5.32</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>108.064</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-102.744</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>5.32</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -15091,18 +15936,18 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -102.74 m. Revisar estación.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Tamshiyacu</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9039635</v>
+        <v>9038269</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46248</v>
@@ -15111,16 +15956,16 @@
         <v>46248</v>
       </c>
       <c r="E8" t="n">
-        <v>4.39</v>
+        <v>3.1</v>
       </c>
       <c r="F8" t="n">
-        <v>4.848</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.458</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.39</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -15142,11 +15987,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Borja</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9040208</v>
+        <v>9039635</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46248</v>
@@ -15155,16 +16000,16 @@
         <v>46248</v>
       </c>
       <c r="E9" t="n">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="F9" t="n">
-        <v>4.798</v>
+        <v>4.848</v>
       </c>
       <c r="G9" t="n">
-        <v>0.222</v>
+        <v>-0.458</v>
       </c>
       <c r="H9" t="n">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15186,11 +16031,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>San Regis</t>
+          <t>Borja</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9040439</v>
+        <v>9040208</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46248</v>
@@ -15199,16 +16044,16 @@
         <v>46248</v>
       </c>
       <c r="E10" t="n">
-        <v>6.12</v>
+        <v>5.02</v>
       </c>
       <c r="F10" t="n">
-        <v>6.229</v>
+        <v>4.798</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.109</v>
+        <v>0.222</v>
       </c>
       <c r="H10" t="n">
-        <v>6.12</v>
+        <v>5.02</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15230,11 +16075,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nauta</t>
+          <t>San Regis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9040454</v>
+        <v>9040439</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46248</v>
@@ -15243,16 +16088,16 @@
         <v>46248</v>
       </c>
       <c r="E11" t="n">
-        <v>7.38</v>
+        <v>6.12</v>
       </c>
       <c r="F11" t="n">
-        <v>5.822</v>
+        <v>6.229</v>
       </c>
       <c r="G11" t="n">
-        <v>1.558</v>
+        <v>-0.109</v>
       </c>
       <c r="H11" t="n">
-        <v>7.38</v>
+        <v>6.12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15267,102 +16112,102 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Offset alto: 1.56 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Nauta</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9042153</v>
+        <v>9040454</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45930</v>
+        <v>46248</v>
       </c>
       <c r="E12" t="n">
-        <v>7.19</v>
+        <v>7.38</v>
       </c>
       <c r="F12" t="n">
-        <v>10.102</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>5.822</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.558</v>
+      </c>
       <c r="H12" t="n">
-        <v>10.102</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>7.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
       <c r="J12" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 318 días</t>
+          <t>Offset alto: 1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Genaro Herrera</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9042214</v>
+        <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46248</v>
+        <v>45930</v>
       </c>
       <c r="E13" t="n">
-        <v>7.37</v>
+        <v>7.19</v>
       </c>
       <c r="F13" t="n">
-        <v>7.744</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.374</v>
-      </c>
+        <v>10.102</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+        <v>10.102</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Observado muy antiguo para ajuste: 318 días</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Angamos</t>
+          <t>Genaro Herrera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9043370</v>
+        <v>9042214</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46248</v>
@@ -15371,16 +16216,16 @@
         <v>46248</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8</v>
+        <v>7.37</v>
       </c>
       <c r="F14" t="n">
-        <v>7.93</v>
+        <v>7.744</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.13</v>
+        <v>-0.374</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>7.37</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15395,18 +16240,18 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Offset alto: -5.13 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Angamos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9043425</v>
+        <v>9043370</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46248</v>
@@ -15415,16 +16260,16 @@
         <v>46248</v>
       </c>
       <c r="E15" t="n">
-        <v>6.54</v>
+        <v>2.8</v>
       </c>
       <c r="F15" t="n">
-        <v>6.322</v>
+        <v>7.93</v>
       </c>
       <c r="G15" t="n">
-        <v>0.218</v>
+        <v>-5.13</v>
       </c>
       <c r="H15" t="n">
-        <v>6.54</v>
+        <v>2.8</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15439,18 +16284,18 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -5.13 m. Revisar estación.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lagunas</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9043597</v>
+        <v>9043425</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46248</v>
@@ -15459,16 +16304,16 @@
         <v>46248</v>
       </c>
       <c r="E16" t="n">
-        <v>4.79</v>
+        <v>6.54</v>
       </c>
       <c r="F16" t="n">
-        <v>5.124</v>
+        <v>6.322</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.334</v>
+        <v>0.218</v>
       </c>
       <c r="H16" t="n">
-        <v>4.79</v>
+        <v>6.54</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15490,82 +16335,126 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flor de Punga</t>
+          <t>Lagunas</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9044756</v>
+        <v>9043597</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46156</v>
+        <v>46248</v>
       </c>
       <c r="E17" t="n">
-        <v>22.8</v>
+        <v>4.79</v>
       </c>
       <c r="F17" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>5.124</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.334</v>
+      </c>
       <c r="H17" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>4.79</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
       <c r="J17" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 92 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Flor de Punga</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9044756</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>92</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Observado muy antiguo para ajuste: 92 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Contamana</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>9053555</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="C19" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E19" t="n">
         <v>6.03</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>11.464</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>-5.434</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>6.03</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Offset alto: -5.43 m. Revisar estación.</t>
         </is>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.532</v>
+        <v>3.531</v>
       </c>
       <c r="H4" t="n">
         <v>3.879</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="H5" t="n">
         <v>6.353</v>
       </c>
       <c r="I5" t="n">
-        <v>6.431</v>
+        <v>6.432</v>
       </c>
       <c r="J5" t="n">
         <v>6.355</v>
@@ -1698,7 +1698,7 @@
         <v>9.438000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9.602</v>
+        <v>9.601000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>9.698</v>
@@ -1707,10 +1707,10 @@
         <v>9.698</v>
       </c>
       <c r="K13" t="n">
-        <v>9.494</v>
+        <v>9.491</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.204</v>
+        <v>-0.207</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         <v>3.133</v>
       </c>
       <c r="K17" t="n">
-        <v>2.59</v>
+        <v>2.589</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.543</v>
+        <v>-0.544</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>46265</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>10242</v>
+        <v>10241</v>
       </c>
       <c r="V17" t="n">
         <v>0.868</v>
@@ -2159,7 +2159,7 @@
         <v>0.847</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.683</v>
+        <v>1.682</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -3049,22 +3049,22 @@
         <v>1.126</v>
       </c>
       <c r="F7" t="n">
-        <v>1.119</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.131</v>
+        <v>1.132</v>
       </c>
       <c r="H7" t="n">
         <v>1.122</v>
       </c>
       <c r="I7" t="n">
-        <v>1.131</v>
+        <v>1.132</v>
       </c>
       <c r="J7" t="n">
         <v>7.443</v>
       </c>
       <c r="K7" t="n">
-        <v>7.436</v>
+        <v>7.437</v>
       </c>
       <c r="L7" t="n">
         <v>7.448</v>
@@ -3076,16 +3076,16 @@
         <v>7.448</v>
       </c>
       <c r="O7" t="n">
-        <v>1.131</v>
+        <v>1.132</v>
       </c>
       <c r="P7" t="n">
-        <v>1.131</v>
+        <v>1.132</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.122</v>
+        <v>1.123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.119</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
         <v>7.448</v>
@@ -3094,10 +3094,10 @@
         <v>7.448</v>
       </c>
       <c r="U7" t="n">
-        <v>7.439</v>
+        <v>7.44</v>
       </c>
       <c r="V7" t="n">
-        <v>7.436</v>
+        <v>7.437</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>4.146</v>
       </c>
       <c r="K19" t="n">
-        <v>4.128</v>
+        <v>4.129</v>
       </c>
       <c r="L19" t="n">
         <v>4.169</v>
@@ -4285,7 +4285,7 @@
         <v>4.13</v>
       </c>
       <c r="V19" t="n">
-        <v>4.128</v>
+        <v>4.129</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>3.812</v>
       </c>
       <c r="G20" t="n">
-        <v>3.894</v>
+        <v>3.893</v>
       </c>
       <c r="H20" t="n">
         <v>3.821</v>
@@ -4360,13 +4360,13 @@
         <v>4.072</v>
       </c>
       <c r="N20" t="n">
-        <v>4.132</v>
+        <v>4.133</v>
       </c>
       <c r="O20" t="n">
         <v>3.878</v>
       </c>
       <c r="P20" t="n">
-        <v>3.894</v>
+        <v>3.893</v>
       </c>
       <c r="Q20" t="n">
         <v>3.824</v>
@@ -4375,7 +4375,7 @@
         <v>3.812</v>
       </c>
       <c r="S20" t="n">
-        <v>4.128</v>
+        <v>4.129</v>
       </c>
       <c r="T20" t="n">
         <v>4.144</v>
@@ -4453,7 +4453,7 @@
         <v>3.917</v>
       </c>
       <c r="L21" t="n">
-        <v>4.119</v>
+        <v>4.118</v>
       </c>
       <c r="M21" t="n">
         <v>3.993</v>
@@ -4477,7 +4477,7 @@
         <v>4.066</v>
       </c>
       <c r="T21" t="n">
-        <v>4.119</v>
+        <v>4.118</v>
       </c>
       <c r="U21" t="n">
         <v>4.018</v>
@@ -4534,7 +4534,7 @@
         <v>3.691</v>
       </c>
       <c r="F22" t="n">
-        <v>3.532</v>
+        <v>3.531</v>
       </c>
       <c r="G22" t="n">
         <v>3.795</v>
@@ -4570,7 +4570,7 @@
         <v>3.738</v>
       </c>
       <c r="R22" t="n">
-        <v>3.532</v>
+        <v>3.531</v>
       </c>
       <c r="S22" t="n">
         <v>3.95</v>
@@ -4828,19 +4828,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="F25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="G25" t="n">
         <v>6.305</v>
       </c>
       <c r="H25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="I25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="J25" t="n">
         <v>12.059</v>
@@ -4861,13 +4861,13 @@
         <v>6.305</v>
       </c>
       <c r="P25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="R25" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="S25" t="n">
         <v>12.059</v>
@@ -4927,19 +4927,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="F26" t="n">
         <v>6.313</v>
       </c>
       <c r="G26" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="H26" t="n">
         <v>6.313</v>
       </c>
       <c r="I26" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="J26" t="n">
         <v>12.068</v>
@@ -4957,10 +4957,10 @@
         <v>12.068</v>
       </c>
       <c r="O26" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="P26" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="Q26" t="n">
         <v>6.313</v>
@@ -5026,19 +5026,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.349</v>
+        <v>6.35</v>
       </c>
       <c r="F27" t="n">
         <v>6.348</v>
       </c>
       <c r="G27" t="n">
-        <v>6.35</v>
+        <v>6.351</v>
       </c>
       <c r="H27" t="n">
-        <v>6.348</v>
+        <v>6.349</v>
       </c>
       <c r="I27" t="n">
-        <v>6.35</v>
+        <v>6.351</v>
       </c>
       <c r="J27" t="n">
         <v>12.104</v>
@@ -5056,13 +5056,13 @@
         <v>12.105</v>
       </c>
       <c r="O27" t="n">
-        <v>6.35</v>
+        <v>6.351</v>
       </c>
       <c r="P27" t="n">
-        <v>6.35</v>
+        <v>6.351</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.348</v>
+        <v>6.349</v>
       </c>
       <c r="R27" t="n">
         <v>6.348</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.392</v>
+        <v>6.393</v>
       </c>
       <c r="F28" t="n">
         <v>6.392</v>
@@ -5161,7 +5161,7 @@
         <v>6.393</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.392</v>
+        <v>6.393</v>
       </c>
       <c r="R28" t="n">
         <v>6.392</v>
@@ -5230,13 +5230,13 @@
         <v>6.431</v>
       </c>
       <c r="G29" t="n">
-        <v>6.431</v>
+        <v>6.432</v>
       </c>
       <c r="H29" t="n">
         <v>6.431</v>
       </c>
       <c r="I29" t="n">
-        <v>6.431</v>
+        <v>6.432</v>
       </c>
       <c r="J29" t="n">
         <v>12.186</v>
@@ -5254,10 +5254,10 @@
         <v>12.186</v>
       </c>
       <c r="O29" t="n">
-        <v>6.431</v>
+        <v>6.432</v>
       </c>
       <c r="P29" t="n">
-        <v>6.431</v>
+        <v>6.432</v>
       </c>
       <c r="Q29" t="n">
         <v>6.431</v>
@@ -6113,58 +6113,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="P38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="S38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="V38" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6601,13 +6601,13 @@
         <v>8.337999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="G43" t="n">
         <v>8.339</v>
       </c>
       <c r="H43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>8.337999999999999</v>
@@ -6616,13 +6616,13 @@
         <v>8.337999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="L43" t="n">
         <v>8.339</v>
       </c>
       <c r="M43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>8.337999999999999</v>
@@ -6634,10 +6634,10 @@
         <v>8.339</v>
       </c>
       <c r="Q43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="R43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="S43" t="n">
         <v>8.337999999999999</v>
@@ -6646,10 +6646,10 @@
         <v>8.339</v>
       </c>
       <c r="U43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="V43" t="n">
-        <v>8.337</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -7190,58 +7190,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="F49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="G49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="H49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="I49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="J49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="K49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="L49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="M49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="N49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="O49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="P49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="R49" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="S49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="T49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="U49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="V49" t="n">
-        <v>7.323</v>
+        <v>7.322</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -7304,19 +7304,19 @@
         <v>7.966</v>
       </c>
       <c r="J50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="K50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="L50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="M50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="N50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="O50" t="n">
         <v>7.966</v>
@@ -7331,16 +7331,16 @@
         <v>7.966</v>
       </c>
       <c r="S50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="T50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="U50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="V50" t="n">
-        <v>7.359</v>
+        <v>7.36</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -7586,58 +7586,58 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="F53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="G53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="H53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="I53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="J53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="K53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="L53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="M53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="N53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="O53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="P53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="R53" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="S53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="T53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="U53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="V53" t="n">
-        <v>5.769</v>
+        <v>5.772</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>5.531</v>
       </c>
       <c r="G55" t="n">
-        <v>5.531</v>
+        <v>5.532</v>
       </c>
       <c r="H55" t="n">
         <v>5.531</v>
@@ -7799,25 +7799,25 @@
         <v>5.531</v>
       </c>
       <c r="J55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="K55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="L55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="M55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="N55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="O55" t="n">
         <v>5.531</v>
       </c>
       <c r="P55" t="n">
-        <v>5.531</v>
+        <v>5.532</v>
       </c>
       <c r="Q55" t="n">
         <v>5.531</v>
@@ -7826,16 +7826,16 @@
         <v>5.531</v>
       </c>
       <c r="S55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="T55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="U55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="V55" t="n">
-        <v>5.686</v>
+        <v>5.687</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -7889,25 +7889,25 @@
         <v>5.335</v>
       </c>
       <c r="G56" t="n">
-        <v>5.335</v>
+        <v>5.336</v>
       </c>
       <c r="H56" t="n">
         <v>5.335</v>
       </c>
       <c r="I56" t="n">
-        <v>5.335</v>
+        <v>5.336</v>
       </c>
       <c r="J56" t="n">
-        <v>5.49</v>
+        <v>5.491</v>
       </c>
       <c r="K56" t="n">
-        <v>5.49</v>
+        <v>5.491</v>
       </c>
       <c r="L56" t="n">
         <v>5.491</v>
       </c>
       <c r="M56" t="n">
-        <v>5.49</v>
+        <v>5.491</v>
       </c>
       <c r="N56" t="n">
         <v>5.491</v>
@@ -7916,7 +7916,7 @@
         <v>5.335</v>
       </c>
       <c r="P56" t="n">
-        <v>5.335</v>
+        <v>5.336</v>
       </c>
       <c r="Q56" t="n">
         <v>5.335</v>
@@ -7931,10 +7931,10 @@
         <v>5.491</v>
       </c>
       <c r="U56" t="n">
-        <v>5.49</v>
+        <v>5.491</v>
       </c>
       <c r="V56" t="n">
-        <v>5.49</v>
+        <v>5.491</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>2.712</v>
       </c>
       <c r="F66" t="n">
-        <v>2.709</v>
+        <v>2.708</v>
       </c>
       <c r="G66" t="n">
         <v>2.717</v>
@@ -8891,7 +8891,7 @@
         <v>3.21</v>
       </c>
       <c r="K66" t="n">
-        <v>3.207</v>
+        <v>3.206</v>
       </c>
       <c r="L66" t="n">
         <v>3.215</v>
@@ -8912,7 +8912,7 @@
         <v>2.709</v>
       </c>
       <c r="R66" t="n">
-        <v>2.709</v>
+        <v>2.708</v>
       </c>
       <c r="S66" t="n">
         <v>3.211</v>
@@ -8924,7 +8924,7 @@
         <v>3.207</v>
       </c>
       <c r="V66" t="n">
-        <v>3.207</v>
+        <v>3.206</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>2.513</v>
       </c>
       <c r="G67" t="n">
-        <v>2.575</v>
+        <v>2.574</v>
       </c>
       <c r="H67" t="n">
         <v>2.518</v>
@@ -8993,7 +8993,7 @@
         <v>3.011</v>
       </c>
       <c r="L67" t="n">
-        <v>3.073</v>
+        <v>3.072</v>
       </c>
       <c r="M67" t="n">
         <v>3.016</v>
@@ -9005,7 +9005,7 @@
         <v>2.558</v>
       </c>
       <c r="P67" t="n">
-        <v>2.575</v>
+        <v>2.574</v>
       </c>
       <c r="Q67" t="n">
         <v>2.52</v>
@@ -9017,7 +9017,7 @@
         <v>3.056</v>
       </c>
       <c r="T67" t="n">
-        <v>3.073</v>
+        <v>3.072</v>
       </c>
       <c r="U67" t="n">
         <v>3.018</v>
@@ -9074,7 +9074,7 @@
         <v>2.54</v>
       </c>
       <c r="F68" t="n">
-        <v>2.483</v>
+        <v>2.484</v>
       </c>
       <c r="G68" t="n">
         <v>2.609</v>
@@ -9089,7 +9089,7 @@
         <v>3.038</v>
       </c>
       <c r="K68" t="n">
-        <v>2.981</v>
+        <v>2.982</v>
       </c>
       <c r="L68" t="n">
         <v>3.107</v>
@@ -9110,7 +9110,7 @@
         <v>2.488</v>
       </c>
       <c r="R68" t="n">
-        <v>2.483</v>
+        <v>2.484</v>
       </c>
       <c r="S68" t="n">
         <v>3.077</v>
@@ -9122,7 +9122,7 @@
         <v>2.986</v>
       </c>
       <c r="V68" t="n">
-        <v>2.981</v>
+        <v>2.982</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>2.37</v>
       </c>
       <c r="I69" t="n">
-        <v>2.581</v>
+        <v>2.58</v>
       </c>
       <c r="J69" t="n">
         <v>2.975</v>
@@ -9197,10 +9197,10 @@
         <v>2.868</v>
       </c>
       <c r="N69" t="n">
-        <v>3.079</v>
+        <v>3.078</v>
       </c>
       <c r="O69" t="n">
-        <v>2.575</v>
+        <v>2.574</v>
       </c>
       <c r="P69" t="n">
         <v>2.598</v>
@@ -9212,7 +9212,7 @@
         <v>2.363</v>
       </c>
       <c r="S69" t="n">
-        <v>3.073</v>
+        <v>3.072</v>
       </c>
       <c r="T69" t="n">
         <v>3.096</v>
@@ -9275,7 +9275,7 @@
         <v>2.187</v>
       </c>
       <c r="G70" t="n">
-        <v>2.477</v>
+        <v>2.478</v>
       </c>
       <c r="H70" t="n">
         <v>2.204</v>
@@ -9290,7 +9290,7 @@
         <v>2.685</v>
       </c>
       <c r="L70" t="n">
-        <v>2.975</v>
+        <v>2.976</v>
       </c>
       <c r="M70" t="n">
         <v>2.702</v>
@@ -9302,7 +9302,7 @@
         <v>2.373</v>
       </c>
       <c r="P70" t="n">
-        <v>2.477</v>
+        <v>2.478</v>
       </c>
       <c r="Q70" t="n">
         <v>2.21</v>
@@ -9314,7 +9314,7 @@
         <v>2.871</v>
       </c>
       <c r="T70" t="n">
-        <v>2.975</v>
+        <v>2.976</v>
       </c>
       <c r="U70" t="n">
         <v>2.708</v>
@@ -10645,31 +10645,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>9.553000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>9.545999999999999</v>
+        <v>9.539</v>
       </c>
       <c r="G84" t="n">
         <v>9.563000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>9.547000000000001</v>
+        <v>9.539</v>
       </c>
       <c r="I84" t="n">
         <v>9.56</v>
       </c>
       <c r="J84" t="n">
-        <v>9.553000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>9.545999999999999</v>
+        <v>9.539</v>
       </c>
       <c r="L84" t="n">
         <v>9.563000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>9.547000000000001</v>
+        <v>9.539</v>
       </c>
       <c r="N84" t="n">
         <v>9.56</v>
@@ -10681,10 +10681,10 @@
         <v>9.563000000000001</v>
       </c>
       <c r="Q84" t="n">
-        <v>9.547000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="R84" t="n">
-        <v>9.545999999999999</v>
+        <v>9.539</v>
       </c>
       <c r="S84" t="n">
         <v>9.558999999999999</v>
@@ -10693,10 +10693,10 @@
         <v>9.563000000000001</v>
       </c>
       <c r="U84" t="n">
-        <v>9.547000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="V84" t="n">
-        <v>9.545999999999999</v>
+        <v>9.539</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -10742,40 +10742,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>9.494</v>
+        <v>9.491</v>
       </c>
       <c r="F85" t="n">
         <v>9.438000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>9.552</v>
+        <v>9.542</v>
       </c>
       <c r="H85" t="n">
         <v>9.446</v>
       </c>
       <c r="I85" t="n">
-        <v>9.539999999999999</v>
+        <v>9.536</v>
       </c>
       <c r="J85" t="n">
-        <v>9.494</v>
+        <v>9.491</v>
       </c>
       <c r="K85" t="n">
         <v>9.438000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>9.552</v>
+        <v>9.542</v>
       </c>
       <c r="M85" t="n">
         <v>9.446</v>
       </c>
       <c r="N85" t="n">
-        <v>9.539999999999999</v>
+        <v>9.536</v>
       </c>
       <c r="O85" t="n">
-        <v>9.536</v>
+        <v>9.534000000000001</v>
       </c>
       <c r="P85" t="n">
-        <v>9.552</v>
+        <v>9.542</v>
       </c>
       <c r="Q85" t="n">
         <v>9.449</v>
@@ -10784,10 +10784,10 @@
         <v>9.438000000000001</v>
       </c>
       <c r="S85" t="n">
-        <v>9.536</v>
+        <v>9.534000000000001</v>
       </c>
       <c r="T85" t="n">
-        <v>9.552</v>
+        <v>9.542</v>
       </c>
       <c r="U85" t="n">
         <v>9.449</v>
@@ -11334,19 +11334,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="F91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="G91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="H91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="I91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="J91" t="n">
         <v>5.492</v>
@@ -11364,16 +11364,16 @@
         <v>5.492</v>
       </c>
       <c r="O91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="P91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="R91" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="S91" t="n">
         <v>5.492</v>
@@ -11745,19 +11745,19 @@
         <v>8.336</v>
       </c>
       <c r="J95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="K95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="L95" t="n">
         <v>6.552</v>
       </c>
       <c r="M95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="N95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="O95" t="n">
         <v>8.336</v>
@@ -11772,16 +11772,16 @@
         <v>8.336</v>
       </c>
       <c r="S95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="T95" t="n">
         <v>6.552</v>
       </c>
       <c r="U95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="V95" t="n">
-        <v>6.551</v>
+        <v>6.552</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -12027,16 +12027,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="G98" t="n">
         <v>8.282999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="I98" t="n">
         <v>8.282999999999999</v>
@@ -12057,13 +12057,13 @@
         <v>6.498</v>
       </c>
       <c r="O98" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="P98" t="n">
         <v>8.282999999999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="R98" t="n">
         <v>8.282999999999999</v>
@@ -12243,13 +12243,13 @@
         <v>4.43</v>
       </c>
       <c r="K100" t="n">
-        <v>4.428</v>
+        <v>4.429</v>
       </c>
       <c r="L100" t="n">
         <v>4.432</v>
       </c>
       <c r="M100" t="n">
-        <v>4.428</v>
+        <v>4.429</v>
       </c>
       <c r="N100" t="n">
         <v>4.431</v>
@@ -12273,10 +12273,10 @@
         <v>4.432</v>
       </c>
       <c r="U100" t="n">
-        <v>4.428</v>
+        <v>4.429</v>
       </c>
       <c r="V100" t="n">
-        <v>4.428</v>
+        <v>4.429</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4.356</v>
+        <v>4.355</v>
       </c>
       <c r="F101" t="n">
         <v>4.31</v>
@@ -12354,7 +12354,7 @@
         <v>4.345</v>
       </c>
       <c r="O101" t="n">
-        <v>4.393</v>
+        <v>4.392</v>
       </c>
       <c r="P101" t="n">
         <v>4.403</v>
@@ -12453,7 +12453,7 @@
         <v>4.465</v>
       </c>
       <c r="O102" t="n">
-        <v>4.509</v>
+        <v>4.508</v>
       </c>
       <c r="P102" t="n">
         <v>4.535</v>
@@ -12624,7 +12624,7 @@
         <v>4.17</v>
       </c>
       <c r="F104" t="n">
-        <v>3.965</v>
+        <v>3.964</v>
       </c>
       <c r="G104" t="n">
         <v>4.392</v>
@@ -12657,10 +12657,10 @@
         <v>4.392</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.054</v>
+        <v>4.053</v>
       </c>
       <c r="R104" t="n">
-        <v>3.965</v>
+        <v>3.964</v>
       </c>
       <c r="S104" t="n">
         <v>4.221</v>
@@ -12723,7 +12723,7 @@
         <v>3.963</v>
       </c>
       <c r="F105" t="n">
-        <v>3.682</v>
+        <v>3.681</v>
       </c>
       <c r="G105" t="n">
         <v>4.25</v>
@@ -12732,7 +12732,7 @@
         <v>3.778</v>
       </c>
       <c r="I105" t="n">
-        <v>4.145</v>
+        <v>4.144</v>
       </c>
       <c r="J105" t="n">
         <v>3.913</v>
@@ -12759,7 +12759,7 @@
         <v>3.81</v>
       </c>
       <c r="R105" t="n">
-        <v>3.682</v>
+        <v>3.681</v>
       </c>
       <c r="S105" t="n">
         <v>4.059</v>
@@ -12825,13 +12825,13 @@
         <v>3.651</v>
       </c>
       <c r="G106" t="n">
-        <v>4.294</v>
+        <v>4.293</v>
       </c>
       <c r="H106" t="n">
         <v>3.726</v>
       </c>
       <c r="I106" t="n">
-        <v>4.15</v>
+        <v>4.149</v>
       </c>
       <c r="J106" t="n">
         <v>3.899</v>
@@ -12849,10 +12849,10 @@
         <v>4.1</v>
       </c>
       <c r="O106" t="n">
-        <v>4.102</v>
+        <v>4.101</v>
       </c>
       <c r="P106" t="n">
-        <v>4.294</v>
+        <v>4.293</v>
       </c>
       <c r="Q106" t="n">
         <v>3.751</v>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="X107" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y107" s="1" t="n">
         <v>46265</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y108" s="1" t="n">
         <v>46265</v>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2.842</v>
+        <v>2.841</v>
       </c>
       <c r="F109" t="n">
         <v>2.841</v>
@@ -13175,7 +13175,7 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y109" s="1" t="n">
         <v>46265</v>
@@ -13221,7 +13221,7 @@
         <v>2.725</v>
       </c>
       <c r="G110" t="n">
-        <v>2.733</v>
+        <v>2.732</v>
       </c>
       <c r="H110" t="n">
         <v>2.725</v>
@@ -13245,7 +13245,7 @@
         <v>3.381</v>
       </c>
       <c r="O110" t="n">
-        <v>2.733</v>
+        <v>2.732</v>
       </c>
       <c r="P110" t="n">
         <v>2.731</v>
@@ -13274,7 +13274,7 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y110" s="1" t="n">
         <v>46265</v>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2.669</v>
+        <v>2.668</v>
       </c>
       <c r="F111" t="n">
         <v>2.659</v>
@@ -13326,16 +13326,16 @@
         <v>2.664</v>
       </c>
       <c r="I111" t="n">
-        <v>2.673</v>
+        <v>2.672</v>
       </c>
       <c r="J111" t="n">
         <v>3.318</v>
       </c>
       <c r="K111" t="n">
-        <v>3.309</v>
+        <v>3.308</v>
       </c>
       <c r="L111" t="n">
-        <v>3.33</v>
+        <v>3.329</v>
       </c>
       <c r="M111" t="n">
         <v>3.314</v>
@@ -13356,16 +13356,16 @@
         <v>2.666</v>
       </c>
       <c r="S111" t="n">
-        <v>3.33</v>
+        <v>3.329</v>
       </c>
       <c r="T111" t="n">
         <v>3.32</v>
       </c>
       <c r="U111" t="n">
-        <v>3.309</v>
+        <v>3.308</v>
       </c>
       <c r="V111" t="n">
-        <v>3.316</v>
+        <v>3.315</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y111" s="1" t="n">
         <v>46265</v>
@@ -13413,25 +13413,25 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2.609</v>
+        <v>2.608</v>
       </c>
       <c r="F112" t="n">
         <v>2.601</v>
       </c>
       <c r="G112" t="n">
-        <v>2.622</v>
+        <v>2.621</v>
       </c>
       <c r="H112" t="n">
-        <v>2.603</v>
+        <v>2.602</v>
       </c>
       <c r="I112" t="n">
-        <v>2.612</v>
+        <v>2.611</v>
       </c>
       <c r="J112" t="n">
         <v>3.258</v>
       </c>
       <c r="K112" t="n">
-        <v>3.251</v>
+        <v>3.25</v>
       </c>
       <c r="L112" t="n">
         <v>3.271</v>
@@ -13443,7 +13443,7 @@
         <v>3.261</v>
       </c>
       <c r="O112" t="n">
-        <v>2.622</v>
+        <v>2.621</v>
       </c>
       <c r="P112" t="n">
         <v>2.608</v>
@@ -13452,16 +13452,16 @@
         <v>2.601</v>
       </c>
       <c r="R112" t="n">
-        <v>2.603</v>
+        <v>2.602</v>
       </c>
       <c r="S112" t="n">
         <v>3.271</v>
       </c>
       <c r="T112" t="n">
-        <v>3.258</v>
+        <v>3.257</v>
       </c>
       <c r="U112" t="n">
-        <v>3.251</v>
+        <v>3.25</v>
       </c>
       <c r="V112" t="n">
         <v>3.252</v>
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y112" s="1" t="n">
         <v>46265</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2.59</v>
+        <v>2.589</v>
       </c>
       <c r="F113" t="n">
         <v>2.581</v>
       </c>
       <c r="G113" t="n">
-        <v>2.595</v>
+        <v>2.594</v>
       </c>
       <c r="H113" t="n">
         <v>2.588</v>
       </c>
       <c r="I113" t="n">
-        <v>2.594</v>
+        <v>2.593</v>
       </c>
       <c r="J113" t="n">
         <v>3.239</v>
@@ -13536,7 +13536,7 @@
         <v>3.244</v>
       </c>
       <c r="M113" t="n">
-        <v>3.238</v>
+        <v>3.237</v>
       </c>
       <c r="N113" t="n">
         <v>3.243</v>
@@ -13545,16 +13545,16 @@
         <v>2.593</v>
       </c>
       <c r="P113" t="n">
-        <v>2.591</v>
+        <v>2.59</v>
       </c>
       <c r="Q113" t="n">
         <v>2.581</v>
       </c>
       <c r="R113" t="n">
-        <v>2.595</v>
+        <v>2.594</v>
       </c>
       <c r="S113" t="n">
-        <v>3.243</v>
+        <v>3.242</v>
       </c>
       <c r="T113" t="n">
         <v>3.24</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="Y113" s="1" t="n">
         <v>46265</v>
@@ -13809,19 +13809,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="F116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="G116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="H116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="I116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="J116" t="n">
         <v>2.369</v>
@@ -13839,16 +13839,16 @@
         <v>2.369</v>
       </c>
       <c r="O116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="P116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="R116" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="S116" t="n">
         <v>2.369</v>
@@ -15132,16 +15132,16 @@
         <v>6.324</v>
       </c>
       <c r="D5" t="n">
-        <v>6.304</v>
+        <v>6.305</v>
       </c>
       <c r="E5" t="n">
-        <v>6.313</v>
+        <v>6.314</v>
       </c>
       <c r="F5" t="n">
-        <v>6.349</v>
+        <v>6.35</v>
       </c>
       <c r="G5" t="n">
-        <v>6.392</v>
+        <v>6.393</v>
       </c>
       <c r="H5" t="n">
         <v>6.431</v>
@@ -15191,7 +15191,7 @@
         <v>9044756</v>
       </c>
       <c r="C7" t="n">
-        <v>8.186999999999999</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>8.199</v>
@@ -15234,7 +15234,7 @@
         <v>7.877</v>
       </c>
       <c r="G8" t="n">
-        <v>7.929</v>
+        <v>7.928</v>
       </c>
       <c r="H8" t="n">
         <v>7.966</v>
@@ -15256,7 +15256,7 @@
         <v>5.48</v>
       </c>
       <c r="D9" t="n">
-        <v>5.614</v>
+        <v>5.617</v>
       </c>
       <c r="E9" t="n">
         <v>5.617</v>
@@ -15389,10 +15389,10 @@
         <v>9.567</v>
       </c>
       <c r="G13" t="n">
-        <v>9.553000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9.494</v>
+        <v>9.491</v>
       </c>
       <c r="I13" t="n">
         <v>9.698</v>
@@ -15420,7 +15420,7 @@
         <v>6.598</v>
       </c>
       <c r="G14" t="n">
-        <v>6.624</v>
+        <v>6.625</v>
       </c>
       <c r="H14" t="n">
         <v>6.65</v>
@@ -15451,7 +15451,7 @@
         <v>8.308</v>
       </c>
       <c r="G15" t="n">
-        <v>8.282</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>8.236000000000001</v>
@@ -15470,7 +15470,7 @@
         <v>9037738</v>
       </c>
       <c r="C16" t="n">
-        <v>4.356</v>
+        <v>4.355</v>
       </c>
       <c r="D16" t="n">
         <v>4.475</v>
@@ -15504,19 +15504,19 @@
         <v>2.897</v>
       </c>
       <c r="D17" t="n">
-        <v>2.842</v>
+        <v>2.841</v>
       </c>
       <c r="E17" t="n">
         <v>2.728</v>
       </c>
       <c r="F17" t="n">
-        <v>2.669</v>
+        <v>2.668</v>
       </c>
       <c r="G17" t="n">
-        <v>2.609</v>
+        <v>2.608</v>
       </c>
       <c r="H17" t="n">
-        <v>2.59</v>
+        <v>2.589</v>
       </c>
       <c r="I17" t="n">
         <v>3.133</v>
@@ -15535,7 +15535,7 @@
         <v>3.185</v>
       </c>
       <c r="D18" t="n">
-        <v>3.185</v>
+        <v>3.186</v>
       </c>
       <c r="E18" t="n">
         <v>3.19</v>
@@ -15986,7 +15986,7 @@
         <v>3.782</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.649</v>
+        <v>-0.65</v>
       </c>
       <c r="H9" t="n">
         <v>3.133</v>
